--- a/languages/ko/output/import/韩语TOPIK3.xlsx
+++ b/languages/ko/output/import/韩语TOPIK3.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ns͈o̞ɾi]] 盤索里 (文化)</t>
+          <t>[[pʰa̠ns͈o̞ɾi]] 盘索里 (文化)</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ns͈o̞ɾi]] 盤索里 (文化)</t>
+          <t>[[pʰa̠ns͈o̞ɾi]] 盘索里 (文化)</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠muɭɭo̞ɾi]] 四物農樂 (文化)</t>
+          <t>[[sʰa̠muɭɭo̞ɾi]] 四物农乐 (文化)</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠muɭɭo̞ɾi]] 四物農樂 (文化)</t>
+          <t>[[sʰa̠muɭɭo̞ɾi]] 四物农乐 (文化)</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋ]] 情（深厚的情感連結） (文化)</t>
+          <t>[[t͡ɕʌ̹ŋ]] 情（深厚的情感连结） (文化)</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋ]] 情（深厚的情感連結） (文化)</t>
+          <t>[[t͡ɕʌ̹ŋ]] 情（深厚的情感连结） (文化)</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>[[nuɲt͡ɕʰi]] 眼色（社交意識） (文化)</t>
+          <t>[[nuɲt͡ɕʰi]] 眼色（社交意识） (文化)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>[[nuɲt͡ɕʰi]] 眼色（社交意識） (文化)</t>
+          <t>[[nuɲt͡ɕʰi]] 眼色（社交意识） (文化)</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>[[kuɡa̠k̚]] 傳統音樂 (文化)</t>
+          <t>[[kuɡa̠k̚]] 传统音乐 (文化)</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[[kuɡa̠k̚]] 傳統音樂 (文化)</t>
+          <t>[[kuɡa̠k̚]] 传统音乐 (文化)</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -627,13 +627,13 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Curriculum (教育)</t>
+          <t>课程大纲 (教育)</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Curriculum (教育)</t>
+          <t>课程大纲 (教育)</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>[[no̞nmun]] 論文 (教育)</t>
+          <t>[[no̞nmun]] 论文 (教育)</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>[[no̞nmun]] 論文 (教育)</t>
+          <t>[[no̞nmun]] 论文 (教育)</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -687,13 +687,13 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>學位論文 (教育)</t>
+          <t>学位论文 (教育)</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>學位論文 (教育)</t>
+          <t>学位论文 (教育)</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[[sʰunɯŋ]] 大學修業能力測驗 (教育)</t>
+          <t>[[sʰunɯŋ]] 大学修业能力测验 (教育)</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[[sʰunɯŋ]] 大學修業能力測驗 (教育)</t>
+          <t>[[sʰunɯŋ]] 大学修业能力测验 (教育)</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ks͈ɛŋβwe̞]] Student Council (Education)</t>
+          <t>[[ha̠ks͈ɛŋβwe̞]] 学生会 (教育)</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ks͈ɛŋβwe̞]] Student Council (Education)</t>
+          <t>[[ha̠ks͈ɛŋβwe̞]] 学生会 (教育)</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -779,13 +779,13 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>Hopeful (Emotions)</t>
+          <t>充满希望 (情感)</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr"/>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Hopeful (Emotions)</t>
+          <t>充满希望 (情感)</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -807,13 +807,13 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>狂喜 (情緒)</t>
+          <t>狂喜 (情绪)</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr"/>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>狂喜 (情緒)</t>
+          <t>狂喜 (情绪)</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwɘ(ː)nma̠ŋɦa̠da̠]] 怨恨 (情緒)</t>
+          <t>[[ˈwɘ(ː)nma̠ŋɦa̠da̠]] 怨恨 (情绪)</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwɘ(ː)nma̠ŋɦa̠da̠]] 怨恨 (情緒)</t>
+          <t>[[ˈwɘ(ː)nma̠ŋɦa̠da̠]] 怨恨 (情绪)</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>[[muɡwa̠nɕʰimɦa̠da̠]] 冷漠 (情緒)</t>
+          <t>[[muɡwa̠nɕʰimɦa̠da̠]] 冷漠 (情绪)</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[[muɡwa̠nɕʰimɦa̠da̠]] 冷漠 (情緒)</t>
+          <t>[[muɡwa̠nɕʰimɦa̠da̠]] 冷漠 (情绪)</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɦʌ̹ɦa̠da̠]] 空虛 (情緒)</t>
+          <t>[[ko̞ŋɦʌ̹ɦa̠da̠]] 空虚 (情绪)</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɦʌ̹ɦa̠da̠]] 空虛 (情緒)</t>
+          <t>[[ko̞ŋɦʌ̹ɦa̠da̠]] 空虚 (情绪)</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -931,13 +931,13 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>渴望 (情緒)</t>
+          <t>渴望 (情绪)</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr"/>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>渴望 (情緒)</t>
+          <t>渴望 (情绪)</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -959,13 +959,13 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>興高采烈 (情緒)</t>
+          <t>兴高采烈 (情绪)</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr"/>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>興高采烈 (情緒)</t>
+          <t>兴高采烈 (情绪)</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[[muŋkxɯɾɦa̠da̠]] Moved (Emotions)</t>
+          <t>[[muŋkxɯɾɦa̠da̠]] 移动 (情感)</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>[[muŋkxɯɾɦa̠da̠]] Moved (Emotions)</t>
+          <t>[[muŋkxɯɾɦa̠da̠]] 移动 (情感)</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1019,13 +1019,13 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Furious (Emotions)</t>
+          <t>愤怒 (情感)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr"/>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Furious (Emotions)</t>
+          <t>愤怒 (情感)</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1047,13 +1047,13 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Enraged (Emotions)</t>
+          <t>激怒 (情感)</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr"/>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Enraged (Emotions)</t>
+          <t>激怒 (情感)</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] Horrified (Emotions)</t>
+          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] 恐惧 (情感)</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] Horrified (Emotions)</t>
+          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] 恐惧 (情感)</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1107,13 +1107,13 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Determined (Emotions)</t>
+          <t>决心 (情感)</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr"/>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Determined (Emotions)</t>
+          <t>决心 (情感)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] Composed (Emotions)</t>
+          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] 组成 (情感)</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] Composed (Emotions)</t>
+          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] 组成 (情感)</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1167,13 +1167,13 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Bittersweet (Emotions)</t>
+          <t>痛快乐 (情感)</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr"/>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Bittersweet (Emotions)</t>
+          <t>痛快乐 (情感)</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾjʌ̹nɦa̠da̠]] Wistful (Emotions)</t>
+          <t>[[a̠ɾjʌ̹nɦa̠da̠]] 渴望的 (情感)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾjʌ̹nɦa̠da̠]] Wistful (Emotions)</t>
+          <t>[[a̠ɾjʌ̹nɦa̠da̠]] 渴望的 (情感)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɭma̠ŋɦa̠da̠]] Yearning (Emotions)</t>
+          <t>[[ka̠ɭma̠ŋɦa̠da̠]] 渴望&amp;#x0D; (情感)</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɭma̠ŋɦa̠da̠]] Yearning (Emotions)</t>
+          <t>[[ka̠ɭma̠ŋɦa̠da̠]] 渴望&amp;#x0D; (情感)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -1259,13 +1259,13 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>憎恨 (情緒)</t>
+          <t>憎恨 (情绪)</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr"/>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>憎恨 (情緒)</t>
+          <t>憎恨 (情绪)</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (obsessive fan) (文化)</t>
+          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (文化)</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (obsessive fan) (文化)</t>
+          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (文化)</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -1319,13 +1319,13 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>整形手術 (文化)</t>
+          <t>整形手术 (文化)</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr"/>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>整形手術 (文化)</t>
+          <t>整形手术 (文化)</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛbʌ̹ɭ]] 財閥 (文化)</t>
+          <t>[[t͡ɕɛbʌ̹ɭ]] 财阀 (文化)</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛbʌ̹ɭ]] 財閥 (文化)</t>
+          <t>[[t͡ɕɛbʌ̹ɭ]] 财阀 (文化)</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1379,13 +1379,13 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>麻木 (情緒)</t>
+          <t>麻木 (情绪)</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr"/>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>麻木 (情緒)</t>
+          <t>麻木 (情绪)</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] Soy Sauce Crab (Food)</t>
+          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] 花生酱 (食物)</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] Soy Sauce Crab (Food)</t>
+          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] 花生酱 (食物)</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[[isʰɯɭbi]] 毛毛雨 (Nature)</t>
+          <t>[[isʰɯɭbi]] 毛毛雨 (自然)</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>[[isʰɯɭbi]] 毛毛雨 (Nature)</t>
+          <t>[[isʰɯɭbi]] 毛毛雨 (自然)</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ɭbu]] 分期付款 (Shopping)</t>
+          <t>[[ha̠ɭbu]] 分期付款 (购物)</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ɭbu]] 分期付款 (Shopping)</t>
+          <t>[[ha̠ɭbu]] 分期付款 (购物)</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)ʎt͡ɕʰum]] 假面舞 (Culture)</t>
+          <t>[[ˈtʰa̠(ː)ʎt͡ɕʰum]] 假面舞 (文化)</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)ʎt͡ɕʰum]] 假面舞 (Culture)</t>
+          <t>[[ˈtʰa̠(ː)ʎt͡ɕʰum]] 假面舞 (文化)</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (Culture)</t>
+          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (文化)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (Culture)</t>
+          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (文化)</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1567,13 +1567,13 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>蘆葦田 (Nature)</t>
+          <t>芦苇田 (自然)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr"/>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>蘆葦田 (Nature)</t>
+          <t>芦苇田 (自然)</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1595,13 +1595,13 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>韓紙 (Culture)</t>
+          <t>韩纸 (文化)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr"/>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>韓紙 (Culture)</t>
+          <t>韩纸 (文化)</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹nmua̠m]] 熔岩石 (Nature)</t>
+          <t>[[çʌ̹nmua̠m]] 熔岩石 (自然)</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹nmua̠m]] 熔岩石 (Nature)</t>
+          <t>[[çʌ̹nmua̠m]] 熔岩石 (自然)</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠nsʰe̞]] 關稅 (購物)</t>
+          <t>[[kwa̠nsʰe̞]] 关税 (购物)</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠nsʰe̞]] 關稅 (購物)</t>
+          <t>[[kwa̠nsʰe̞]] 关税 (购物)</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠da̠kʰo̞k͈iɾi]] 海象 (動物)</t>
+          <t>[[pa̠da̠kʰo̞k͈iɾi]] 海象 (动物)</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠da̠kʰo̞k͈iɾi]] 海象 (動物)</t>
+          <t>[[pa̠da̠kʰo̞k͈iɾi]] 海象 (动物)</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞p͈uɭs͈o̞]] 犀牛 (動物)</t>
+          <t>[[kʰo̞p͈uɭs͈o̞]] 犀牛 (动物)</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞p͈uɭs͈o̞]] 犀牛 (動物)</t>
+          <t>[[kʰo̞p͈uɭs͈o̞]] 犀牛 (动物)</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ma̠]] 河馬 (動物)</t>
+          <t>[[ha̠ma̠]] 河马 (动物)</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ma̠]] 河馬 (動物)</t>
+          <t>[[ha̠ma̠]] 河马 (动物)</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛɡjuʌ̹]] 美洲豹 (動物)</t>
+          <t>[[t͡ɕɛɡjuʌ̹]] 美洲豹 (动物)</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛɡjuʌ̹]] 美洲豹 (動物)</t>
+          <t>[[t͡ɕɛɡjuʌ̹]] 美洲豹 (动物)</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ie̞na̠]] 鬣狗 (動物)</t>
+          <t>[[ha̠ie̞na̠]] 鬣狗 (动物)</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ie̞na̠]] 鬣狗 (動物)</t>
+          <t>[[ha̠ie̞na̠]] 鬣狗 (动物)</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>[[miʌ̹kʰɛt̚]] 狐獴 (動物)</t>
+          <t>[[miʌ̹kʰɛt̚]] 狐獴 (动物)</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>[[miʌ̹kʰɛt̚]] 狐獴 (動物)</t>
+          <t>[[miʌ̹kʰɛt̚]] 狐獴 (动物)</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾɯma̠diɭɭo̞]] 犰狳 (動物)</t>
+          <t>[[a̠ɾɯma̠diɭɭo̞]] 犰狳 (动物)</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾɯma̠diɭɭo̞]] 犰狳 (動物)</t>
+          <t>[[a̠ɾɯma̠diɭɭo̞]] 犰狳 (动物)</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>[[ˈo̞(ː)ɾinʌ̹ɡuɾi]] 鴨嘴獸 (動物)</t>
+          <t>[[ˈo̞(ː)ɾinʌ̹ɡuɾi]] 鸭嘴兽 (动物)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>[[ˈo̞(ː)ɾinʌ̹ɡuɾi]] 鴨嘴獸 (動物)</t>
+          <t>[[ˈo̞(ː)ɾinʌ̹ɡuɾi]] 鸭嘴兽 (动物)</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -1975,13 +1975,13 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>飛鼠 (動物)</t>
+          <t>飞鼠 (动物)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>飛鼠 (動物)</t>
+          <t>飞鼠 (动物)</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)ŋsʰɛ]] 鸛 (動物)</t>
+          <t>[[ˈɸwa̠(ː)ŋsʰɛ]] 鹳 (动物)</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)ŋsʰɛ]] 鸛 (動物)</t>
+          <t>[[ˈɸwa̠(ː)ŋsʰɛ]] 鹳 (动物)</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋɡo̞ŋ]] 瞳孔 (身體部位)</t>
+          <t>[[ˈto̞(ː)ŋɡo̞ŋ]] 瞳孔 (身体部位)</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋɡo̞ŋ]] 瞳孔 (身體部位)</t>
+          <t>[[ˈto̞(ː)ŋɡo̞ŋ]] 瞳孔 (身体部位)</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋmɛk̚]] 靜脈 (身體部位)</t>
+          <t>[[t͡ɕʌ̹ŋmɛk̚]] 静脉 (身体部位)</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋmɛk̚]] 靜脈 (身體部位)</t>
+          <t>[[t͡ɕʌ̹ŋmɛk̚]] 静脉 (身体部位)</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰinɡjʌ̹ŋ]] 神經 (身體部位)</t>
+          <t>[[ɕʰinɡjʌ̹ŋ]] 神经 (身体部位)</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰinɡjʌ̹ŋ]] 神經 (身體部位)</t>
+          <t>[[ɕʰinɡjʌ̹ŋ]] 神经 (身体部位)</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>[[çimt͡ɕ͈uɭ]] 肌腱 (身體部位)</t>
+          <t>[[çimt͡ɕ͈uɭ]] 肌腱 (身体部位)</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>[[çimt͡ɕ͈uɭ]] 肌腱 (身體部位)</t>
+          <t>[[çimt͡ɕ͈uɭ]] 肌腱 (身体部位)</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɭɡjʌ̹k̚]] Skeleton (身體部位)</t>
+          <t>[[ko̞ɭɡjʌ̹k̚]] 骨架 (身体部位)</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɭɡjʌ̹k̚]] Skeleton (身體部位)</t>
+          <t>[[ko̞ɭɡjʌ̹k̚]] 骨架 (身体部位)</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ma̠k̚]] Eardrum (身體部位)</t>
+          <t>[[ko̞ma̠k̚]] 耳膜 (身体部位)</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ma̠k̚]] Eardrum (身體部位)</t>
+          <t>[[ko̞ma̠k̚]] 耳膜 (身体部位)</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕi(ː)nβo̞ŋsʰɛk̚]] 深紅色 (顏色與形狀)</t>
+          <t>[[ˈt͡ɕi(ː)nβo̞ŋsʰɛk̚]] 深红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕi(ː)nβo̞ŋsʰɛk̚]] 深紅色 (顏色與形狀)</t>
+          <t>[[ˈt͡ɕi(ː)nβo̞ŋsʰɛk̚]] 深红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -2259,13 +2259,13 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>緋紅色 (顏色與形狀)</t>
+          <t>绯红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr"/>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>緋紅色 (顏色與形狀)</t>
+          <t>绯红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2287,13 +2287,13 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>翠綠色 (顏色與形狀)</t>
+          <t>翠绿色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr"/>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>翠綠色 (顏色與形狀)</t>
+          <t>翠绿色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
@@ -2315,13 +2315,13 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>鈷藍色 (顏色與形狀)</t>
+          <t>钴蓝色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr"/>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>鈷藍色 (顏色與形狀)</t>
+          <t>钴蓝色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
@@ -2343,13 +2343,13 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>琥珀色 (顏色與形狀)</t>
+          <t>琥珀色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr"/>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>琥珀色 (顏色與形狀)</t>
+          <t>琥珀色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2371,13 +2371,13 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>炭灰色 (顏色與形狀)</t>
+          <t>炭灰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr"/>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>炭灰色 (顏色與形狀)</t>
+          <t>炭灰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2399,13 +2399,13 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>垂直線 (顏色與形狀)</t>
+          <t>垂直线 (颜色与形状)</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr"/>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>垂直線 (顏色與形狀)</t>
+          <t>垂直线 (颜色与形状)</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -2427,13 +2427,13 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>Bullying (School Life)</t>
+          <t>欺凌 (校园生活)</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr"/>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>Bullying (School Life)</t>
+          <t>欺凌 (校园生活)</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>[[tʰo̞ne̞ido̞]] 龍捲風 (天氣)</t>
+          <t>[[tʰo̞ne̞ido̞]] 龙卷风 (天气)</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>[[tʰo̞ne̞ido̞]] 龍捲風 (天氣)</t>
+          <t>[[tʰo̞ne̞ido̞]] 龙卷风 (天气)</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹ɾikʰe̞in]] 颶風 (天氣)</t>
+          <t>[[hʌ̹ɾikʰe̞in]] 飓风 (天气)</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹ɾikʰe̞in]] 颶風 (天氣)</t>
+          <t>[[hʌ̹ɾikʰe̞in]] 飓风 (天气)</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞nsʰun]] 季風 (天氣)</t>
+          <t>[[mo̞nsʰun]] 季风 (天气)</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞nsʰun]] 季風 (天氣)</t>
+          <t>[[mo̞nsʰun]] 季风 (天气)</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2551,13 +2551,13 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Barometric Pressure (天氣)</t>
+          <t>气压 (天气)</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>Barometric Pressure (天氣)</t>
+          <t>气压 (天气)</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
@@ -2579,13 +2579,13 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>Visibility (天氣)</t>
+          <t>可见性 (天气)</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>Visibility (天氣)</t>
+          <t>可见性 (天气)</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
@@ -2607,13 +2607,13 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Dew Point (天氣)</t>
+          <t>露点 (天气)</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>Dew Point (天氣)</t>
+          <t>露点 (天气)</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋsʰa̠ŋ]] Frostbite (天氣)</t>
+          <t>[[ˈto̞(ː)ŋsʰa̠ŋ]] 冻伤 (天气)</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋsʰa̠ŋ]] Frostbite (天氣)</t>
+          <t>[[ˈto̞(ː)ŋsʰa̠ŋ]] 冻伤 (天气)</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2667,13 +2667,13 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>降雪量 (天氣)</t>
+          <t>降雪量 (天气)</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr"/>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>降雪量 (天氣)</t>
+          <t>降雪量 (天气)</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
@@ -2695,13 +2695,13 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>口袋巾 (服飾)</t>
+          <t>口袋巾 (服饰)</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>口袋巾 (服飾)</t>
+          <t>口袋巾 (服饰)</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
@@ -2723,13 +2723,13 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>袖扣 (服飾)</t>
+          <t>袖扣 (服饰)</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>袖扣 (服飾)</t>
+          <t>袖扣 (服饰)</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2751,13 +2751,13 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>壓力服 (服飾)</t>
+          <t>压力服 (服饰)</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>壓力服 (服飾)</t>
+          <t>压力服 (服饰)</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠k̚t͡ɕ͈a̠ŋ]] 狗血劇 (韓劇用語)</t>
+          <t>[[ma̠k̚t͡ɕ͈a̠ŋ]] 狗血剧 (韩剧用语)</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠k̚t͡ɕ͈a̠ŋ]] 狗血劇 (韓劇用語)</t>
+          <t>[[ma̠k̚t͡ɕ͈a̠ŋ]] 狗血剧 (韩剧用语)</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] Weasel (Animals)</t>
+          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] 鼬属 (动物)</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] Weasel (Animals)</t>
+          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] 鼬属 (动物)</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰibʌ̹k̚]] Billion (Numbers and Time)</t>
+          <t>[[ɕʰibʌ̹k̚]] 十亿 (数字与时间)</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰibʌ̹k̚]] Billion (Numbers and Time)</t>
+          <t>[[ɕʰibʌ̹k̚]] 十亿 (数字与时间)</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -2875,13 +2875,13 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Fiscal Year (Numbers and Time)</t>
+          <t>年度 (数字与时间)</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>Fiscal Year (Numbers and Time)</t>
+          <t>年度 (数字与时间)</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
@@ -2903,13 +2903,13 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Spring Thaw (Weather)</t>
+          <t>春季解冻 (天气)</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>Spring Thaw (Weather)</t>
+          <t>春季解冻 (天气)</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰut͡ɕʰʌ̹nsʰʌ̹]] 推薦信 (校園生活)</t>
+          <t>[[t͡ɕʰut͡ɕʰʌ̹nsʰʌ̹]] 推荐信 (校园生活)</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰut͡ɕʰʌ̹nsʰʌ̹]] 推薦信 (校園生活)</t>
+          <t>[[t͡ɕʰut͡ɕʰʌ̹nsʰʌ̹]] 推荐信 (校园生活)</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -2963,13 +2963,13 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>股票期權 (商業)</t>
+          <t>股票期权 (商业)</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr"/>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>股票期權 (商業)</t>
+          <t>股票期权 (商业)</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕibun]] 股權 (商業)</t>
+          <t>[[t͡ɕibun]] 股权 (商业)</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕibun]] 股權 (商業)</t>
+          <t>[[t͡ɕibun]] 股权 (商业)</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -3023,13 +3023,13 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>加值稅 (商業)</t>
+          <t>加值税 (商业)</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr"/>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>加值稅 (商業)</t>
+          <t>加值税 (商业)</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>[[ˈka̠(ː)msʰa̠]] 審計 (商業)</t>
+          <t>[[ˈka̠(ː)msʰa̠]] 审计 (商业)</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>[[ˈka̠(ː)msʰa̠]] 審計 (商業)</t>
+          <t>[[ˈka̠(ː)msʰa̠]] 审计 (商业)</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -3083,13 +3083,13 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>資產負債表 (商業)</t>
+          <t>资产负债表 (商业)</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr"/>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>資產負債表 (商業)</t>
+          <t>资产负债表 (商业)</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -3111,13 +3111,13 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>創投 (商業)</t>
+          <t>创投 (商业)</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr"/>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>創投 (商業)</t>
+          <t>创投 (商业)</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -3139,13 +3139,13 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>首次公開發行 (商業)</t>
+          <t>首次公开发行 (商业)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr"/>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>首次公開發行 (商業)</t>
+          <t>首次公开发行 (商业)</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠p̚p͈jʌ̹ŋ]] 合併 (商業)</t>
+          <t>[[ha̠p̚p͈jʌ̹ŋ]] 合并 (商业)</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠p̚p͈jʌ̹ŋ]] 合併 (商業)</t>
+          <t>[[ha̠p̚p͈jʌ̹ŋ]] 合并 (商业)</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>[[insʰu]] 收購 (商業)</t>
+          <t>[[insʰu]] 收购 (商业)</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>[[insʰu]] 收購 (商業)</t>
+          <t>[[insʰu]] 收购 (商业)</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3231,13 +3231,13 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>子公司 (商業)</t>
+          <t>子公司 (商业)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr"/>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>子公司 (商業)</t>
+          <t>子公司 (商业)</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕud͡ʑu]] 股東 (商業)</t>
+          <t>[[t͡ɕud͡ʑu]] 股东 (商业)</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕud͡ʑu]] 股東 (商業)</t>
+          <t>[[t͡ɕud͡ʑu]] 股东 (商业)</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3291,13 +3291,13 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>財務長 (商業)</t>
+          <t>财务长 (商业)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr"/>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>財務長 (商業)</t>
+          <t>财务长 (商业)</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
@@ -3319,13 +3319,13 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>營運長 (商業)</t>
+          <t>营运长 (商业)</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr"/>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>營運長 (商業)</t>
+          <t>营运长 (商业)</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
@@ -3347,13 +3347,13 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>Ferment (Cooking)</t>
+          <t>发酵 (烹饪)</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr"/>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>Ferment (Cooking)</t>
+          <t>发酵 (烹饪)</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
@@ -3375,13 +3375,13 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Cure (Cooking)</t>
+          <t>治愈 (烹饪)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr"/>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Cure (Cooking)</t>
+          <t>治愈 (烹饪)</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3403,13 +3403,13 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Smoke (Cooking)</t>
+          <t>烟 (烹饪)</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr"/>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>Smoke (Cooking)</t>
+          <t>烟 (烹饪)</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -3431,13 +3431,13 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Profit Margin (商業)</t>
+          <t>利润率 (商业)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr"/>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>Profit Margin (商業)</t>
+          <t>利润率 (商业)</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
@@ -3459,13 +3459,13 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Supply Chain (商業)</t>
+          <t>Supply Chain (商业)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr"/>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Supply Chain (商業)</t>
+          <t>Supply Chain (商业)</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>[[kimd͡ʑa̠ŋ]] Kimchi Making (烹飪)</t>
+          <t>[[kimd͡ʑa̠ŋ]] 泡菜制作 (烹饪)</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>[[kimd͡ʑa̠ŋ]] Kimchi Making (烹飪)</t>
+          <t>[[kimd͡ʑa̠ŋ]] 泡菜制作 (烹饪)</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -3519,13 +3519,13 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Tangjinjam (俚語)</t>
+          <t>Tangjinjam (俚语)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr"/>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>Tangjinjam (俚語)</t>
+          <t>Tangjinjam (俚语)</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -3547,13 +3547,13 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>No Chill / Intense (俚語)</t>
+          <t>没有寒意/强烈 (俚语)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr"/>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>No Chill / Intense (俚語)</t>
+          <t>没有寒意/强烈 (俚语)</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3575,13 +3575,13 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Really (俚語)</t>
+          <t>真真 (俚语)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr"/>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>Really (俚語)</t>
+          <t>真真 (俚语)</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -3603,13 +3603,13 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>瞬間赤貧 (俚語)</t>
+          <t>瞬间赤贫 (俚语)</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr"/>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>瞬間赤貧 (俚語)</t>
+          <t>瞬间赤贫 (俚语)</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ʎd͡ʑo̞sʰʌ̹n]] 逃離韓國 (俚語)</t>
+          <t>[[tʰa̠ʎd͡ʑo̞sʰʌ̹n]] 逃离韩国 (俚语)</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ʎd͡ʑo̞sʰʌ̹n]] 逃離韓國 (俚語)</t>
+          <t>[[tʰa̠ʎd͡ʑo̞sʰʌ̹n]] 逃离韩国 (俚语)</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>[[he̞ʎd͡ʑo̞sʰʌ̹n]] 地獄朝鮮 (俚語)</t>
+          <t>[[he̞ʎd͡ʑo̞sʰʌ̹n]] 地狱朝鲜 (俚语)</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>[[he̞ʎd͡ʑo̞sʰʌ̹n]] 地獄朝鮮 (俚語)</t>
+          <t>[[he̞ʎd͡ʑo̞sʰʌ̹n]] 地狱朝鲜 (俚语)</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3695,13 +3695,13 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>泥土湯匙 (俚語)</t>
+          <t>泥土汤匙 (俚语)</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr"/>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>泥土湯匙 (俚語)</t>
+          <t>泥土汤匙 (俚语)</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>[[kɯmsʰud͡ʑʌ̹]] 金湯匙 (俚語)</t>
+          <t>[[kɯmsʰud͡ʑʌ̹]] 金汤匙 (俚语)</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>[[kɯmsʰud͡ʑʌ̹]] 金湯匙 (俚語)</t>
+          <t>[[kɯmsʰud͡ʑʌ̹]] 金汤匙 (俚语)</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -3755,13 +3755,13 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>努力中毒者 (俚語)</t>
+          <t>努力中毒者 (俚语)</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr"/>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>努力中毒者 (俚語)</t>
+          <t>努力中毒者 (俚语)</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -3783,13 +3783,13 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>熱情薪資 (俚語)</t>
+          <t>热情薪资 (俚语)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr"/>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>熱情薪資 (俚語)</t>
+          <t>热情薪资 (俚语)</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -3811,13 +3811,13 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>鐵人三項 (運動)</t>
+          <t>铁人三项 (运动)</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr"/>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>鐵人三項 (運動)</t>
+          <t>铁人三项 (运动)</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ŋdɛno̞pʰit͈ɥiɡi]] 撐竿跳高 (運動)</t>
+          <t>[[t͡ɕa̠ŋdɛno̞pʰit͈ɥiɡi]] 撑竿跳高 (运动)</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ŋdɛno̞pʰit͈ɥiɡi]] 撐竿跳高 (運動)</t>
+          <t>[[t͡ɕa̠ŋdɛno̞pʰit͈ɥiɡi]] 撑竿跳高 (运动)</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>[[hɛmʌ̹dʌ̹ɲd͡ʑiɡi]] 鏈球 (運動)</t>
+          <t>[[hɛmʌ̹dʌ̹ɲd͡ʑiɡi]] 链球 (运动)</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>[[hɛmʌ̹dʌ̹ɲd͡ʑiɡi]] 鏈球 (運動)</t>
+          <t>[[hɛmʌ̹dʌ̹ɲd͡ʑiɡi]] 链球 (运动)</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -3903,13 +3903,13 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>CrossFit (運動)</t>
+          <t>Crossfit (运动)</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr"/>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>CrossFit (運動)</t>
+          <t>Crossfit (运动)</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -3931,13 +3931,13 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>區塊鏈 (科技)</t>
+          <t>区块链 (科技)</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr"/>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>區塊鏈 (科技)</t>
+          <t>区块链 (科技)</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>[[ˈa̠(ː)mβo̞βwa̠pʰje̞]] 加密貨幣 (科技)</t>
+          <t>[[ˈa̠(ː)mβo̞βwa̠pʰje̞]] 加密货币 (科技)</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>[[ˈa̠(ː)mβo̞βwa̠pʰje̞]] 加密貨幣 (科技)</t>
+          <t>[[ˈa̠(ː)mβo̞βwa̠pʰje̞]] 加密货币 (科技)</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4023,13 +4023,13 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>虛擬實境 (科技)</t>
+          <t>虚拟实境 (科技)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr"/>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>虛擬實境 (科技)</t>
+          <t>虚拟实境 (科技)</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
@@ -4051,13 +4051,13 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>擴增實境 (科技)</t>
+          <t>扩增实境 (科技)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr"/>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>擴增實境 (科技)</t>
+          <t>扩增实境 (科技)</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
@@ -4107,13 +4107,13 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>量子計算 (科技)</t>
+          <t>量子计算 (科技)</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>量子計算 (科技)</t>
+          <t>量子计算 (科技)</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰwe̞(ː)d͡ʑik̚k͈ɯm]] 資遣費 (商業)</t>
+          <t>[[ˈtʰwe̞(ː)d͡ʑik̚k͈ɯm]] 资遣费 (商业)</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰwe̞(ː)d͡ʑik̚k͈ɯm]] 資遣費 (商業)</t>
+          <t>[[ˈtʰwe̞(ː)d͡ʑik̚k͈ɯm]] 资遣费 (商业)</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimsʰuɭ]] 針灸 (健康與醫療)</t>
+          <t>[[t͡ɕʰimsʰuɭ]] 针灸 (健康与医疗)</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimsʰuɭ]] 針灸 (健康與醫療)</t>
+          <t>[[t͡ɕʰimsʰuɭ]] 针灸 (健康与医疗)</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -4227,13 +4227,13 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>韓醫學 (健康與醫療)</t>
+          <t>韩医学 (健康与医疗)</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr"/>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>韓醫學 (健康與醫療)</t>
+          <t>韩医学 (健康与医疗)</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -4255,13 +4255,13 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>MRI (健康與醫療)</t>
+          <t>MRI (健康与医疗)</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr"/>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>MRI (健康與醫療)</t>
+          <t>MRI (健康与医疗)</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɯ(ː)nɕʰi]] Myopia (Health &amp; Medical)</t>
+          <t>[[ˈkɯ(ː)nɕʰi]] 近视 (健康医疗)</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɯ(ː)nɕʰi]] Myopia (Health &amp; Medical)</t>
+          <t>[[ˈkɯ(ː)nɕʰi]] 近视 (健康医疗)</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠nbuink͈wa̠]] Obstetrics / OB-GYN (Health &amp; Medical)</t>
+          <t>[[sʰa̠nbuink͈wa̠]] 产科/妇产科 (健康医疗)</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠nbuink͈wa̠]] Obstetrics / OB-GYN (Health &amp; Medical)</t>
+          <t>[[sʰa̠nbuink͈wa̠]] 产科/妇产科 (健康医疗)</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4347,13 +4347,13 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Cardiology (Health &amp; Medical)</t>
+          <t>心脏病科 (健康医疗)</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr"/>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>Cardiology (Health &amp; Medical)</t>
+          <t>心脏病科 (健康医疗)</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -4375,13 +4375,13 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Orthopedics (Health &amp; Medical)</t>
+          <t>骨科 (健康医疗)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr"/>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>Orthopedics (Health &amp; Medical)</t>
+          <t>骨科 (健康医疗)</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -4403,13 +4403,13 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Neurology (Health &amp; Medical)</t>
+          <t>神经内科 (健康医疗)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr"/>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>Neurology (Health &amp; Medical)</t>
+          <t>神经内科 (健康医疗)</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4431,13 +4431,13 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>BMI (Health &amp; Medical)</t>
+          <t>Prowess BMI计算器 (健康医疗)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr"/>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>BMI (Health &amp; Medical)</t>
+          <t>Prowess BMI计算器 (健康医疗)</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>[[a̠(ː)m]] Cancer (Health &amp; Medical)</t>
+          <t>[[a̠(ː)m]] 癌症 (健康医疗)</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>[[a̠(ː)m]] Cancer (Health &amp; Medical)</t>
+          <t>[[a̠(ː)m]] 癌症 (健康医疗)</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -4491,13 +4491,13 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Copay (Health &amp; Medical)</t>
+          <t>定额手续费 (健康医疗)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr"/>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>Copay (Health &amp; Medical)</t>
+          <t>定额手续费 (健康医疗)</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>[[nwe̞d͡ʑo̞ʎt͡ɕ͈uŋ]] 中風 (健康與醫療)</t>
+          <t>[[nwe̞d͡ʑo̞ʎt͡ɕ͈uŋ]] 中风 (健康与医疗)</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>[[nwe̞d͡ʑo̞ʎt͡ɕ͈uŋ]] 中風 (健康與醫療)</t>
+          <t>[[nwe̞d͡ʑo̞ʎt͡ɕ͈uŋ]] 中风 (健康与医疗)</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimd͡ʑa̠ŋma̠bi]] 心臟病發作 (健康與醫療)</t>
+          <t>[[ɕʰimd͡ʑa̠ŋma̠bi]] 心脏病发作 (健康与医疗)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimd͡ʑa̠ŋma̠bi]] 心臟病發作 (健康與醫療)</t>
+          <t>[[ɕʰimd͡ʑa̠ŋma̠bi]] 心脏病发作 (健康与医疗)</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4583,13 +4583,13 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>腎臟疾病 (健康與醫療)</t>
+          <t>肾脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr"/>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>腎臟疾病 (健康與醫療)</t>
+          <t>肾脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -4611,13 +4611,13 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>肝臟疾病 (健康與醫療)</t>
+          <t>肝脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr"/>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>肝臟疾病 (健康與醫療)</t>
+          <t>肝脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
@@ -4639,13 +4639,13 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>胃鏡檢查 (健康與醫療)</t>
+          <t>胃镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr"/>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>胃鏡檢查 (健康與醫療)</t>
+          <t>胃镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -4667,13 +4667,13 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>結腸鏡檢查 (健康與醫療)</t>
+          <t>结肠镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr"/>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>結腸鏡檢查 (健康與醫療)</t>
+          <t>结肠镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>[[joja̠ŋwʌ̹n]] Sanatorium / Convalescent Home (Health &amp; Medical)</t>
+          <t>[[joja̠ŋwʌ̹n]] 疗养院/疗养院 (健康医疗)</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>[[joja̠ŋwʌ̹n]] Sanatorium / Convalescent Home (Health &amp; Medical)</t>
+          <t>[[joja̠ŋwʌ̹n]] 疗养院/疗养院 (健康医疗)</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -4727,13 +4727,13 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Hospice (Health &amp; Medical)</t>
+          <t>临终关怀 (健康医疗)</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr"/>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>Hospice (Health &amp; Medical)</t>
+          <t>临终关怀 (健康医疗)</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕe̞(ː)sʰa̠]] Jesa (Ancestral Rites) (Holidays &amp; Festivals)</t>
+          <t>[[ˈt͡ɕe̞(ː)sʰa̠]] 祭礼；祭祀 (节日庆典)</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕe̞(ː)sʰa̠]] Jesa (Ancestral Rites) (Holidays &amp; Festivals)</t>
+          <t>[[ˈt͡ɕe̞(ː)sʰa̠]] 祭礼；祭祀 (节日庆典)</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰa̠ɾje̞]] Charye (Holiday Ancestral Rites) (Holidays &amp; Festivals)</t>
+          <t>[[t͡ɕʰa̠ɾje̞]] 茶礼（节日祭祖仪式） (节日庆典)</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰa̠ɾje̞]] Charye (Holiday Ancestral Rites) (Holidays &amp; Festivals)</t>
+          <t>[[t͡ɕʰa̠ɾje̞]] 茶礼（节日祭祖仪式） (节日庆典)</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -4819,13 +4819,13 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Daeboreum (First Full Moon Festival) (Holidays &amp; Festivals)</t>
+          <t>正月大满月（元宵） (节日庆典)</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr"/>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>Daeboreum (First Full Moon Festival) (Holidays &amp; Festivals)</t>
+          <t>正月大满月（元宵） (节日庆典)</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)ɾʌ̹m]] Buram (Nut Cracking Ritual) (Holidays &amp; Festivals)</t>
+          <t>[[ˈpu(ː)ɾʌ̹m]] 布拉姆 (节日庆典)</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)ɾʌ̹m]] Buram (Nut Cracking Ritual) (Holidays &amp; Festivals)</t>
+          <t>[[ˈpu(ː)ɾʌ̹m]] 布拉姆 (节日庆典)</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>[[o̞ɡo̞k̚p͈a̠p̚]] Five Grain Rice (Holidays &amp; Festivals)</t>
+          <t>[[o̞ɡo̞k̚p͈a̠p̚]] 五谷大米 (节日庆典)</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>[[o̞ɡo̞k̚p͈a̠p̚]] Five Grain Rice (Holidays &amp; Festivals)</t>
+          <t>[[o̞ɡo̞k̚p͈a̠p̚]] 五谷大米 (节日庆典)</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -4911,13 +4911,13 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>National Foundation Day (Holidays &amp; Festivals)</t>
+          <t>建国纪念日 (节日庆典)</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr"/>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>National Foundation Day (Holidays &amp; Festivals)</t>
+          <t>建国纪念日 (节日庆典)</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -4939,13 +4939,13 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Lotus Lantern Festival (Holidays &amp; Festivals)</t>
+          <t>莲花灯节 (节日庆典)</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr"/>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>Lotus Lantern Festival (Holidays &amp; Festivals)</t>
+          <t>莲花灯节 (节日庆典)</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
@@ -4967,13 +4967,13 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Dano Festival (Holidays &amp; Festivals)</t>
+          <t>达诺节 (节日庆典)</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr"/>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>Dano Festival (Holidays &amp; Festivals)</t>
+          <t>达诺节 (节日庆典)</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>[[to̞ʎd͡ʑa̠bi]] Doljabi (Birthday Fortune Ritual) (Holidays &amp; Festivals)</t>
+          <t>[[to̞ʎd͡ʑa̠bi]] 抓周（婴儿周岁礼） (节日庆典)</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>[[to̞ʎd͡ʑa̠bi]] Doljabi (Birthday Fortune Ritual) (Holidays &amp; Festivals)</t>
+          <t>[[to̞ʎd͡ʑa̠bi]] 抓周（婴儿周岁礼） (节日庆典)</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)nɡa̠p̚]] Hwangap (60th Birthday) (Holidays &amp; Festivals)</t>
+          <t>[[ˈɸwa̠(ː)nɡa̠p̚]] 花甲（六十岁寿辰） (节日庆典)</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)nɡa̠p̚]] Hwangap (60th Birthday) (Holidays &amp; Festivals)</t>
+          <t>[[ˈɸwa̠(ː)nɡa̠p̚]] 花甲（六十岁寿辰） (节日庆典)</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
@@ -5059,13 +5059,13 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>Gijedo (Memorial Flag Day) (Holidays &amp; Festivals)</t>
+          <t>希赫多 (节日庆典)</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr"/>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>Gijedo (Memorial Flag Day) (Holidays &amp; Festivals)</t>
+          <t>希赫多 (节日庆典)</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>[[ɕ͈iɾɯm]] Ssireum (Korean Wrestling) (Holidays &amp; Festivals)</t>
+          <t>[[ɕ͈iɾɯm]] 韩式摔跤 (节日庆典)</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>[[ɕ͈iɾɯm]] Ssireum (Korean Wrestling) (Holidays &amp; Festivals)</t>
+          <t>[[ɕ͈iɾɯm]] 韩式摔跤 (节日庆典)</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>[[ˈnɘ(ː)ɭt͈ɥiɡi]] Neolttuigi (Seesaw Jumping) (Holidays &amp; Festivals)</t>
+          <t>[[ˈnɘ(ː)ɭt͈ɥiɡi]] 跳板（韩国传统游戏） (节日庆典)</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>[[ˈnɘ(ː)ɭt͈ɥiɡi]] Neolttuigi (Seesaw Jumping) (Holidays &amp; Festivals)</t>
+          <t>[[ˈnɘ(ː)ɭt͈ɥiɡi]] 跳板（韩国传统游戏） (节日庆典)</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
@@ -5151,13 +5151,13 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Jesa Table (Holidays &amp; Festivals)</t>
+          <t>Jesa桌子 (节日庆典)</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>Jesa Table (Holidays &amp; Festivals)</t>
+          <t>Jesa桌子 (节日庆典)</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
@@ -5179,13 +5179,13 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Pungmul (Farmer's Music) (Holidays &amp; Festivals)</t>
+          <t>农乐（韩国传统打击乐） (节日庆典)</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr"/>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>Pungmul (Farmer's Music) (Holidays &amp; Festivals)</t>
+          <t>农乐（韩国传统打击乐） (节日庆典)</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
@@ -5207,13 +5207,13 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Condolence Money (Holidays &amp; Festivals)</t>
+          <t>哀悼金 (节日庆典)</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>Condolence Money (Holidays &amp; Festivals)</t>
+          <t>哀悼金 (节日庆典)</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (傳統婚禮儀式) (節日與慶典)</t>
+          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (传统婚礼仪式) (节日与庆典)</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (傳統婚禮儀式) (節日與慶典)</t>
+          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (传统婚礼仪式) (节日与庆典)</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕa̠(ː)ŋɲe̞ɕʰik̚]] 葬禮 (節日與慶典)</t>
+          <t>[[ˈt͡ɕa̠(ː)ŋɲe̞ɕʰik̚]] 葬礼 (节日与庆典)</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕa̠(ː)ŋɲe̞ɕʰik̚]] 葬禮 (節日與慶典)</t>
+          <t>[[ˈt͡ɕa̠(ː)ŋɲe̞ɕʰik̚]] 葬礼 (节日与庆典)</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>[[judu]] Yudu（夏日沐浴節） (節日與慶典)</t>
+          <t>[[judu]] Yudu（夏日沐浴节） (节日与庆典)</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>[[judu]] Yudu（夏日沐浴節） (節日與慶典)</t>
+          <t>[[judu]] Yudu（夏日沐浴节） (节日与庆典)</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (節日與慶典)</t>
+          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (节日与庆典)</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (節日與慶典)</t>
+          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (节日与庆典)</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠nɡa̠ɥi]] 豐收之月 (節日與慶典)</t>
+          <t>[[ha̠nɡa̠ɥi]] 丰收之月 (节日与庆典)</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠nɡa̠ɥi]] 豐收之月 (節日與慶典)</t>
+          <t>[[ha̠nɡa̠ɥi]] 丰收之月 (节日与庆典)</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞d͡ʑʌ̹nɡjot͡ɕʰa̠ɾo̞]] Roundabout (Transportation)</t>
+          <t>[[ɸwe̞d͡ʑʌ̹nɡjot͡ɕʰa̠ɾo̞]] 环形交叉路口 (交通)</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞d͡ʑʌ̹nɡjot͡ɕʰa̠ɾo̞]] Roundabout (Transportation)</t>
+          <t>[[ɸwe̞d͡ʑʌ̹nɡjot͡ɕʰa̠ɾo̞]] 环形交叉路口 (交通)</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹nsʰʌ̹k̚]] Curb (Transportation)</t>
+          <t>[[jʌ̹nsʰʌ̹k̚]] 路沿 (交通)</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹nsʰʌ̹k̚]] Curb (Transportation)</t>
+          <t>[[jʌ̹nsʰʌ̹k̚]] 路沿 (交通)</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5459,13 +5459,13 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>獨立運動家 (節慶與活動)</t>
+          <t>独立运动家 (节庆与活动)</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr"/>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>獨立運動家 (節慶與活動)</t>
+          <t>独立运动家 (节庆与活动)</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -5487,13 +5487,13 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>神主牌 (Holidays &amp; Festivals)</t>
+          <t>神主牌 (节日庆典)</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr"/>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>神主牌 (Holidays &amp; Festivals)</t>
+          <t>神主牌 (节日庆典)</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
@@ -5515,13 +5515,13 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸 (Beauty &amp; Skincare)</t>
+          <t>玻尿酸 (美妆护肤)</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr"/>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸 (Beauty &amp; Skincare)</t>
+          <t>玻尿酸 (美妆护肤)</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>[[ɾe̞tʰino̞ɭ]] 視黃醇 (Beauty &amp; Skincare)</t>
+          <t>[[ɾe̞tʰino̞ɭ]] 视黄醇 (美妆护肤)</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>[[ɾe̞tʰino̞ɭ]] 視黃醇 (Beauty &amp; Skincare)</t>
+          <t>[[ɾe̞tʰino̞ɭ]] 视黄醇 (美妆护肤)</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
@@ -5575,13 +5575,13 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>煙酰胺 (Beauty &amp; Skincare)</t>
+          <t>烟酰胺 (美妆护肤)</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr"/>
       <c r="D172" s="1" t="inlineStr">
         <is>
-          <t>煙酰胺 (Beauty &amp; Skincare)</t>
+          <t>烟酰胺 (美妆护肤)</t>
         </is>
       </c>
       <c r="E172" s="1" t="inlineStr">
@@ -5603,13 +5603,13 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>蜂膠 (Beauty &amp; Skincare)</t>
+          <t>蜂胶 (美妆护肤)</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr"/>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t>蜂膠 (Beauty &amp; Skincare)</t>
+          <t>蜂胶 (美妆护肤)</t>
         </is>
       </c>
       <c r="E173" s="1" t="inlineStr">
@@ -5631,13 +5631,13 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>安瓶 (美容與護膚)</t>
+          <t>安瓶 (美容与护肤)</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr"/>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>安瓶 (美容與護膚)</t>
+          <t>安瓶 (美容与护肤)</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
@@ -5659,13 +5659,13 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺 (美容與護膚)</t>
+          <t>神经醯胺 (美容与护肤)</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr"/>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>神經醯胺 (美容與護膚)</t>
+          <t>神经醯胺 (美容与护肤)</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>[[pʰe̞p̚tʰa̠idɯ]] 胜肽 (美容與護膚)</t>
+          <t>[[pʰe̞p̚tʰa̠idɯ]] 胜肽 (美容与护肤)</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>[[pʰe̞p̚tʰa̠idɯ]] 胜肽 (美容與護膚)</t>
+          <t>[[pʰe̞p̚tʰa̠idɯ]] 胜肽 (美容与护肤)</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
@@ -5719,13 +5719,13 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>玫瑰果 (美容與護膚)</t>
+          <t>玫瑰果 (美容与护肤)</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr"/>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>玫瑰果 (美容與護膚)</t>
+          <t>玫瑰果 (美容与护肤)</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
@@ -5747,13 +5747,13 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>膚色底調 (美容與護膚)</t>
+          <t>肤色底调 (美容与护肤)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr"/>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t>膚色底調 (美容與護膚)</t>
+          <t>肤色底调 (美容与护肤)</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠duk̚]] 圍棋 (Baduk) (嗜好與休閒)</t>
+          <t>[[pa̠duk̚]] 围棋 (Baduk) (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠duk̚]] 圍棋 (Baduk) (嗜好與休閒)</t>
+          <t>[[pa̠duk̚]] 围棋 (Baduk) (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹nmunɦa̠k̚]] 天文學 (嗜好與休閒)</t>
+          <t>[[t͡ɕʰʌ̹nmunɦa̠k̚]] 天文学 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹nmunɦa̠k̚]] 天文學 (嗜好與休閒)</t>
+          <t>[[t͡ɕʰʌ̹nmunɦa̠k̚]] 天文学 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯŋma̠]] 騎馬 (嗜好與休閒)</t>
+          <t>[[sʰɯŋma̠]] 骑马 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯŋma̠]] 騎馬 (嗜好與休閒)</t>
+          <t>[[sʰɯŋma̠]] 骑马 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛo̞ŋd͡ʑima̠]] 塞翁失馬，焉知非福 (成語與諺語)</t>
+          <t>[[sʰɛo̞ŋd͡ʑima̠]] 塞翁失马，焉知非福 (成语与谚语)</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛo̞ŋd͡ʑima̠]] 塞翁失馬，焉知非福 (成語與諺語)</t>
+          <t>[[sʰɛo̞ŋd͡ʑima̠]] 塞翁失马，焉知非福 (成语与谚语)</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>[[ˈju(ː)jusʰa̠ŋd͡ʑo̞ŋ]] 物以類聚 (成語與諺語)</t>
+          <t>[[ˈju(ː)jusʰa̠ŋd͡ʑo̞ŋ]] 物以类聚 (成语与谚语)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t>[[ˈju(ː)jusʰa̠ŋd͡ʑo̞ŋ]] 物以類聚 (成語與諺語)</t>
+          <t>[[ˈju(ː)jusʰa̠ŋd͡ʑo̞ŋ]] 物以类聚 (成语与谚语)</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
@@ -5935,13 +5935,13 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>錦上添花 (慣用語與諺語)</t>
+          <t>锦上添花 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr"/>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>錦上添花 (慣用語與諺語)</t>
+          <t>锦上添花 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
@@ -5963,13 +5963,13 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>兩難局面 (慣用語與諺語)</t>
+          <t>两难局面 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr"/>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>兩難局面 (慣用語與諺語)</t>
+          <t>两难局面 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
@@ -5991,13 +5991,13 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>口才出眾 (慣用語與諺語)</t>
+          <t>口才出众 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr"/>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>口才出眾 (慣用語與諺語)</t>
+          <t>口才出众 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛda̠nsʰa̠]] Tailor (Fashion &amp; Style)</t>
+          <t>[[t͡ɕɛda̠nsʰa̠]] 网页装修工 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛda̠nsʰa̠]] Tailor (Fashion &amp; Style)</t>
+          <t>[[t͡ɕɛda̠nsʰa̠]] 网页装修工 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞ɭɭa̠bo̞]] Collaboration (fashion) (時尚與風格)</t>
+          <t>[[kʰo̞ɭɭa̠bo̞]] 协作 (时尚与风格)</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞ɭɭa̠bo̞]] Collaboration (fashion) (時尚與風格)</t>
+          <t>[[kʰo̞ɭɭa̠bo̞]] 协作 (时尚与风格)</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6083,13 +6083,13 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Runway (Fashion &amp; Style)</t>
+          <t>资金跑道 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr"/>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>Runway (Fashion &amp; Style)</t>
+          <t>资金跑道 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
@@ -6111,13 +6111,13 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Greenhouse Gas (Environment)</t>
+          <t>温室气体 (环境)</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr"/>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>Greenhouse Gas (Environment)</t>
+          <t>温室气体 (环境)</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -6139,13 +6139,13 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Reforestation (Environment)</t>
+          <t>再造林 (环境)</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr"/>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t>Reforestation (Environment)</t>
+          <t>再造林 (环境)</t>
         </is>
       </c>
       <c r="E191" s="1" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɡje̞]] Ecosystem (Environment)</t>
+          <t>[[sʰɛŋtʰɛɡje̞]] 生态系统 (环境)</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɡje̞]] Ecosystem (Environment)</t>
+          <t>[[sʰɛŋtʰɛɡje̞]] 生态系统 (环境)</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
@@ -6199,13 +6199,13 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>臭氧層 (環境)</t>
+          <t>臭氧层 (环境)</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr"/>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>臭氧層 (環境)</t>
+          <t>臭氧层 (环境)</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
@@ -6227,13 +6227,13 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>酸雨 (環境)</t>
+          <t>酸雨 (环境)</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr"/>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>酸雨 (環境)</t>
+          <t>酸雨 (环境)</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpo̞(ː)d͡ʑʌ̹n]] 保育 (環境)</t>
+          <t>[[ˈpo̞(ː)d͡ʑʌ̹n]] 保育 (环境)</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpo̞(ː)d͡ʑʌ̹n]] 保育 (環境)</t>
+          <t>[[ˈpo̞(ː)d͡ʑʌ̹n]] 保育 (环境)</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -6287,13 +6287,13 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>升級再造 (環境)</t>
+          <t>升级再造 (环境)</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr"/>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>升級再造 (環境)</t>
+          <t>升级再造 (环境)</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰɘ(ː)ɕʰik̚t͡ɕ͈i]] 棲息地 (環境)</t>
+          <t>[[ˈsʰɘ(ː)ɕʰik̚t͡ɕ͈i]] 栖息地 (环境)</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰɘ(ː)ɕʰik̚t͡ɕ͈i]] 棲息地 (環境)</t>
+          <t>[[ˈsʰɘ(ː)ɕʰik̚t͡ɕ͈i]] 栖息地 (环境)</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -6347,13 +6347,13 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>環境法 (環境)</t>
+          <t>环境法 (环境)</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr"/>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>環境法 (環境)</t>
+          <t>环境法 (环境)</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -6375,13 +6375,13 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>環境部 (環境)</t>
+          <t>环境部 (环境)</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr"/>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>環境部 (環境)</t>
+          <t>环境部 (环境)</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)sʰa̠nβwa̠tʰa̠nsʰo̞]] 二氧化碳 (環境)</t>
+          <t>[[ˈi(ː)sʰa̠nβwa̠tʰa̠nsʰo̞]] 二氧化碳 (环境)</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)sʰa̠nβwa̠tʰa̠nsʰo̞]] 二氧化碳 (環境)</t>
+          <t>[[ˈi(ː)sʰa̠nβwa̠tʰa̠nsʰo̞]] 二氧化碳 (环境)</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[[me̞tʰa̠n]] 甲烷 (環境)</t>
+          <t>[[me̞tʰa̠n]] 甲烷 (环境)</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>[[me̞tʰa̠n]] 甲烷 (環境)</t>
+          <t>[[me̞tʰa̠n]] 甲烷 (环境)</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -6467,13 +6467,13 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>綠色稅 (環境)</t>
+          <t>绿色税 (环境)</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr"/>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>綠色稅 (環境)</t>
+          <t>绿色税 (环境)</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
@@ -6495,13 +6495,13 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>水處理 (環境)</t>
+          <t>水处理 (环境)</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr"/>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>水處理 (環境)</t>
+          <t>水处理 (环境)</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋmuɭk͈wʌ̹n]] 生物圈 (環境)</t>
+          <t>[[sʰɛŋmuɭk͈wʌ̹n]] 生物圈 (环境)</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋmuɭk͈wʌ̹n]] 生物圈 (環境)</t>
+          <t>[[sʰɛŋmuɭk͈wʌ̹n]] 生物圈 (环境)</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕiɦa̠sʰu]] Groundwater (Environment)</t>
+          <t>[[t͡ɕiɦa̠sʰu]] 地下水 (环境)</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕiɦa̠sʰu]] Groundwater (Environment)</t>
+          <t>[[t͡ɕiɦa̠sʰu]] 地下水 (环境)</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -6587,13 +6587,13 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>Overfishing (Environment)</t>
+          <t>过度捕捞 (环境)</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr"/>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>Overfishing (Environment)</t>
+          <t>过度捕捞 (环境)</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
@@ -6615,13 +6615,13 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>Erosion (Environment)</t>
+          <t>腐蚀 (环境)</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr"/>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>Erosion (Environment)</t>
+          <t>腐蚀 (环境)</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɦa̠k̚]] Ecology (Environment)</t>
+          <t>[[sʰɛŋtʰɛɦa̠k̚]] 生态 (环境)</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɦa̠k̚]] Ecology (Environment)</t>
+          <t>[[sʰɛŋtʰɛɦa̠k̚]] 生态 (环境)</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -6675,13 +6675,13 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>獨立運動 (韓國歷史)</t>
+          <t>独立运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr"/>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>獨立運動 (韓國歷史)</t>
+          <t>独立运动 (韩国历史)</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -6703,13 +6703,13 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>三一運動 (韓國歷史)</t>
+          <t>三一运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr"/>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>三一運動 (韓國歷史)</t>
+          <t>三一运动 (韩国历史)</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)d͡ʑo̞sʰʌ̹n]] 古朝鮮 (韓國歷史)</t>
+          <t>[[ˈko̞(ː)d͡ʑo̞sʰʌ̹n]] 古朝鲜 (韩国历史)</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)d͡ʑo̞sʰʌ̹n]] 古朝鮮 (韓國歷史)</t>
+          <t>[[ˈko̞(ː)d͡ʑo̞sʰʌ̹n]] 古朝鲜 (韩国历史)</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɡuɾjʌ̹]] 高句麗 (韓國歷史)</t>
+          <t>[[ko̞ɡuɾjʌ̹]] 高句丽 (韩国历史)</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɡuɾjʌ̹]] 高句麗 (韓國歷史)</t>
+          <t>[[ko̞ɡuɾjʌ̹]] 高句丽 (韩国历史)</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>[[pɛk̚t͡ɕ͈e̞]] 百濟王國 (韓國歷史)</t>
+          <t>[[pɛk̚t͡ɕ͈e̞]] 百济王国 (韩国历史)</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>[[pɛk̚t͡ɕ͈e̞]] 百濟王國 (韓國歷史)</t>
+          <t>[[pɛk̚t͡ɕ͈e̞]] 百济王国 (韩国历史)</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -6827,13 +6827,13 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>李成桂（太祖） (韓國歷史)</t>
+          <t>李成桂（太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr"/>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>李成桂（太祖） (韓國歷史)</t>
+          <t>李成桂（太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>[[juɡjo]] 韓國儒學 (韓國歷史)</t>
+          <t>[[juɡjo]] 韩国儒学 (韩国历史)</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>[[juɡjo]] 韓國儒學 (韓國歷史)</t>
+          <t>[[juɡjo]] 韩国儒学 (韩国历史)</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -6887,13 +6887,13 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>高麗大藏經 (韓國歷史)</t>
+          <t>高丽大藏经 (韩国历史)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr"/>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>高麗大藏經 (韓國歷史)</t>
+          <t>高丽大藏经 (韩国历史)</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
@@ -6915,13 +6915,13 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>李舜臣將軍 (韓國歷史)</t>
+          <t>李舜臣将军 (韩国历史)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr"/>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>李舜臣將軍 (韓國歷史)</t>
+          <t>李舜臣将军 (韩国历史)</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[[imd͡ʑinwɛɾa̠n]] 壬辰戰爭 (韓國歷史)</t>
+          <t>[[imd͡ʑinwɛɾa̠n]] 壬辰战争 (韩国历史)</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>[[imd͡ʑinwɛɾa̠n]] 壬辰戰爭 (韓國歷史)</t>
+          <t>[[imd͡ʑinwɛɾa̠n]] 壬辰战争 (韩国历史)</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -6975,13 +6975,13 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>臨時政府 (韓國歷史)</t>
+          <t>临时政府 (韩国历史)</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr"/>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>臨時政府 (韓國歷史)</t>
+          <t>临时政府 (韩国历史)</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ŋd͡ʑa̠]] 青瓷 (韓國歷史)</t>
+          <t>[[t͡ɕʰʌ̹ŋd͡ʑa̠]] 青瓷 (韩国历史)</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ŋd͡ʑa̠]] 青瓷 (韓國歷史)</t>
+          <t>[[t͡ɕʰʌ̹ŋd͡ʑa̠]] 青瓷 (韩国历史)</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>[[çud͡ʑʌ̹n]] 停戰協定 (韓國歷史)</t>
+          <t>[[çud͡ʑʌ̹n]] 停战协定 (韩国历史)</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>[[çud͡ʑʌ̹n]] 停戰協定 (韓國歷史)</t>
+          <t>[[çud͡ʑʌ̹n]] 停战协定 (韩国历史)</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠nɡun]] 檀君 (韓國歷史)</t>
+          <t>[[ta̠nɡun]] 檀君 (韩国历史)</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠nɡun]] 檀君 (韓國歷史)</t>
+          <t>[[ta̠nɡun]] 檀君 (韩国历史)</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹nbi]] 儒生（朝鮮） (韓國歷史)</t>
+          <t>[[sʰʌ̹nbi]] 儒生（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹nbi]] 儒生（朝鮮） (韓國歷史)</t>
+          <t>[[sʰʌ̹nbi]] 儒生（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠ɾa̠ŋ]] 花郎 (韓國歷史)</t>
+          <t>[[ɸwa̠ɾa̠ŋ]] 花郎 (韩国历史)</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠ɾa̠ŋ]] 花郎 (韓國歷史)</t>
+          <t>[[ɸwa̠ɾa̠ŋ]] 花郎 (韩国历史)</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
@@ -7163,13 +7163,13 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>高宗皇帝 (韓國歷史)</t>
+          <t>高宗皇帝 (韩国历史)</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr"/>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>高宗皇帝 (韓國歷史)</t>
+          <t>高宗皇帝 (韩国历史)</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
@@ -7191,13 +7191,13 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>大韓帝國 (韓國歷史)</t>
+          <t>大韩帝国 (韩国历史)</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr"/>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>大韓帝國 (韓國歷史)</t>
+          <t>大韩帝国 (韩国历史)</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
@@ -7219,13 +7219,13 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>甲午戰爭 (韓國歷史)</t>
+          <t>甲午战争 (韩国历史)</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr"/>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>甲午戰爭 (韓國歷史)</t>
+          <t>甲午战争 (韩国历史)</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
@@ -7247,13 +7247,13 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>瞻星臺天文台 (韓國歷史)</t>
+          <t>瞻星台天文台 (韩国历史)</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr"/>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t>瞻星臺天文台 (韓國歷史)</t>
+          <t>瞻星台天文台 (韩国历史)</t>
         </is>
       </c>
       <c r="E228" s="1" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ŋɡjunɡwa̠n]] 成均館 (韓國歷史)</t>
+          <t>[[sʰʌ̹ŋɡjunɡwa̠n]] 成均馆 (韩国历史)</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ŋɡjunɡwa̠n]] 成均館 (韓國歷史)</t>
+          <t>[[sʰʌ̹ŋɡjunɡwa̠n]] 成均馆 (韩国历史)</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -7307,13 +7307,13 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>宗廟 (韓國歷史)</t>
+          <t>宗庙 (韩国历史)</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr"/>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>宗廟 (韓國歷史)</t>
+          <t>宗庙 (韩国历史)</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
@@ -7335,13 +7335,13 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>奎章閣御覽所 (韓國歷史)</t>
+          <t>奎章阁御览所 (韩国历史)</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr"/>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>奎章閣御覽所 (韓國歷史)</t>
+          <t>奎章阁御览所 (韩国历史)</t>
         </is>
       </c>
       <c r="E231" s="1" t="inlineStr">
@@ -7363,13 +7363,13 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>東學運動 (韓國歷史)</t>
+          <t>东学运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr"/>
       <c r="D232" s="1" t="inlineStr">
         <is>
-          <t>東學運動 (韓國歷史)</t>
+          <t>东学运动 (韩国历史)</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>[[pʰuŋsʰu]] 風水（韓國堪輿學） (韓國歷史)</t>
+          <t>[[pʰuŋsʰu]] 风水（韩国堪舆学） (韩国历史)</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>[[pʰuŋsʰu]] 風水（韓國堪輿學） (韓國歷史)</t>
+          <t>[[pʰuŋsʰu]] 风水（韩国堪舆学） (韩国历史)</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋba̠n]] 兩班（貴族） (韓國歷史)</t>
+          <t>[[ja̠ŋba̠n]] 两班（贵族） (韩国历史)</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋba̠n]] 兩班（貴族） (韓國歷史)</t>
+          <t>[[ja̠ŋba̠n]] 两班（贵族） (韩国历史)</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
@@ -7455,13 +7455,13 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>科舉考試 (韓國歷史)</t>
+          <t>科举考试 (韩国历史)</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr"/>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t>科舉考試 (韓國歷史)</t>
+          <t>科举考试 (韩国历史)</t>
         </is>
       </c>
       <c r="E235" s="1" t="inlineStr">
@@ -7483,13 +7483,13 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>朝鮮社會階級 (韓國歷史)</t>
+          <t>朝鲜社会阶级 (韩国历史)</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr"/>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t>朝鮮社會階級 (韓國歷史)</t>
+          <t>朝鲜社会阶级 (韩国历史)</t>
         </is>
       </c>
       <c r="E236" s="1" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚k͈uŋ]] 韓國傳統射箭 (韓國歷史)</t>
+          <t>[[kuk̚k͈uŋ]] 韩国传统射箭 (韩国历史)</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚k͈uŋ]] 韓國傳統射箭 (韓國歷史)</t>
+          <t>[[kuk̚k͈uŋ]] 韩国传统射箭 (韩国历史)</t>
         </is>
       </c>
       <c r="E237" s="1" t="inlineStr">
@@ -7543,13 +7543,13 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>石窟庵 (韓國歷史)</t>
+          <t>石窟庵 (韩国历史)</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr"/>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t>石窟庵 (韓國歷史)</t>
+          <t>石窟庵 (韩国历史)</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
@@ -7571,13 +7571,13 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>科舉考試（朝鮮） (韓國歷史)</t>
+          <t>科举考试（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr"/>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>科舉考試（朝鮮） (韓國歷史)</t>
+          <t>科举考试（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
@@ -7599,13 +7599,13 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>統一新羅 (韓國歷史)</t>
+          <t>统一新罗 (韩国历史)</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr"/>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t>統一新羅 (韓國歷史)</t>
+          <t>统一新罗 (韩国历史)</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
@@ -7627,13 +7627,13 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>王建（高麗太祖） (韓國歷史)</t>
+          <t>王建（高丽太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr"/>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t>王建（高麗太祖） (韓國歷史)</t>
+          <t>王建（高丽太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="E241" s="1" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ndo̞ɡjo]] 天道教 (韓國歷史)</t>
+          <t>[[t͡ɕʰʌ̹ndo̞ɡjo]] 天道教 (韩国历史)</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ndo̞ɡjo]] 天道教 (韓國歷史)</t>
+          <t>[[t͡ɕʰʌ̹ndo̞ɡjo]] 天道教 (韩国历史)</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuks͈a̠ɡi]] 三國史記 (韓國歷史)</t>
+          <t>[[sʰa̠mɡuks͈a̠ɡi]] 三国史记 (韩国历史)</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuks͈a̠ɡi]] 三國史記 (韓國歷史)</t>
+          <t>[[sʰa̠mɡuks͈a̠ɡi]] 三国史记 (韩国历史)</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuɡjusʰa̠]] 三國遺事 (韓國歷史)</t>
+          <t>[[sʰa̠mɡuɡjusʰa̠]] 三国遗事 (韩国历史)</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuɡjusʰa̠]] 三國遺事 (韓國歷史)</t>
+          <t>[[sʰa̠mɡuɡjusʰa̠]] 三国遗事 (韩国历史)</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
@@ -7751,13 +7751,13 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>東醫寶鑑 (韓國歷史)</t>
+          <t>东医宝鉴 (韩国历史)</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr"/>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>東醫寶鑑 (韓國歷史)</t>
+          <t>东医宝鉴 (韩国历史)</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
@@ -7779,13 +7779,13 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>朴正熙 (韓國歷史)</t>
+          <t>朴正熙 (韩国历史)</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr"/>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>朴正熙 (韓國歷史)</t>
+          <t>朴正熙 (韩国历史)</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
@@ -7807,13 +7807,13 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>李承晚 (韓國歷史)</t>
+          <t>李承晚 (韩国历史)</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr"/>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t>李承晚 (韓國歷史)</t>
+          <t>李承晚 (韩国历史)</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
@@ -7835,13 +7835,13 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>安重根 (韓國歷史)</t>
+          <t>安重根 (韩国历史)</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr"/>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t>安重根 (韓國歷史)</t>
+          <t>安重根 (韩国历史)</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
@@ -7863,13 +7863,13 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>直指心傳 (韓國歷史)</t>
+          <t>直指心传 (韩国历史)</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr"/>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t>直指心傳 (韓國歷史)</t>
+          <t>直指心传 (韩国历史)</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɘ(ː)np͈ʌ̹p̚]] 憲法 (法律與政府)</t>
+          <t>[[ˈhɘ(ː)np͈ʌ̹p̚]] 宪法 (法律与政府)</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɘ(ː)np͈ʌ̹p̚]] 憲法 (法律與政府)</t>
+          <t>[[ˈhɘ(ː)np͈ʌ̹p̚]] 宪法 (法律与政府)</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰa̠(ː)ŋwʌ̹nɰiwʌ̹n]] 參議員 (法律與政府)</t>
+          <t>[[ˈsʰa̠(ː)ŋwʌ̹nɰiwʌ̹n]] 参议员 (法律与政府)</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰa̠(ː)ŋwʌ̹nɰiwʌ̹n]] 參議員 (法律與政府)</t>
+          <t>[[ˈsʰa̠(ː)ŋwʌ̹nɰiwʌ̹n]] 参议员 (法律与政府)</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ŋβwa̠ɡuk̚]] 共和國 (法律與政府)</t>
+          <t>[[ˈko̞(ː)ŋβwa̠ɡuk̚]] 共和国 (法律与政府)</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ŋβwa̠ɡuk̚]] 共和國 (法律與政府)</t>
+          <t>[[ˈko̞(ː)ŋβwa̠ɡuk̚]] 共和国 (法律与政府)</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
@@ -7987,13 +7987,13 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>君主制 (法律與政府)</t>
+          <t>君主制 (法律与政府)</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr"/>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>君主制 (法律與政府)</t>
+          <t>君主制 (法律与政府)</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>[[ip̚p͈ʌ̹p̚]] 立法 (法律與政府)</t>
+          <t>[[ip̚p͈ʌ̹p̚]] 立法 (法律与政府)</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>[[ip̚p͈ʌ̹p̚]] 立法 (法律與政府)</t>
+          <t>[[ip̚p͈ʌ̹p̚]] 立法 (法律与政府)</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>[[wʌ̹nɡo̞]] 原告 (法律與政府)</t>
+          <t>[[wʌ̹nɡo̞]] 原告 (法律与政府)</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t>[[wʌ̹nɡo̞]] 原告 (法律與政府)</t>
+          <t>[[wʌ̹nɡo̞]] 原告 (法律与政府)</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
@@ -8079,13 +8079,13 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>陪審團 (法律與政府)</t>
+          <t>陪审团 (法律与政府)</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr"/>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t>陪審團 (法律與政府)</t>
+          <t>陪审团 (法律与政府)</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ŋɡjʌ̹ɭ]] 判決 (法律與政府)</t>
+          <t>[[pʰjʌ̹ŋɡjʌ̹ɭ]] 判决 (法律与政府)</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ŋɡjʌ̹ɭ]] 判決 (法律與政府)</t>
+          <t>[[pʰjʌ̹ŋɡjʌ̹ɭ]] 判决 (法律与政府)</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ŋsʰo̞]] 上訴 (法律與政府)</t>
+          <t>[[ˈha̠(ː)ŋsʰo̞]] 上诉 (法律与政府)</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ŋsʰo̞]] 上訴 (法律與政府)</t>
+          <t>[[ˈha̠(ː)ŋsʰo̞]] 上诉 (法律与政府)</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律與政府)</t>
+          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律与政府)</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律與政府)</t>
+          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律与政府)</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɕʰi(ː)mink͈wʌ̹n]] 公民權利 (法律與政府)</t>
+          <t>[[ˈɕʰi(ː)mink͈wʌ̹n]] 公民权利 (法律与政府)</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɕʰi(ː)mink͈wʌ̹n]] 公民權利 (法律與政府)</t>
+          <t>[[ˈɕʰi(ː)mink͈wʌ̹n]] 公民权利 (法律与政府)</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞ŋɲʌ̹ŋ]] 挪用公款 (法律與政府)</t>
+          <t>[[ɸwe̞ŋɲʌ̹ŋ]] 挪用公款 (法律与政府)</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞ŋɲʌ̹ŋ]] 挪用公款 (法律與政府)</t>
+          <t>[[ɸwe̞ŋɲʌ̹ŋ]] 挪用公款 (法律与政府)</t>
         </is>
       </c>
       <c r="E261" s="1" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ɭs͈e̞]] 逃漏稅 (法律與政府)</t>
+          <t>[[tʰa̠ɭs͈e̞]] 逃漏税 (法律与政府)</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ɭs͈e̞]] 逃漏稅 (法律與政府)</t>
+          <t>[[tʰa̠ɭs͈e̞]] 逃漏税 (法律与政府)</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -8299,13 +8299,13 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>性騷擾 (法律與政府)</t>
+          <t>性骚扰 (法律与政府)</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr"/>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t>性騷擾 (法律與政府)</t>
+          <t>性骚扰 (法律与政府)</t>
         </is>
       </c>
       <c r="E263" s="1" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɘ(ː)d͡ʑa̠k̚k͈wʌ̹n]] 版權 (法律與政府)</t>
+          <t>[[ˈt͡ɕɘ(ː)d͡ʑa̠k̚k͈wʌ̹n]] 版权 (法律与政府)</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɘ(ː)d͡ʑa̠k̚k͈wʌ̹n]] 版權 (法律與政府)</t>
+          <t>[[ˈt͡ɕɘ(ː)d͡ʑa̠k̚k͈wʌ̹n]] 版权 (法律与政府)</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠ŋpʰjo]] 商標 (法律與政府)</t>
+          <t>[[sʰa̠ŋpʰjo]] 商标 (法律与政府)</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠ŋpʰjo]] 商標 (法律與政府)</t>
+          <t>[[sʰa̠ŋpʰjo]] 商标 (法律与政府)</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɯkʰʌ̹]] 專利 (法律與政府)</t>
+          <t>[[tʰɯkʰʌ̹]] 专利 (法律与政府)</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɯkʰʌ̹]] 專利 (法律與政府)</t>
+          <t>[[tʰɯkʰʌ̹]] 专利 (法律与政府)</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋd͡ʑɯŋin]] 公證人 (法律與政府)</t>
+          <t>[[ko̞ŋd͡ʑɯŋin]] 公证人 (法律与政府)</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋd͡ʑɯŋin]] 公證人 (法律與政府)</t>
+          <t>[[ko̞ŋd͡ʑɯŋin]] 公证人 (法律与政府)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
@@ -8455,13 +8455,13 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>民法 (法律與政府)</t>
+          <t>民法 (法律与政府)</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr"/>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>民法 (法律與政府)</t>
+          <t>民法 (法律与政府)</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹ŋp͈ʌ̹p̚]] 刑法 (法律與政府)</t>
+          <t>[[çʌ̹ŋp͈ʌ̹p̚]] 刑法 (法律与政府)</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹ŋp͈ʌ̹p̚]] 刑法 (法律與政府)</t>
+          <t>[[çʌ̹ŋp͈ʌ̹p̚]] 刑法 (法律与政府)</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹p̚]] 行政法 (法律與政府)</t>
+          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹p̚]] 行政法 (法律与政府)</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹p̚]] 行政法 (法律與政府)</t>
+          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹p̚]] 行政法 (法律与政府)</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚t͡ɕ͈e̞bʌ̹p̚]] 國際法 (法律與政府)</t>
+          <t>[[kuk̚t͡ɕ͈e̞bʌ̹p̚]] 国际法 (法律与政府)</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚t͡ɕ͈e̞bʌ̹p̚]] 國際法 (法律與政府)</t>
+          <t>[[kuk̚t͡ɕ͈e̞bʌ̹p̚]] 国际法 (法律与政府)</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ja̠k̚]] 條約 (法律與政府)</t>
+          <t>[[t͡ɕo̞ja̠k̚]] 条约 (法律与政府)</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ja̠k̚]] 條約 (法律與政府)</t>
+          <t>[[t͡ɕo̞ja̠k̚]] 条约 (法律与政府)</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋsʰa̠]] 領事 (法律與政府)</t>
+          <t>[[jʌ̹ŋsʰa̠]] 领事 (法律与政府)</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋsʰa̠]] 領事 (法律與政府)</t>
+          <t>[[jʌ̹ŋsʰa̠]] 领事 (法律与政府)</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwe̞(ː)ɡjo]] 外交事務 (法律與政府)</t>
+          <t>[[ˈwe̞(ː)ɡjo]] 外交事务 (法律与政府)</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwe̞(ː)ɡjo]] 外交事務 (法律與政府)</t>
+          <t>[[ˈwe̞(ː)ɡjo]] 外交事务 (法律与政府)</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
@@ -8675,13 +8675,13 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Naturalization (法律與政府)</t>
+          <t>归化 (法律与政府)</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr"/>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>Naturalization (法律與政府)</t>
+          <t>归化 (法律与政府)</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
@@ -8703,13 +8703,13 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>Resident Registration (法律與政府)</t>
+          <t>居民登记 (法律与政府)</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr"/>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>Resident Registration (法律與政府)</t>
+          <t>居民登记 (法律与政府)</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋmu]] Public Service (法律與政府)</t>
+          <t>[[ko̞ŋmu]] 公务员制度 (法律与政府)</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋmu]] Public Service (法律與政府)</t>
+          <t>[[ko̞ŋmu]] 公务员制度 (法律与政府)</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠ʎʎod͡ʑe̞]] Bureaucracy (法律與政府)</t>
+          <t>[[kwa̠ʎʎod͡ʑe̞]] 官僚制 (法律与政府)</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠ʎʎod͡ʑe̞]] Bureaucracy (法律與政府)</t>
+          <t>[[kwa̠ʎʎod͡ʑe̞]] 官僚制 (法律与政府)</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕipʰɛŋ]] Enforcement (法律與政府)</t>
+          <t>[[t͡ɕipʰɛŋ]] 强制执行 (法律与政府)</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕipʰɛŋ]] Enforcement (法律與政府)</t>
+          <t>[[t͡ɕipʰɛŋ]] 强制执行 (法律与政府)</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠sʰe̞]] Taxation (法律與政府)</t>
+          <t>[[kwa̠sʰe̞]] 税项 (法律与政府)</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠sʰe̞]] Taxation (法律與政府)</t>
+          <t>[[kwa̠sʰe̞]] 税项 (法律与政府)</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋa̠ŋɯnɦɛŋ]] Central Bank (法律與政府)</t>
+          <t>[[t͡ɕuŋa̠ŋɯnɦɛŋ]] 中央银行 (法律与政府)</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋa̠ŋɯnɦɛŋ]] Central Bank (法律與政府)</t>
+          <t>[[t͡ɕuŋa̠ŋɯnɦɛŋ]] 中央银行 (法律与政府)</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[[tɛbʌ̹bwʌ̹n]] Supreme Court (法律與政府)</t>
+          <t>[[tɛbʌ̹bwʌ̹n]] 最高法院 (法律与政府)</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>[[tɛbʌ̹bwʌ̹n]] Supreme Court (法律與政府)</t>
+          <t>[[tɛbʌ̹bwʌ̹n]] 最高法院 (法律与政府)</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹nbʌ̹p̚t͡ɕ͈ɛpʰa̠nsʰo̞]] Constitutional Court (法律與政府)</t>
+          <t>[[hʌ̹nbʌ̹p̚t͡ɕ͈ɛpʰa̠nsʰo̞]] 宪法法庭 (法律与政府)</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹nbʌ̹p̚t͡ɕ͈ɛpʰa̠nsʰo̞]] Constitutional Court (法律與政府)</t>
+          <t>[[hʌ̹nbʌ̹p̚t͡ɕ͈ɛpʰa̠nsʰo̞]] 宪法法庭 (法律与政府)</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹bwʌ̹n]] Administrative Court (法律與政府)</t>
+          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹bwʌ̹n]] 行政法院 (法律与政府)</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹bwʌ̹n]] Administrative Court (法律與政府)</t>
+          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹bwʌ̹n]] 行政法院 (法律与政府)</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>[[kuŋmintʰupʰjo]] Referendum (法律與政府)</t>
+          <t>[[kuŋmintʰupʰjo]] 公民投票 (法律与政府)</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>[[kuŋmintʰupʰjo]] Referendum (法律與政府)</t>
+          <t>[[kuŋmintʰupʰjo]] 公民投票 (法律与政府)</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)nɦɛk̚]] Impeachment (法律與政府)</t>
+          <t>[[ˈtʰa̠(ː)nɦɛk̚]] 弹劾 (法律与政府)</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)nɦɛk̚]] Impeachment (法律與政府)</t>
+          <t>[[ˈtʰa̠(ː)nɦɛk̚]] 弹劾 (法律与政府)</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ʎʎe̞]] Legal Precedent (法律與政府)</t>
+          <t>[[pʰa̠ʎʎe̞]] 成案 ,判例 (法律与政府)</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ʎʎe̞]] Legal Precedent (法律與政府)</t>
+          <t>[[pʰa̠ʎʎe̞]] 成案 ,判例 (法律与政府)</t>
         </is>
       </c>
       <c r="E287" s="1" t="inlineStr">
@@ -9083,13 +9083,13 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Statute of Limitations (法律與政府)</t>
+          <t>时效法规 (法律与政府)</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr"/>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t>Statute of Limitations (法律與政府)</t>
+          <t>时效法规 (法律与政府)</t>
         </is>
       </c>
       <c r="E288" s="1" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>[[kut̚]] 巫俗儀式 (宗教)</t>
+          <t>[[kut̚]] 巫俗仪式 (宗教)</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t>[[kut̚]] 巫俗儀式 (宗教)</t>
+          <t>[[kut̚]] 巫俗仪式 (宗教)</t>
         </is>
       </c>
       <c r="E289" s="1" t="inlineStr">
@@ -9143,13 +9143,13 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>排燈節 (宗教)</t>
+          <t>排灯节 (宗教)</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr"/>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>排燈節 (宗教)</t>
+          <t>排灯节 (宗教)</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)ɡjodo̞]] 異教徒 (宗教)</t>
+          <t>[[ˈi(ː)ɡjodo̞]] 异教徒 (宗教)</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)ɡjodo̞]] 異教徒 (宗教)</t>
+          <t>[[ˈi(ː)ɡjodo̞]] 异教徒 (宗教)</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
@@ -9203,13 +9203,13 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>不可知論者 (宗教)</t>
+          <t>不可知论者 (宗教)</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr"/>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>不可知論者 (宗教)</t>
+          <t>不可知论者 (宗教)</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰo̞(ː)ɡjo]] 傳教 (宗教)</t>
+          <t>[[ˈpʰo̞(ː)ɡjo]] 传教 (宗教)</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰo̞(ː)ɡjo]] 傳教 (宗教)</t>
+          <t>[[ˈpʰo̞(ː)ɡjo]] 传教 (宗教)</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹n]] 禪 (宗教)</t>
+          <t>[[sʰʌ̹n]] 禅 (宗教)</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹n]] 禪 (宗教)</t>
+          <t>[[sʰʌ̹n]] 禅 (宗教)</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
@@ -9327,13 +9327,13 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>驅魔 (宗教)</t>
+          <t>驱魔 (宗教)</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr"/>
       <c r="D296" s="1" t="inlineStr">
         <is>
-          <t>驅魔 (宗教)</t>
+          <t>驱魔 (宗教)</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
@@ -9355,13 +9355,13 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>KOSPI (金融與銀行)</t>
+          <t>台湾加权 (金融与银行)</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr"/>
       <c r="D297" s="1" t="inlineStr">
         <is>
-          <t>KOSPI (金融與銀行)</t>
+          <t>台湾加权 (金融与银行)</t>
         </is>
       </c>
       <c r="E297" s="1" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>[[pitʰɯkʰo̞in]] 比特幣 (金融與銀行)</t>
+          <t>[[pitʰɯkʰo̞in]] 比特币 (金融与银行)</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="D298" s="1" t="inlineStr">
         <is>
-          <t>[[pitʰɯkʰo̞in]] 比特幣 (金融與銀行)</t>
+          <t>[[pitʰɯkʰo̞in]] 比特币 (金融与银行)</t>
         </is>
       </c>
       <c r="E298" s="1" t="inlineStr">
@@ -9415,13 +9415,13 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>企業稅 (金融與銀行)</t>
+          <t>企业税 (金融与银行)</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr"/>
       <c r="D299" s="1" t="inlineStr">
         <is>
-          <t>企業稅 (金融與銀行)</t>
+          <t>企业税 (金融与银行)</t>
         </is>
       </c>
       <c r="E299" s="1" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰa̠(ː)sʰa̠n]] 破產 (金融與銀行)</t>
+          <t>[[ˈpʰa̠(ː)sʰa̠n]] 破产 (金融与银行)</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰa̠(ː)sʰa̠n]] 破產 (金融與銀行)</t>
+          <t>[[ˈpʰa̠(ː)sʰa̠n]] 破产 (金融与银行)</t>
         </is>
       </c>
       <c r="E300" s="1" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)ɡwʌ̹ɲd͡ʑa̠]] 債權人 (金融與銀行)</t>
+          <t>[[ˈt͡ɕʰɛ(ː)ɡwʌ̹ɲd͡ʑa̠]] 债权人 (金融与银行)</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)ɡwʌ̹ɲd͡ʑa̠]] 債權人 (金融與銀行)</t>
+          <t>[[ˈt͡ɕʰɛ(ː)ɡwʌ̹ɲd͡ʑa̠]] 债权人 (金融与银行)</t>
         </is>
       </c>
       <c r="E301" s="1" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)mud͡ʑa̠]] 債務人 (金融與銀行)</t>
+          <t>[[ˈt͡ɕʰɛ(ː)mud͡ʑa̠]] 债务人 (金融与银行)</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)mud͡ʑa̠]] 債務人 (金融與銀行)</t>
+          <t>[[ˈt͡ɕʰɛ(ː)mud͡ʑa̠]] 债务人 (金融与银行)</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠mbo̞]] 抵押品 (金融與銀行)</t>
+          <t>[[ta̠mbo̞]] 抵押品 (金融与银行)</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠mbo̞]] 抵押品 (金融與銀行)</t>
+          <t>[[ta̠mbo̞]] 抵押品 (金融与银行)</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
@@ -9571,13 +9571,13 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>擔保人 (金融與銀行)</t>
+          <t>担保人 (金融与银行)</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr"/>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t>擔保人 (金融與銀行)</t>
+          <t>担保人 (金融与银行)</t>
         </is>
       </c>
       <c r="E304" s="1" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>[[tipʰɯɭɭe̞iɕʰʌ̹n]] 通貨緊縮 (金融與銀行)</t>
+          <t>[[tipʰɯɭɭe̞iɕʰʌ̹n]] 通货紧缩 (金融与银行)</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="D305" s="1" t="inlineStr">
         <is>
-          <t>[[tipʰɯɭɭe̞iɕʰʌ̹n]] 通貨緊縮 (金融與銀行)</t>
+          <t>[[tipʰɯɭɭe̞iɕʰʌ̹n]] 通货紧缩 (金融与银行)</t>
         </is>
       </c>
       <c r="E305" s="1" t="inlineStr">
@@ -9631,13 +9631,13 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>FSC (Financial Services Commission) (Finance &amp; Banking)</t>
+          <t>金融监督委员会 (金融银行)</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr"/>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t>FSC (Financial Services Commission) (Finance &amp; Banking)</t>
+          <t>金融监督委员会 (金融银行)</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
@@ -9659,13 +9659,13 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>OECD (Finance &amp; Banking)</t>
+          <t>经济合作与发展组织（OECD） (金融银行)</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr"/>
       <c r="D307" s="1" t="inlineStr">
         <is>
-          <t>OECD (Finance &amp; Banking)</t>
+          <t>经济合作与发展组织（OECD） (金融银行)</t>
         </is>
       </c>
       <c r="E307" s="1" t="inlineStr">
@@ -9687,13 +9687,13 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>IMF (Finance &amp; Banking)</t>
+          <t>国际货币基金组织（IMF） (金融银行)</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr"/>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t>IMF (Finance &amp; Banking)</t>
+          <t>国际货币基金组织（IMF） (金融银行)</t>
         </is>
       </c>
       <c r="E308" s="1" t="inlineStr">
@@ -9715,13 +9715,13 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>World Bank (Finance &amp; Banking)</t>
+          <t>世界银行 (金融银行)</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr"/>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t>World Bank (Finance &amp; Banking)</t>
+          <t>世界银行 (金融银行)</t>
         </is>
       </c>
       <c r="E309" s="1" t="inlineStr">
@@ -9743,13 +9743,13 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>M&amp;A (Finance &amp; Banking)</t>
+          <t>并购 (金融银行)</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr"/>
       <c r="D310" s="1" t="inlineStr">
         <is>
-          <t>M&amp;A (Finance &amp; Banking)</t>
+          <t>并购 (金融银行)</t>
         </is>
       </c>
       <c r="E310" s="1" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋɡɛin]] Broker (Finance &amp; Banking)</t>
+          <t>[[t͡ɕuŋɡɛin]] 经纪商 (金融银行)</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋɡɛin]] Broker (Finance &amp; Banking)</t>
+          <t>[[t͡ɕuŋɡɛin]] 经纪商 (金融银行)</t>
         </is>
       </c>
       <c r="E311" s="1" t="inlineStr">
@@ -9803,13 +9803,13 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>Trader (Finance &amp; Banking)</t>
+          <t>交易商 (金融银行)</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr"/>
       <c r="D312" s="1" t="inlineStr">
         <is>
-          <t>Trader (Finance &amp; Banking)</t>
+          <t>交易商 (金融银行)</t>
         </is>
       </c>
       <c r="E312" s="1" t="inlineStr">
@@ -9831,13 +9831,13 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>幕牆 (建築)</t>
+          <t>幕墙 (建筑)</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr"/>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t>幕牆 (建築)</t>
+          <t>幕墙 (建筑)</t>
         </is>
       </c>
       <c r="E313" s="1" t="inlineStr">
@@ -9859,13 +9859,13 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>Zoning (建築)</t>
+          <t>分区 (建筑)</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr"/>
       <c r="D314" s="1" t="inlineStr">
         <is>
-          <t>Zoning (建築)</t>
+          <t>分区 (建筑)</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
@@ -9887,13 +9887,13 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>Wayfinding (建築)</t>
+          <t>寻路。 (建筑)</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr"/>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t>Wayfinding (建築)</t>
+          <t>寻路。 (建筑)</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmʝa̠ŋ]] 聲學 (建築)</t>
+          <t>[[ɯmʝa̠ŋ]] 声学 (建筑)</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmʝa̠ŋ]] 聲學 (建築)</t>
+          <t>[[ɯmʝa̠ŋ]] 声学 (建筑)</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -9947,13 +9947,13 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>暖通空調 (建築)</t>
+          <t>暖通空调 (建筑)</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr"/>
       <c r="D317" s="1" t="inlineStr">
         <is>
-          <t>暖通空調 (建築)</t>
+          <t>暖通空调 (建筑)</t>
         </is>
       </c>
       <c r="E317" s="1" t="inlineStr">
@@ -9975,13 +9975,13 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>預製 (建築)</t>
+          <t>预制 (建筑)</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr"/>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t>預製 (建築)</t>
+          <t>预制 (建筑)</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
@@ -10003,13 +10003,13 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>神經科學 (科學與研究)</t>
+          <t>神经科学 (科学与研究)</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr"/>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t>神經科學 (科學與研究)</t>
+          <t>神经科学 (科学与研究)</t>
         </is>
       </c>
       <c r="E319" s="1" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>[[iʎʎuɦa̠k̚]] 人類學 (科學與研究)</t>
+          <t>[[iʎʎuɦa̠k̚]] 人类学 (科学与研究)</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t>[[iʎʎuɦa̠k̚]] 人類學 (科學與研究)</t>
+          <t>[[iʎʎuɦa̠k̚]] 人类学 (科学与研究)</t>
         </is>
       </c>
       <c r="E320" s="1" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ɡo̞ɦa̠k̚]] 考古學 (科學與研究)</t>
+          <t>[[ˈko̞(ː)ɡo̞ɦa̠k̚]] 考古学 (科学与研究)</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ɡo̞ɦa̠k̚]] 考古學 (科學與研究)</t>
+          <t>[[ˈko̞(ː)ɡo̞ɦa̠k̚]] 考古学 (科学与研究)</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>[[ʌ̹nʌ̹ɦa̠k̚]] 語言學 (科學與研究)</t>
+          <t>[[ʌ̹nʌ̹ɦa̠k̚]] 语言学 (科学与研究)</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>[[ʌ̹nʌ̹ɦa̠k̚]] 語言學 (科學與研究)</t>
+          <t>[[ʌ̹nʌ̹ɦa̠k̚]] 语言学 (科学与研究)</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -10127,13 +10127,13 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>機器人學 (科學與研究)</t>
+          <t>机器人学 (科学与研究)</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr"/>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t>機器人學 (科學與研究)</t>
+          <t>机器人学 (科学与研究)</t>
         </is>
       </c>
       <c r="E323" s="1" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>[[na̠no̞ɡisʰuɭ]] 奈米技術 (科學與研究)</t>
+          <t>[[na̠no̞ɡisʰuɭ]] 奈米技术 (科学与研究)</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t>[[na̠no̞ɡisʰuɭ]] 奈米技術 (科學與研究)</t>
+          <t>[[na̠no̞ɡisʰuɭ]] 奈米技术 (科学与研究)</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
@@ -10187,13 +10187,13 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>生物技術 (科學與研究)</t>
+          <t>生物技术 (科学与研究)</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr"/>
       <c r="D325" s="1" t="inlineStr">
         <is>
-          <t>生物技術 (科學與研究)</t>
+          <t>生物技术 (科学与研究)</t>
         </is>
       </c>
       <c r="E325" s="1" t="inlineStr">
@@ -10215,13 +10215,13 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>基因工程 (科學與研究)</t>
+          <t>基因工程 (科学与研究)</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr"/>
       <c r="D326" s="1" t="inlineStr">
         <is>
-          <t>基因工程 (科學與研究)</t>
+          <t>基因工程 (科学与研究)</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
@@ -10243,13 +10243,13 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>幹細胞 (科學與研究)</t>
+          <t>干细胞 (科学与研究)</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr"/>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t>幹細胞 (科學與研究)</t>
+          <t>干细胞 (科学与研究)</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
@@ -10271,13 +10271,13 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>臨床試驗 (科學與研究)</t>
+          <t>临床试验 (科学与研究)</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr"/>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t>臨床試驗 (科學與研究)</t>
+          <t>临床试验 (科学与研究)</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
@@ -10299,13 +10299,13 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>博士後研究員 (科學與研究)</t>
+          <t>博士后研究员 (科学与研究)</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr"/>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t>博士後研究員 (科學與研究)</t>
+          <t>博士后研究员 (科学与研究)</t>
         </is>
       </c>
       <c r="E329" s="1" t="inlineStr">
@@ -10327,13 +10327,13 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>Meta-analysis (Science &amp; Research)</t>
+          <t>元分析 (科学研究)</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr"/>
       <c r="D330" s="1" t="inlineStr">
         <is>
-          <t>Meta-analysis (Science &amp; Research)</t>
+          <t>元分析 (科学研究)</t>
         </is>
       </c>
       <c r="E330" s="1" t="inlineStr">
@@ -10355,13 +10355,13 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>Control Group (Science &amp; Research)</t>
+          <t>对照组 (科学研究)</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr"/>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t>Control Group (Science &amp; Research)</t>
+          <t>对照组 (科学研究)</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpjɘ(ː)nsʰu]] Variable (Science &amp; Research)</t>
+          <t>[[ˈpjɘ(ː)nsʰu]] 变量 (科学研究)</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpjɘ(ː)nsʰu]] Variable (Science &amp; Research)</t>
+          <t>[[ˈpjɘ(ː)nsʰu]] 变量 (科学研究)</t>
         </is>
       </c>
       <c r="E332" s="1" t="inlineStr">
@@ -10415,13 +10415,13 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>Correlation (Science &amp; Research)</t>
+          <t>相关性 (科学研究)</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr"/>
       <c r="D333" s="1" t="inlineStr">
         <is>
-          <t>Correlation (Science &amp; Research)</t>
+          <t>相关性 (科学研究)</t>
         </is>
       </c>
       <c r="E333" s="1" t="inlineStr">
@@ -10443,13 +10443,13 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>Causation (Science &amp; Research)</t>
+          <t>因果关系 (科学研究)</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr"/>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t>Causation (Science &amp; Research)</t>
+          <t>因果关系 (科学研究)</t>
         </is>
       </c>
       <c r="E334" s="1" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimjuɭɭe̞iɕʰʌ̹n]] Simulation (Science &amp; Research)</t>
+          <t>[[ɕʰimjuɭɭe̞iɕʰʌ̹n]] 模拟 (科学研究)</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimjuɭɭe̞iɕʰʌ̹n]] Simulation (Science &amp; Research)</t>
+          <t>[[ɕʰimjuɭɭe̞iɕʰʌ̹n]] 模拟 (科学研究)</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕid͡ʑinɦa̠k̚]] Seismology (Science &amp; Research)</t>
+          <t>[[t͡ɕid͡ʑinɦa̠k̚]] 地震学 (科学研究)</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕid͡ʑinɦa̠k̚]] Seismology (Science &amp; Research)</t>
+          <t>[[t͡ɕid͡ʑinɦa̠k̚]] 地震学 (科学研究)</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)sʰa̠nɦa̠k̚]] Volcanology (Science &amp; Research)</t>
+          <t>[[ˈɸwa̠(ː)sʰa̠nɦa̠k̚]] 火山学 (科学研究)</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)sʰa̠nɦa̠k̚]] Volcanology (Science &amp; Research)</t>
+          <t>[[ˈɸwa̠(ː)sʰa̠nɦa̠k̚]] 火山学 (科学研究)</t>
         </is>
       </c>
       <c r="E337" s="1" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)sʰɛŋmuɾɦa̠k̚]] Paleontology (Science &amp; Research)</t>
+          <t>[[ˈko̞(ː)sʰɛŋmuɾɦa̠k̚]] 古生物 (科学研究)</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)sʰɛŋmuɾɦa̠k̚]] Paleontology (Science &amp; Research)</t>
+          <t>[[ˈko̞(ː)sʰɛŋmuɾɦa̠k̚]] 古生物 (科学研究)</t>
         </is>
       </c>
       <c r="E338" s="1" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpɘ(ː)bɰiɦa̠k̚]] Forensic Science (Science &amp; Research)</t>
+          <t>[[ˈpɘ(ː)bɰiɦa̠k̚]] 法医学 (科学研究)</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="D339" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpɘ(ː)bɰiɦa̠k̚]] Forensic Science (Science &amp; Research)</t>
+          <t>[[ˈpɘ(ː)bɰiɦa̠k̚]] 法医学 (科学研究)</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
@@ -10631,13 +10631,13 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>毒理學 (科學與研究)</t>
+          <t>毒理学 (科学与研究)</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr"/>
       <c r="D340" s="1" t="inlineStr">
         <is>
-          <t>毒理學 (科學與研究)</t>
+          <t>毒理学 (科学与研究)</t>
         </is>
       </c>
       <c r="E340" s="1" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹kʰa̠k̚]] 流行病學 (科學與研究)</t>
+          <t>[[jʌ̹kʰa̠k̚]] 流行病学 (科学与研究)</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹kʰa̠k̚]] 流行病學 (科學與研究)</t>
+          <t>[[jʌ̹kʰa̠k̚]] 流行病学 (科学与研究)</t>
         </is>
       </c>
       <c r="E341" s="1" t="inlineStr">
@@ -10691,13 +10691,13 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>材料科學 (科學與研究)</t>
+          <t>材料科学 (科学与研究)</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr"/>
       <c r="D342" s="1" t="inlineStr">
         <is>
-          <t>材料科學 (科學與研究)</t>
+          <t>材料科学 (科学与研究)</t>
         </is>
       </c>
       <c r="E342" s="1" t="inlineStr">
@@ -10719,13 +10719,13 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>知情同意 (科學與研究)</t>
+          <t>知情同意 (科学与研究)</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr"/>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t>知情同意 (科學與研究)</t>
+          <t>知情同意 (科学与研究)</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>[[po̞ŋni]] 複利 (金融與銀行)</t>
+          <t>[[po̞ŋni]] 复利 (金融与银行)</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t>[[po̞ŋni]] 複利 (金融與銀行)</t>
+          <t>[[po̞ŋni]] 复利 (金融与银行)</t>
         </is>
       </c>
       <c r="E344" s="1" t="inlineStr">
@@ -10779,13 +10779,13 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>淨資產 (金融與銀行)</t>
+          <t>净资产 (金融与银行)</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr"/>
       <c r="D345" s="1" t="inlineStr">
         <is>
-          <t>淨資產 (金融與銀行)</t>
+          <t>净资产 (金融与银行)</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
@@ -10807,13 +10807,13 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>建築規範 (建築)</t>
+          <t>建筑规范 (建筑)</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr"/>
       <c r="D346" s="1" t="inlineStr">
         <is>
-          <t>建築規範 (建築)</t>
+          <t>建筑规范 (建筑)</t>
         </is>
       </c>
       <c r="E346" s="1" t="inlineStr">
@@ -10835,13 +10835,13 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>儲蓄率 (金融與銀行)</t>
+          <t>储蓄率 (金融与银行)</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr"/>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t>儲蓄率 (金融與銀行)</t>
+          <t>储蓄率 (金融与银行)</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[[tɛdɯɭbo̞]] 木樑 (建築)</t>
+          <t>[[tɛdɯɭbo̞]] 木梁 (建筑)</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>[[tɛdɯɭbo̞]] 木樑 (建築)</t>
+          <t>[[tɛdɯɭbo̞]] 木梁 (建筑)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -10895,13 +10895,13 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>懸臂 (建築)</t>
+          <t>悬臂 (建筑)</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr"/>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t>懸臂 (建築)</t>
+          <t>悬臂 (建筑)</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
@@ -10923,13 +10923,13 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>女兒牆 (建築)</t>
+          <t>女儿墙 (建筑)</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr"/>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t>女兒牆 (建築)</t>
+          <t>女儿墙 (建筑)</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
@@ -10951,13 +10951,13 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>高窗 (建築)</t>
+          <t>高窗 (建筑)</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr"/>
       <c r="D351" s="1" t="inlineStr">
         <is>
-          <t>高窗 (建築)</t>
+          <t>高窗 (建筑)</t>
         </is>
       </c>
       <c r="E351" s="1" t="inlineStr">
@@ -10979,13 +10979,13 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>厚塗法 (藝術與設計)</t>
+          <t>厚涂法 (艺术与设计)</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr"/>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t>厚塗法 (藝術與設計)</t>
+          <t>厚涂法 (艺术与设计)</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɘ(ː)mɲʌ̹ɭ]] 審查 (媒體與新聞)</t>
+          <t>[[ˈkɘ(ː)mɲʌ̹ɭ]] 审查 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɘ(ː)mɲʌ̹ɭ]] 審查 (媒體與新聞)</t>
+          <t>[[ˈkɘ(ː)mɲʌ̹ɭ]] 审查 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E353" s="1" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ɲd͡ʑʌ̹n]] 宣傳 (媒體與新聞)</t>
+          <t>[[sʰʌ̹ɲd͡ʑʌ̹n]] 宣传 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ɲd͡ʑʌ̹n]] 宣傳 (媒體與新聞)</t>
+          <t>[[sʰʌ̹ɲd͡ʑʌ̹n]] 宣传 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E354" s="1" t="inlineStr">
@@ -11071,13 +11071,13 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>評論文章 (媒體與新聞)</t>
+          <t>评论文章 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr"/>
       <c r="D355" s="1" t="inlineStr">
         <is>
-          <t>評論文章 (媒體與新聞)</t>
+          <t>评论文章 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
@@ -11099,13 +11099,13 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>新聞攝影 (媒體與新聞)</t>
+          <t>新闻摄影 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr"/>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t>新聞攝影 (媒體與新聞)</t>
+          <t>新闻摄影 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E356" s="1" t="inlineStr">
@@ -11127,13 +11127,13 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>評論員 (媒體與新聞)</t>
+          <t>评论员 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr"/>
       <c r="D357" s="1" t="inlineStr">
         <is>
-          <t>評論員 (媒體與新聞)</t>
+          <t>评论员 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E357" s="1" t="inlineStr">
@@ -11155,13 +11155,13 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>煽情主義 (媒體與新聞學)</t>
+          <t>煽情主义 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr"/>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t>煽情主義 (媒體與新聞學)</t>
+          <t>煽情主义 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E358" s="1" t="inlineStr">
@@ -11183,13 +11183,13 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>深度偽造 (媒體與新聞學)</t>
+          <t>深度伪造 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr"/>
       <c r="D359" s="1" t="inlineStr">
         <is>
-          <t>深度偽造 (媒體與新聞學)</t>
+          <t>深度伪造 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E359" s="1" t="inlineStr">
@@ -11211,13 +11211,13 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>Media Law (媒體與新聞學)</t>
+          <t>媒体法 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr"/>
       <c r="D360" s="1" t="inlineStr">
         <is>
-          <t>Media Law (媒體與新聞學)</t>
+          <t>媒体法 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E360" s="1" t="inlineStr">
@@ -11239,13 +11239,13 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>Broadcast Rights (媒體與新聞學)</t>
+          <t>广播权限 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr"/>
       <c r="D361" s="1" t="inlineStr">
         <is>
-          <t>Broadcast Rights (媒體與新聞學)</t>
+          <t>广播权限 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="E361" s="1" t="inlineStr">
@@ -11267,13 +11267,13 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>編輯委員會 (媒體與新聞業)</t>
+          <t>编辑委员会 (媒体与新闻业)</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr"/>
       <c r="D362" s="1" t="inlineStr">
         <is>
-          <t>編輯委員會 (媒體與新聞業)</t>
+          <t>编辑委员会 (媒体与新闻业)</t>
         </is>
       </c>
       <c r="E362" s="1" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>[[jukʰwe̞]] 生拌牛肉 (韓國美食與餐飲)</t>
+          <t>[[jukʰwe̞]] 生拌牛肉 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="D363" s="1" t="inlineStr">
         <is>
-          <t>[[jukʰwe̞]] 生拌牛肉 (韓國美食與餐飲)</t>
+          <t>[[jukʰwe̞]] 生拌牛肉 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E363" s="1" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>[[kud͡ʑʌ̹ɭpʰa̠n]] 九節板 (韓國美食與餐飲)</t>
+          <t>[[kud͡ʑʌ̹ɭpʰa̠n]] 九节板 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>[[kud͡ʑʌ̹ɭpʰa̠n]] 九節板 (韓國美食與餐飲)</t>
+          <t>[[kud͡ʑʌ̹ɭpʰa̠n]] 九节板 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ɲd͡ʑʌ̹ŋɕʰik̚]] 韓定食 (韓國美食與餐飲)</t>
+          <t>[[ˈha̠(ː)ɲd͡ʑʌ̹ŋɕʰik̚]] 韩定食 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ɲd͡ʑʌ̹ŋɕʰik̚]] 韓定食 (韓國美食與餐飲)</t>
+          <t>[[ˈha̠(ː)ɲd͡ʑʌ̹ŋɕʰik̚]] 韩定食 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠kɕ͈ik̚]] 藥飯 (韓國美食與餐飲)</t>
+          <t>[[ja̠kɕ͈ik̚]] 药饭 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠kɕ͈ik̚]] 藥飯 (韓國美食與餐飲)</t>
+          <t>[[ja̠kɕ͈ik̚]] 药饭 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E366" s="1" t="inlineStr">
@@ -11423,13 +11423,13 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>年糕排 (Tteok Galbi) (韓國飲食)</t>
+          <t>年糕排 (Tteok Galbi) (韩国饮食)</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr"/>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t>年糕排 (Tteok Galbi) (韓國飲食)</t>
+          <t>年糕排 (Tteok Galbi) (韩国饮食)</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛud͡ʑʌ̹t̚]] 蝦醬 (Saeujeot) (韓國飲食)</t>
+          <t>[[sʰɛud͡ʑʌ̹t̚]] 虾酱 (Saeujeot) (韩国饮食)</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛud͡ʑʌ̹t̚]] 蝦醬 (Saeujeot) (韓國飲食)</t>
+          <t>[[sʰɛud͡ʑʌ̹t̚]] 虾酱 (Saeujeot) (韩国饮食)</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹k̚]] Jeok (韓國飲食文化)</t>
+          <t>[[t͡ɕʌ̹k̚]] Jeok (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹k̚]] Jeok (韓國飲食文化)</t>
+          <t>[[t͡ɕʌ̹k̚]] Jeok (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韓國飲食文化)</t>
+          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韓國飲食文化)</t>
+          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E370" s="1" t="inlineStr">
@@ -11547,13 +11547,13 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>Nakji Bokkeum (韓國飲食文化)</t>
+          <t>Nakji Bokkeum (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr"/>
       <c r="D371" s="1" t="inlineStr">
         <is>
-          <t>Nakji Bokkeum (韓國飲食文化)</t>
+          <t>Nakji Bokkeum (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E371" s="1" t="inlineStr">
@@ -11575,13 +11575,13 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Fish Mandu (韓國飲食文化)</t>
+          <t>Fish Mandu (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr"/>
       <c r="D372" s="1" t="inlineStr">
         <is>
-          <t>Fish Mandu (韓國飲食文化)</t>
+          <t>Fish Mandu (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E372" s="1" t="inlineStr">
@@ -11603,13 +11603,13 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>Toranguk (韓國飲食文化)</t>
+          <t>Toranguk (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr"/>
       <c r="D373" s="1" t="inlineStr">
         <is>
-          <t>Toranguk (韓國飲食文化)</t>
+          <t>Toranguk (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E373" s="1" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲuk̚]] 肉片 (韓國飲食文化)</t>
+          <t>[[pʰjʌ̹ɲuk̚]] 肉片 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="D374" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲuk̚]] 肉片 (韓國飲食文化)</t>
+          <t>[[pʰjʌ̹ɲuk̚]] 肉片 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E374" s="1" t="inlineStr">
@@ -11663,13 +11663,13 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>牛尾湯 (韓國飲食文化)</t>
+          <t>牛尾汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr"/>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t>牛尾湯 (韓國飲食文化)</t>
+          <t>牛尾汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E375" s="1" t="inlineStr">
@@ -11691,13 +11691,13 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>烤山藥根 (韓國飲食文化)</t>
+          <t>烤山药根 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr"/>
       <c r="D376" s="1" t="inlineStr">
         <is>
-          <t>烤山藥根 (韓國飲食文化)</t>
+          <t>烤山药根 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E376" s="1" t="inlineStr">
@@ -11719,13 +11719,13 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>清湯 (韓國飲食文化)</t>
+          <t>清汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr"/>
       <c r="D377" s="1" t="inlineStr">
         <is>
-          <t>清湯 (韓國飲食文化)</t>
+          <t>清汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E377" s="1" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ʝʌ̹nbjʌ̹ŋ]] Schizophrenia (心理健康與保健)</t>
+          <t>[[t͡ɕo̞ʝʌ̹nbjʌ̹ŋ]] 精神分裂症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="D378" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ʝʌ̹nbjʌ̹ŋ]] Schizophrenia (心理健康與保健)</t>
+          <t>[[t͡ɕo̞ʝʌ̹nbjʌ̹ŋ]] 精神分裂症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E378" s="1" t="inlineStr">
@@ -11779,13 +11779,13 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>Cognitive Behavioral Therapy (心理健康與保健)</t>
+          <t>认知行为疗法 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr"/>
       <c r="D379" s="1" t="inlineStr">
         <is>
-          <t>Cognitive Behavioral Therapy (心理健康與保健)</t>
+          <t>认知行为疗法 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E379" s="1" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ɡiɛ]] Narcissism (心理健康與保健)</t>
+          <t>[[t͡ɕa̠ɡiɛ]] 自恋 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="D380" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ɡiɛ]] Narcissism (心理健康與保健)</t>
+          <t>[[t͡ɕa̠ɡiɛ]] 自恋 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɛ(ː)ɾi]] 分離 (心理健康與保健)</t>
+          <t>[[ˈhɛ(ː)ɾi]] 分离 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɛ(ː)ɾi]] 分離 (心理健康與保健)</t>
+          <t>[[ˈhɛ(ː)ɾi]] 分离 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E381" s="1" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠pʰje̞t͡ɕ͈ɯŋ]] 自閉症 (心理健康與保健)</t>
+          <t>[[t͡ɕa̠pʰje̞t͡ɕ͈ɯŋ]] 自闭症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠pʰje̞t͡ɕ͈ɯŋ]] 自閉症 (心理健康與保健)</t>
+          <t>[[t͡ɕa̠pʰje̞t͡ɕ͈ɯŋ]] 自闭症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E382" s="1" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲd͡ʑip̚t͡ɕ͈ɯŋ]] 偏執 (心理健康與保健)</t>
+          <t>[[pʰjʌ̹ɲd͡ʑip̚t͡ɕ͈ɯŋ]] 偏执 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="D383" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲd͡ʑip̚t͡ɕ͈ɯŋ]] 偏執 (心理健康與保健)</t>
+          <t>[[pʰjʌ̹ɲd͡ʑip̚t͡ɕ͈ɯŋ]] 偏执 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E383" s="1" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠sʰɯɾa̠itʰiŋ]] 煤氣燈效應 (心理健康與保健)</t>
+          <t>[[ka̠sʰɯɾa̠itʰiŋ]] 煤气灯效应 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="D384" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠sʰɯɾa̠itʰiŋ]] 煤氣燈效應 (心理健康與保健)</t>
+          <t>[[ka̠sʰɯɾa̠itʰiŋ]] 煤气灯效应 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E384" s="1" t="inlineStr">
@@ -11967,13 +11967,13 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>共依存 (心理健康與保健)</t>
+          <t>共依存 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr"/>
       <c r="D385" s="1" t="inlineStr">
         <is>
-          <t>共依存 (心理健康與保健)</t>
+          <t>共依存 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E385" s="1" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞ɾip̚]] 心流狀態 (心理健康與保健)</t>
+          <t>[[mo̞ɾip̚]] 心流状态 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞ɾip̚]] 心流狀態 (心理健康與保健)</t>
+          <t>[[mo̞ɾip̚]] 心流状态 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E386" s="1" t="inlineStr">
@@ -12027,13 +12027,13 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>生物回饋 (心理健康與養生)</t>
+          <t>生物回馈 (心理健康与养生)</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr"/>
       <c r="D387" s="1" t="inlineStr">
         <is>
-          <t>生物回饋 (心理健康與養生)</t>
+          <t>生物回馈 (心理健康与养生)</t>
         </is>
       </c>
       <c r="E387" s="1" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɥi(ː)ja̠ks͈ʌ̹ŋ]] 脆弱性 (心理健康與養生)</t>
+          <t>[[ˈt͡ɕʰɥi(ː)ja̠ks͈ʌ̹ŋ]] 脆弱性 (心理健康与养生)</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɥi(ː)ja̠ks͈ʌ̹ŋ]] 脆弱性 (心理健康與養生)</t>
+          <t>[[ˈt͡ɕʰɥi(ː)ja̠ks͈ʌ̹ŋ]] 脆弱性 (心理健康与养生)</t>
         </is>
       </c>
       <c r="E388" s="1" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)ɡje̞ɡwa̠n]] 世界觀 (韓國流行文化)</t>
+          <t>[[ˈsʰe̞(ː)ɡje̞ɡwa̠n]] 世界观 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)ɡje̞ɡwa̠n]] 世界觀 (韓國流行文化)</t>
+          <t>[[ˈsʰe̞(ː)ɡje̞ɡwa̠n]] 世界观 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -12119,13 +12119,13 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>續約/合約 (韓國流行文化)</t>
+          <t>续约/合约 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr"/>
       <c r="D390" s="1" t="inlineStr">
         <is>
-          <t>續約/合約 (韓國流行文化)</t>
+          <t>续约/合约 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E390" s="1" t="inlineStr">
@@ -12147,13 +12147,13 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>HYBE (韓國流行文化)</t>
+          <t>HYBE (韩国流行文化)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr"/>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t>HYBE (韓國流行文化)</t>
+          <t>HYBE (韩国流行文化)</t>
         </is>
       </c>
       <c r="E391" s="1" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)dɛ]] 世代 (韓國流行文化)</t>
+          <t>[[ˈsʰe̞(ː)dɛ]] 世代 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)dɛ]] 世代 (韓國流行文化)</t>
+          <t>[[ˈsʰe̞(ː)dɛ]] 世代 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E392" s="1" t="inlineStr">
@@ -12207,13 +12207,13 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>動物權利 (寵物護理與動物)</t>
+          <t>动物权利 (宠物护理与动物)</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr"/>
       <c r="D393" s="1" t="inlineStr">
         <is>
-          <t>動物權利 (寵物護理與動物)</t>
+          <t>动物权利 (宠物护理与动物)</t>
         </is>
       </c>
       <c r="E393" s="1" t="inlineStr">
@@ -12235,13 +12235,13 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>All-Kill (韓國流行文化)</t>
+          <t>一网打尽 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr"/>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t>All-Kill (韓國流行文化)</t>
+          <t>一网打尽 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E394" s="1" t="inlineStr">
@@ -12263,13 +12263,13 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>刷榜派對 (韓國流行文化)</t>
+          <t>刷榜派对 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr"/>
       <c r="D395" s="1" t="inlineStr">
         <is>
-          <t>刷榜派對 (韓國流行文化)</t>
+          <t>刷榜派对 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E395" s="1" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɭɭa̠ks͈a̠]] 寵物安樂死 (寵物照護與動物)</t>
+          <t>[[a̠ɭɭa̠ks͈a̠]] 宠物安乐死 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="D396" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɭɭa̠ks͈a̠]] 寵物安樂死 (寵物照護與動物)</t>
+          <t>[[a̠ɭɭa̠ks͈a̠]] 宠物安乐死 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="E396" s="1" t="inlineStr">
@@ -12323,13 +12323,13 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>速通 (遊戲與電競)</t>
+          <t>速通 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr"/>
       <c r="D397" s="1" t="inlineStr">
         <is>
-          <t>速通 (遊戲與電競)</t>
+          <t>速通 (游戏与电竞)</t>
         </is>
       </c>
       <c r="E397" s="1" t="inlineStr">
@@ -12351,13 +12351,13 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>觀戰者（旁觀工具） (遊戲與電競)</t>
+          <t>观战者（旁观工具） (游戏与电竞)</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr"/>
       <c r="D398" s="1" t="inlineStr">
         <is>
-          <t>觀戰者（旁觀工具） (遊戲與電競)</t>
+          <t>观战者（旁观工具） (游戏与电竞)</t>
         </is>
       </c>
       <c r="E398" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK3.xlsx
+++ b/languages/ko/output/import/韩语TOPIK3.xlsx
@@ -445,7 +445,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>[[ˈki(ː)sʰɛŋ]] 妓生 (文化)</t>
+          <t>妓生 (文化)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ns͈o̞ɾi]] 盘索里 (文化)</t>
+          <t>盘索里 (文化)</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠muɭɭo̞ɾi]] 四物农乐 (文化)</t>
+          <t>四物农乐 (文化)</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋ]] 情（深厚的情感连结） (文化)</t>
+          <t>情（深厚的情感连结） (文化)</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>[[nuɲt͡ɕʰi]] 眼色（社交意识） (文化)</t>
+          <t>眼色（社交意识） (文化)</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[[kuɡa̠k̚]] 传统音乐 (文化)</t>
+          <t>传统音乐 (文化)</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -627,10 +627,14 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>课程大纲 (教育)</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr"/>
+          <t>[kychwkkwkot] 课程大纲 (教育)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>kychwkkwkot</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>课程大纲 (教育)</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>[[no̞nmun]] 论文 (教育)</t>
+          <t>论文 (教育)</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
@@ -687,10 +691,14 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>学位论文 (教育)</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr"/>
+          <t>[akchenunmin] 学位论文 (教育)</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>akchenunmin</t>
+        </is>
+      </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
           <t>学位论文 (教育)</t>
@@ -725,7 +733,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[[sʰunɯŋ]] 大学修业能力测验 (教育)</t>
+          <t>大学修业能力测验 (教育)</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -757,7 +765,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ks͈ɛŋβwe̞]] 学生会 (教育)</t>
+          <t>学生会 (教育)</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -779,10 +787,14 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>充满希望 (情感)</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr"/>
+          <t>[ymatpata] 充满希望 (情感)</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>ymatpata</t>
+        </is>
+      </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
           <t>充满希望 (情感)</t>
@@ -807,10 +819,14 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>狂喜 (情绪)</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr"/>
+          <t>[wtumata] 狂喜 (情绪)</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>wtumata</t>
+        </is>
+      </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
           <t>狂喜 (情绪)</t>
@@ -845,7 +861,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwɘ(ː)nma̠ŋɦa̠da̠]] 怨恨 (情绪)</t>
+          <t>怨恨 (情绪)</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -877,7 +893,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[[muɡwa̠nɕʰimɦa̠da̠]] 冷漠 (情绪)</t>
+          <t>冷漠 (情绪)</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -909,7 +925,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋɦʌ̹ɦa̠da̠]] 空虚 (情绪)</t>
+          <t>空虚 (情绪)</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -931,10 +947,14 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>渴望 (情绪)</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr"/>
+          <t>[kankomata] 渴望 (情绪)</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>kankomata</t>
+        </is>
+      </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
           <t>渴望 (情绪)</t>
@@ -959,10 +979,14 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>兴高采烈 (情绪)</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr"/>
+          <t>[chykichyatchyatata] 兴高采烈 (情绪)</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>chykichyatchyatata</t>
+        </is>
+      </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
           <t>兴高采烈 (情绪)</t>
@@ -997,7 +1021,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>[[muŋkxɯɾɦa̠da̠]] 移动 (情感)</t>
+          <t>移动 (情感)</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1019,10 +1043,14 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>愤怒 (情感)</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr"/>
+          <t>[pinnuata] 愤怒 (情感)</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>pinnuata</t>
+        </is>
+      </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
           <t>愤怒 (情感)</t>
@@ -1047,10 +1075,14 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>激怒 (情感)</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr"/>
+          <t>[kyokpinata] 激怒 (情感)</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>kyokpinata</t>
+        </is>
+      </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
           <t>激怒 (情感)</t>
@@ -1085,7 +1117,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] 恐惧 (情感)</t>
+          <t>恐惧 (情感)</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1107,10 +1139,14 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>决心 (情感)</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr"/>
+          <t>[kyomchyonata] 决心 (情感)</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>kyomchyonata</t>
+        </is>
+      </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
           <t>决心 (情感)</t>
@@ -1145,7 +1181,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] 组成 (情感)</t>
+          <t>组成 (情感)</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1167,10 +1203,14 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>痛快乐 (情感)</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr"/>
+          <t>[tamhungcengcemata] 痛快乐 (情感)</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>tamhungcengcemata</t>
+        </is>
+      </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
           <t>痛快乐 (情感)</t>
@@ -1205,7 +1245,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾjʌ̹nɦa̠da̠]] 渴望的 (情感)</t>
+          <t>渴望的 (情感)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1237,7 +1277,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɭma̠ŋɦa̠da̠]] 渴望&amp;#x0D; (情感)</t>
+          <t>渴望&amp;#x0D; (情感)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -1259,10 +1299,14 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>憎恨 (情绪)</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr"/>
+          <t>[ketchuata] 憎恨 (情绪)</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>ketchuata</t>
+        </is>
+      </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
           <t>憎恨 (情绪)</t>
@@ -1297,7 +1341,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (文化)</t>
+          <t>Sasaeng (文化)</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -1319,10 +1363,14 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>整形手术 (文化)</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr"/>
+          <t>[ngotyotngingim] 整形手术 (文化)</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>ngotyotngingim</t>
+        </is>
+      </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
           <t>整形手术 (文化)</t>
@@ -1357,7 +1405,7 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛbʌ̹ɭ]] 财阀 (文化)</t>
+          <t>财阀 (文化)</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1379,10 +1427,14 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>麻木 (情绪)</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr"/>
+          <t>[mikangkakan] 麻木 (情绪)</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>mikangkakan</t>
+        </is>
+      </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
           <t>麻木 (情绪)</t>
@@ -1417,7 +1469,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] 花生酱 (食物)</t>
+          <t>花生酱 (食物)</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1449,7 +1501,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>[[isʰɯɭbi]] 毛毛雨 (自然)</t>
+          <t>毛毛雨 (自然)</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1481,7 +1533,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ɭbu]] 分期付款 (购物)</t>
+          <t>分期付款 (购物)</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1513,7 +1565,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)ʎt͡ɕʰum]] 假面舞 (文化)</t>
+          <t>假面舞 (文化)</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
@@ -1545,7 +1597,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (文化)</t>
+          <t>跆拳 (文化)</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1567,10 +1619,14 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>芦苇田 (自然)</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr"/>
+          <t>[kamtepa] 芦苇田 (自然)</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>kamtepa</t>
+        </is>
+      </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
           <t>芦苇田 (自然)</t>
@@ -1595,10 +1651,14 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>韩纸 (文化)</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr"/>
+          <t>[anki] 韩纸 (文化)</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>anki</t>
+        </is>
+      </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
           <t>韩纸 (文化)</t>
@@ -1633,7 +1693,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹nmua̠m]] 熔岩石 (自然)</t>
+          <t>熔岩石 (自然)</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1665,7 +1725,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>[[piŋɦa̠]] 冰川 (自然)</t>
+          <t>冰川 (自然)</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1697,7 +1757,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠nsʰe̞]] 关税 (购物)</t>
+          <t>关税 (购物)</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1729,7 +1789,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠da̠kʰo̞k͈iɾi]] 海象 (动物)</t>
+          <t>海象 (动物)</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1761,7 +1821,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞p͈uɭs͈o̞]] 犀牛 (动物)</t>
+          <t>犀牛 (动物)</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
@@ -1793,7 +1853,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ma̠]] 河马 (动物)</t>
+          <t>河马 (动物)</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -1825,7 +1885,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛɡjuʌ̹]] 美洲豹 (动物)</t>
+          <t>美洲豹 (动物)</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1857,7 +1917,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠ie̞na̠]] 鬣狗 (动物)</t>
+          <t>鬣狗 (动物)</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1889,7 +1949,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>[[miʌ̹kʰɛt̚]] 狐獴 (动物)</t>
+          <t>狐獴 (动物)</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1921,7 +1981,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾɯma̠diɭɭo̞]] 犰狳 (动物)</t>
+          <t>犰狳 (动物)</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -1953,7 +2013,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>[[ˈo̞(ː)ɾinʌ̹ɡuɾi]] 鸭嘴兽 (动物)</t>
+          <t>鸭嘴兽 (动物)</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -1975,10 +2035,14 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>飞鼠 (动物)</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr"/>
+          <t>[namtarangke] 飞鼠 (动物)</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>namtarangke</t>
+        </is>
+      </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
           <t>飞鼠 (动物)</t>
@@ -2013,7 +2077,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)ŋsʰɛ]] 鹳 (动物)</t>
+          <t>鹳 (动物)</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
@@ -2045,7 +2109,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋɡo̞ŋ]] 瞳孔 (身体部位)</t>
+          <t>瞳孔 (身体部位)</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
@@ -2077,7 +2141,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹ŋmɛk̚]] 静脉 (身体部位)</t>
+          <t>静脉 (身体部位)</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2109,7 +2173,7 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰinɡjʌ̹ŋ]] 神经 (身体部位)</t>
+          <t>神经 (身体部位)</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
@@ -2141,7 +2205,7 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>[[çimt͡ɕ͈uɭ]] 肌腱 (身体部位)</t>
+          <t>肌腱 (身体部位)</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2173,7 +2237,7 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɭɡjʌ̹k̚]] 骨架 (身体部位)</t>
+          <t>骨架 (身体部位)</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -2205,7 +2269,7 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ma̠k̚]] 耳膜 (身体部位)</t>
+          <t>耳膜 (身体部位)</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -2237,7 +2301,7 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕi(ː)nβo̞ŋsʰɛk̚]] 深红色 (颜色与形状)</t>
+          <t>深红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -2259,10 +2323,14 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>绯红色 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr"/>
+          <t>[kiutngek] 绯红色 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>kiutngek</t>
+        </is>
+      </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
           <t>绯红色 (颜色与形状)</t>
@@ -2287,10 +2355,14 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>翠绿色 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr"/>
+          <t>[chemeramtengek] 翠绿色 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>chemeramtengek</t>
+        </is>
+      </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
           <t>翠绿色 (颜色与形状)</t>
@@ -2315,10 +2387,14 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>钴蓝色 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr"/>
+          <t>[hupamengek] 钴蓝色 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>hupamengek</t>
+        </is>
+      </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
           <t>钴蓝色 (颜色与形状)</t>
@@ -2343,10 +2419,14 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>琥珀色 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr"/>
+          <t>[upakngek] 琥珀色 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>upakngek</t>
+        </is>
+      </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
           <t>琥珀色 (颜色与形状)</t>
@@ -2371,10 +2451,14 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>炭灰色 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr"/>
+          <t>[ngitngek] 炭灰色 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>ngitngek</t>
+        </is>
+      </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
           <t>炭灰色 (颜色与形状)</t>
@@ -2399,10 +2483,14 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>垂直线 (颜色与形状)</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr"/>
+          <t>[ngikikngon] 垂直线 (颜色与形状)</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>ngikikngon</t>
+        </is>
+      </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
           <t>垂直线 (颜色与形状)</t>
@@ -2427,10 +2515,14 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>欺凌 (校园生活)</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr"/>
+          <t>[tatumring] 欺凌 (校园生活)</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>tatumring</t>
+        </is>
+      </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
           <t>欺凌 (校园生活)</t>
@@ -2465,7 +2557,7 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>[[tʰo̞ne̞ido̞]] 龙卷风 (天气)</t>
+          <t>龙卷风 (天气)</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -2497,7 +2589,7 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹ɾikʰe̞in]] 飓风 (天气)</t>
+          <t>飓风 (天气)</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2529,7 +2621,7 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞nsʰun]] 季风 (天气)</t>
+          <t>季风 (天气)</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2551,10 +2643,14 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>气压 (天气)</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr"/>
+          <t>[kichang] 气压 (天气)</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>kichang</t>
+        </is>
+      </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
           <t>气压 (天气)</t>
@@ -2579,10 +2675,14 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>可见性 (天气)</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr"/>
+          <t>[ngikot] 可见性 (天气)</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>ngikot</t>
+        </is>
+      </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
           <t>可见性 (天气)</t>
@@ -2607,10 +2707,14 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>露点 (天气)</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr"/>
+          <t>[chingemkong] 露点 (天气)</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>chingemkong</t>
+        </is>
+      </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
           <t>露点 (天气)</t>
@@ -2645,7 +2749,7 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ŋsʰa̠ŋ]] 冻伤 (天气)</t>
+          <t>冻伤 (天气)</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -2667,10 +2771,14 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>降雪量 (天气)</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr"/>
+          <t>[katngomryat] 降雪量 (天气)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>katngomryat</t>
+        </is>
+      </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
           <t>降雪量 (天气)</t>
@@ -2695,10 +2803,14 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>口袋巾 (服饰)</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr"/>
+          <t>[uhetngehecho] 口袋巾 (服饰)</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>uhetngehecho</t>
+        </is>
+      </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
           <t>口袋巾 (服饰)</t>
@@ -2723,10 +2835,14 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>袖扣 (服饰)</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr"/>
+          <t>[hoerithe] 袖扣 (服饰)</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>hoerithe</t>
+        </is>
+      </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
           <t>袖扣 (服饰)</t>
@@ -2751,10 +2867,14 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>压力服 (服饰)</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr"/>
+          <t>[changpikpuk] 压力服 (服饰)</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>changpikpuk</t>
+        </is>
+      </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
           <t>压力服 (服饰)</t>
@@ -2789,7 +2909,7 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>[[ma̠k̚t͡ɕ͈a̠ŋ]] 狗血剧 (韩剧用语)</t>
+          <t>狗血剧 (韩剧用语)</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2821,7 +2941,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] 鼬属 (动物)</t>
+          <t>鼬属 (动物)</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -2853,7 +2973,7 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰibʌ̹k̚]] 十亿 (数字与时间)</t>
+          <t>十亿 (数字与时间)</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -2875,10 +2995,14 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>年度 (数字与时间)</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr"/>
+          <t>[wikyechyontu] 年度 (数字与时间)</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>wikyechyontu</t>
+        </is>
+      </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
           <t>年度 (数字与时间)</t>
@@ -2903,10 +3027,14 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>春季解冻 (天气)</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr"/>
+          <t>[epit] 春季解冻 (天气)</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>epit</t>
+        </is>
+      </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
           <t>春季解冻 (天气)</t>
@@ -2941,7 +3069,7 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰut͡ɕʰʌ̹nsʰʌ̹]] 推荐信 (校园生活)</t>
+          <t>推荐信 (校园生活)</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -2963,10 +3091,14 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>股票期权 (商业)</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr"/>
+          <t>[ngeukchungngyon] 股票期权 (商业)</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>ngeukchungngyon</t>
+        </is>
+      </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
           <t>股票期权 (商业)</t>
@@ -3001,7 +3133,7 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕibun]] 股权 (商业)</t>
+          <t>股权 (商业)</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -3023,10 +3155,14 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>加值税 (商业)</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr"/>
+          <t>[pikakapinge] 加值税 (商业)</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>pikakapinge</t>
+        </is>
+      </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
           <t>加值税 (商业)</t>
@@ -3061,7 +3197,7 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>[[ˈka̠(ː)msʰa̠]] 审计 (商业)</t>
+          <t>审计 (商业)</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -3083,10 +3219,14 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>资产负债表 (商业)</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr"/>
+          <t>[tepatekuy] 资产负债表 (商业)</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>tepatekuy</t>
+        </is>
+      </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
           <t>资产负债表 (商业)</t>
@@ -3111,10 +3251,14 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>创投 (商业)</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr"/>
+          <t>[penpoheiam] 创投 (商业)</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>penpoheiam</t>
+        </is>
+      </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
           <t>创投 (商业)</t>
@@ -3139,10 +3283,14 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>首次公开发行 (商业)</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr"/>
+          <t>[kichongkutke] 首次公开发行 (商业)</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>kichongkutke</t>
+        </is>
+      </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
           <t>首次公开发行 (商业)</t>
@@ -3177,7 +3325,7 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠p̚p͈jʌ̹ŋ]] 合并 (商业)</t>
+          <t>合并 (商业)</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -3209,7 +3357,7 @@
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>[[insʰu]] 收购 (商业)</t>
+          <t>收购 (商业)</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
@@ -3231,10 +3379,14 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>子公司 (商业)</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr"/>
+          <t>[kawinga] 子公司 (商业)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>kawinga</t>
+        </is>
+      </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
           <t>子公司 (商业)</t>
@@ -3269,7 +3421,7 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕud͡ʑu]] 股东 (商业)</t>
+          <t>股东 (商业)</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3291,10 +3443,14 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>财务长 (商业)</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr"/>
+          <t>[pwikukemipekchingka] 财务长 (商业)</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>pwikukemipekchingka</t>
+        </is>
+      </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
           <t>财务长 (商业)</t>
@@ -3319,10 +3475,14 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>营运长 (商业)</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr"/>
+          <t>[pwikuchinchyotpekchingka] 营运长 (商业)</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>pwikuchinchyotpekchingka</t>
+        </is>
+      </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
           <t>营运长 (商业)</t>
@@ -3347,10 +3507,14 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>发酵 (烹饪)</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr"/>
+          <t>[pamyata] 发酵 (烹饪)</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>pamyata</t>
+        </is>
+      </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
           <t>发酵 (烹饪)</t>
@@ -3375,10 +3539,14 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>治愈 (烹饪)</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="inlineStr"/>
+          <t>[chyongkatata] 治愈 (烹饪)</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>chyongkatata</t>
+        </is>
+      </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
           <t>治愈 (烹饪)</t>
@@ -3403,10 +3571,14 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>烟 (烹饪)</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr"/>
+          <t>[inkeata] 烟 (烹饪)</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>inkeata</t>
+        </is>
+      </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
           <t>烟 (烹饪)</t>
@@ -3431,10 +3603,14 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>利润率 (商业)</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr"/>
+          <t>[ngichikrwm] 利润率 (商业)</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>ngichikrwm</t>
+        </is>
+      </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
           <t>利润率 (商业)</t>
@@ -3459,10 +3635,14 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Supply Chain (商业)</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr"/>
+          <t>[kutkengmat] Supply Chain (商业)</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>kutkengmat</t>
+        </is>
+      </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
           <t>Supply Chain (商业)</t>
@@ -3497,7 +3677,7 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>[[kimd͡ʑa̠ŋ]] 泡菜制作 (烹饪)</t>
+          <t>泡菜制作 (烹饪)</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
@@ -3519,10 +3699,14 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Tangjinjam (俚语)</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr"/>
+          <t>[atkinkeng] Tangjinjam (俚语)</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>atkinkeng</t>
+        </is>
+      </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Tangjinjam (俚语)</t>
@@ -3547,10 +3731,14 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>没有寒意/强烈 (俚语)</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr"/>
+          <t>[kekngotngerongta] 没有寒意/强烈 (俚语)</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>kekngotngerongta</t>
+        </is>
+      </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
           <t>没有寒意/强烈 (俚语)</t>
@@ -3575,10 +3763,14 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>真真 (俚语)</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr"/>
+          <t>[kunna] 真真 (俚语)</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>kunna</t>
+        </is>
+      </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
           <t>真真 (俚语)</t>
@@ -3603,10 +3795,14 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>瞬间赤贫 (俚语)</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr"/>
+          <t>[pyorakkoki] 瞬间赤贫 (俚语)</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>pyorakkoki</t>
+        </is>
+      </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
           <t>瞬间赤贫 (俚语)</t>
@@ -3641,7 +3837,7 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ʎd͡ʑo̞sʰʌ̹n]] 逃离韩国 (俚语)</t>
+          <t>逃离韩国 (俚语)</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3673,7 +3869,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>[[he̞ʎd͡ʑo̞sʰʌ̹n]] 地狱朝鲜 (俚语)</t>
+          <t>地狱朝鲜 (俚语)</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3695,10 +3891,14 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>泥土汤匙 (俚语)</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr"/>
+          <t>[elngiko] 泥土汤匙 (俚语)</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>elngiko</t>
+        </is>
+      </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
           <t>泥土汤匙 (俚语)</t>
@@ -3733,7 +3933,7 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>[[kɯmsʰud͡ʑʌ̹]] 金汤匙 (俚语)</t>
+          <t>金汤匙 (俚语)</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -3755,10 +3955,14 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>努力中毒者 (俚语)</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr"/>
+          <t>[nuryokpit] 努力中毒者 (俚语)</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>nuryokpit</t>
+        </is>
+      </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
           <t>努力中毒者 (俚语)</t>
@@ -3783,10 +3987,14 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>热情薪资 (俚语)</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr"/>
+          <t>[chyomkotechi] 热情薪资 (俚语)</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>chyomkotechi</t>
+        </is>
+      </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
           <t>热情薪资 (俚语)</t>
@@ -3811,10 +4019,14 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>铁人三项 (运动)</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr"/>
+          <t>[erachichengemrun] 铁人三项 (运动)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>erachichengemrun</t>
+        </is>
+      </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
           <t>铁人三项 (运动)</t>
@@ -3849,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ŋdɛno̞pʰit͈ɥiɡi]] 撑竿跳高 (运动)</t>
+          <t>撑竿跳高 (运动)</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -3881,7 +4093,7 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>[[hɛmʌ̹dʌ̹ɲd͡ʑiɡi]] 链球 (运动)</t>
+          <t>链球 (运动)</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -3903,10 +4115,14 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Crossfit (运动)</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr"/>
+          <t>[herungeit] Crossfit (运动)</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>herungeit</t>
+        </is>
+      </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
           <t>Crossfit (运动)</t>
@@ -3931,10 +4147,14 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>区块链 (科技)</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr"/>
+          <t>[pemrukpechin] 区块链 (科技)</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>pemrukpechin</t>
+        </is>
+      </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
           <t>区块链 (科技)</t>
@@ -3969,7 +4189,7 @@
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>[[ˈa̠(ː)mβo̞βwa̠pʰje̞]] 加密货币 (科技)</t>
+          <t>加密货币 (科技)</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
@@ -4001,7 +4221,7 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>[[me̞tʰa̠bʌ̹sʰɯ]] 元宇宙 (科技)</t>
+          <t>元宇宙 (科技)</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
@@ -4023,10 +4243,14 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>虚拟实境 (科技)</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr"/>
+          <t>[kangatyonngim] 虚拟实境 (科技)</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>kangatyonngim</t>
+        </is>
+      </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
           <t>虚拟实境 (科技)</t>
@@ -4051,10 +4275,14 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>扩增实境 (科技)</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr"/>
+          <t>[ketkatyonngim] 扩增实境 (科技)</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>ketkatyonngim</t>
+        </is>
+      </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
           <t>扩增实境 (科技)</t>
@@ -4079,10 +4307,14 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>太空科技 (科技)</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr"/>
+          <t>[chikikingim] 太空科技 (科技)</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>chikikingim</t>
+        </is>
+      </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
           <t>太空科技 (科技)</t>
@@ -4107,10 +4339,14 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>量子计算 (科技)</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr"/>
+          <t>[chyatkahongwit] 量子计算 (科技)</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>chyatkahongwit</t>
+        </is>
+      </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
           <t>量子计算 (科技)</t>
@@ -4135,10 +4371,14 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>再生能源科技 (科技)</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr"/>
+          <t>[kengetchenokikingim] 再生能源科技 (科技)</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>kengetchenokikingim</t>
+        </is>
+      </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
           <t>再生能源科技 (科技)</t>
@@ -4173,7 +4413,7 @@
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰwe̞(ː)d͡ʑik̚k͈ɯm]] 资遣费 (商业)</t>
+          <t>资遣费 (商业)</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -4205,7 +4445,7 @@
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimsʰuɭ]] 针灸 (健康与医疗)</t>
+          <t>针灸 (健康与医疗)</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -4227,10 +4467,14 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>韩医学 (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr"/>
+          <t>[anchyak] 韩医学 (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>anchyak</t>
+        </is>
+      </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
           <t>韩医学 (健康与医疗)</t>
@@ -4255,10 +4499,14 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>MRI (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr"/>
+          <t>[kakikutmyotchyotngat] MRI (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>kakikutmyotchyotngat</t>
+        </is>
+      </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
           <t>MRI (健康与医疗)</t>
@@ -4293,7 +4541,7 @@
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɯ(ː)nɕʰi]] 近视 (健康医疗)</t>
+          <t>近视 (健康医疗)</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -4325,7 +4573,7 @@
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠nbuink͈wa̠]] 产科/妇产科 (健康医疗)</t>
+          <t>产科/妇产科 (健康医疗)</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -4347,10 +4595,14 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>心脏病科 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr"/>
+          <t>[ngingkatnekw] 心脏病科 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>ngingkatnekw</t>
+        </is>
+      </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
           <t>心脏病科 (健康医疗)</t>
@@ -4375,10 +4627,14 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>骨科 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr"/>
+          <t>[kotyotchwikw] 骨科 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>kotyotchwikw</t>
+        </is>
+      </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
           <t>骨科 (健康医疗)</t>
@@ -4403,10 +4659,14 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>神经内科 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr"/>
+          <t>[nginkyotkw] 神经内科 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>nginkyotkw</t>
+        </is>
+      </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
           <t>神经内科 (健康医疗)</t>
@@ -4431,10 +4691,14 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Prowess BMI计算器 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr"/>
+          <t>[pekimryatkingi] Prowess BMI计算器 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>pekimryatkingi</t>
+        </is>
+      </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
           <t>Prowess BMI计算器 (健康医疗)</t>
@@ -4469,7 +4733,7 @@
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>[[a̠(ː)m]] 癌症 (健康医疗)</t>
+          <t>癌症 (健康医疗)</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -4491,10 +4755,14 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>定额手续费 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr"/>
+          <t>[punchinpitangkeng] 定额手续费 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>punchinpitangkeng</t>
+        </is>
+      </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
           <t>定额手续费 (健康医疗)</t>
@@ -4529,7 +4797,7 @@
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>[[nwe̞d͡ʑo̞ʎt͡ɕ͈uŋ]] 中风 (健康与医疗)</t>
+          <t>中风 (健康与医疗)</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -4561,7 +4829,7 @@
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimd͡ʑa̠ŋma̠bi]] 心脏病发作 (健康与医疗)</t>
+          <t>心脏病发作 (健康与医疗)</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
@@ -4583,10 +4851,14 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>肾脏疾病 (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr"/>
+          <t>[nginkatpyot] 肾脏疾病 (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>nginkatpyot</t>
+        </is>
+      </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
           <t>肾脏疾病 (健康与医疗)</t>
@@ -4611,10 +4883,14 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>肝脏疾病 (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr"/>
+          <t>[kankimwn] 肝脏疾病 (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>kankimwn</t>
+        </is>
+      </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
           <t>肝脏疾病 (健康与医疗)</t>
@@ -4639,10 +4915,14 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>胃镜检查 (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr"/>
+          <t>[chenengikyot] 胃镜检查 (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>chenengikyot</t>
+        </is>
+      </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
           <t>胃镜检查 (健康与医疗)</t>
@@ -4667,10 +4947,14 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>结肠镜检查 (健康与医疗)</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr"/>
+          <t>[tekatnengikyot] 结肠镜检查 (健康与医疗)</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>tekatnengikyot</t>
+        </is>
+      </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
           <t>结肠镜检查 (健康与医疗)</t>
@@ -4705,7 +4989,7 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>[[joja̠ŋwʌ̹n]] 疗养院/疗养院 (健康医疗)</t>
+          <t>疗养院/疗养院 (健康医疗)</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -4727,10 +5011,14 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>临终关怀 (健康医疗)</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr"/>
+          <t>[ungeinge] 临终关怀 (健康医疗)</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>ungeinge</t>
+        </is>
+      </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
           <t>临终关怀 (健康医疗)</t>
@@ -4765,7 +5053,7 @@
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕe̞(ː)sʰa̠]] 祭礼；祭祀 (节日庆典)</t>
+          <t>祭礼；祭祀 (节日庆典)</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -4797,7 +5085,7 @@
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰa̠ɾje̞]] 茶礼（节日祭祖仪式） (节日庆典)</t>
+          <t>茶礼（节日祭祖仪式） (节日庆典)</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
@@ -4819,10 +5107,14 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>正月大满月（元宵） (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr"/>
+          <t>[kotchemtepureng] 正月大满月（元宵） (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>kotchemtepureng</t>
+        </is>
+      </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
           <t>正月大满月（元宵） (节日庆典)</t>
@@ -4857,7 +5149,7 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)ɾʌ̹m]] 布拉姆 (节日庆典)</t>
+          <t>布拉姆 (节日庆典)</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -4889,7 +5181,7 @@
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>[[o̞ɡo̞k̚p͈a̠p̚]] 五谷大米 (节日庆典)</t>
+          <t>五谷大米 (节日庆典)</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -4911,10 +5203,14 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>建国纪念日 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr"/>
+          <t>[keponkom] 建国纪念日 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>keponkom</t>
+        </is>
+      </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
           <t>建国纪念日 (节日庆典)</t>
@@ -4939,10 +5235,14 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>莲花灯节 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr"/>
+          <t>[chyontetwi] 莲花灯节 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>chyontetwi</t>
+        </is>
+      </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
           <t>莲花灯节 (节日庆典)</t>
@@ -4967,10 +5267,14 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>达诺节 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr"/>
+          <t>[tanchu] 达诺节 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>tanchu</t>
+        </is>
+      </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
           <t>达诺节 (节日庆典)</t>
@@ -5005,7 +5309,7 @@
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>[[to̞ʎd͡ʑa̠bi]] 抓周（婴儿周岁礼） (节日庆典)</t>
+          <t>抓周（婴儿周岁礼） (节日庆典)</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -5037,7 +5341,7 @@
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)nɡa̠p̚]] 花甲（六十岁寿辰） (节日庆典)</t>
+          <t>花甲（六十岁寿辰） (节日庆典)</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
@@ -5059,10 +5363,14 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>希赫多 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C155" s="1" t="inlineStr"/>
+          <t>[kiketu] 希赫多 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>kiketu</t>
+        </is>
+      </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
           <t>希赫多 (节日庆典)</t>
@@ -5097,7 +5405,7 @@
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>[[ɕ͈iɾɯm]] 韩式摔跤 (节日庆典)</t>
+          <t>韩式摔跤 (节日庆典)</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
@@ -5129,7 +5437,7 @@
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>[[ˈnɘ(ː)ɭt͈ɥiɡi]] 跳板（韩国传统游戏） (节日庆典)</t>
+          <t>跳板（韩国传统游戏） (节日庆典)</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
@@ -5151,10 +5459,14 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Jesa桌子 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C158" s="1" t="inlineStr"/>
+          <t>[kengat] Jesa桌子 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>kengat</t>
+        </is>
+      </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
           <t>Jesa桌子 (节日庆典)</t>
@@ -5179,10 +5491,14 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>农乐（韩国传统打击乐） (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr"/>
+          <t>[itmim] 农乐（韩国传统打击乐） (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>itmim</t>
+        </is>
+      </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
           <t>农乐（韩国传统打击乐） (节日庆典)</t>
@@ -5207,10 +5523,14 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>哀悼金 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr"/>
+          <t>[pichykeng] 哀悼金 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>pichykeng</t>
+        </is>
+      </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
           <t>哀悼金 (节日庆典)</t>
@@ -5245,7 +5565,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (传统婚礼仪式) (节日与庆典)</t>
+          <t>Pyebaek (传统婚礼仪式) (节日与庆典)</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5277,7 +5597,7 @@
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕa̠(ː)ŋɲe̞ɕʰik̚]] 葬礼 (节日与庆典)</t>
+          <t>葬礼 (节日与庆典)</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
@@ -5309,7 +5629,7 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>[[judu]] Yudu（夏日沐浴节） (节日与庆典)</t>
+          <t>Yudu（夏日沐浴节） (节日与庆典)</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -5341,7 +5661,7 @@
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (节日与庆典)</t>
+          <t>祭祀食物 (节日与庆典)</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
@@ -5373,7 +5693,7 @@
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠nɡa̠ɥi]] 丰收之月 (节日与庆典)</t>
+          <t>丰收之月 (节日与庆典)</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -5405,7 +5725,7 @@
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞d͡ʑʌ̹nɡjot͡ɕʰa̠ɾo̞]] 环形交叉路口 (交通)</t>
+          <t>环形交叉路口 (交通)</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -5437,7 +5757,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹nsʰʌ̹k̚]] 路沿 (交通)</t>
+          <t>路沿 (交通)</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5459,10 +5779,14 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>独立运动家 (节庆与活动)</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr"/>
+          <t>[tukringchintutka] 独立运动家 (节庆与活动)</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>tukringchintutka</t>
+        </is>
+      </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
           <t>独立运动家 (节庆与活动)</t>
@@ -5487,10 +5811,14 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>神主牌 (节日庆典)</t>
-        </is>
-      </c>
-      <c r="C169" s="1" t="inlineStr"/>
+          <t>[nginche] 神主牌 (节日庆典)</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>nginche</t>
+        </is>
+      </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
           <t>神主牌 (节日庆典)</t>
@@ -5515,10 +5843,14 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>玻尿酸 (美妆护肤)</t>
-        </is>
-      </c>
-      <c r="C170" s="1" t="inlineStr"/>
+          <t>[ichamrirunngan] 玻尿酸 (美妆护肤)</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>ichamrirunngan</t>
+        </is>
+      </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
           <t>玻尿酸 (美妆护肤)</t>
@@ -5553,7 +5885,7 @@
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>[[ɾe̞tʰino̞ɭ]] 视黄醇 (美妆护肤)</t>
+          <t>视黄醇 (美妆护肤)</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
@@ -5575,10 +5907,14 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>烟酰胺 (美妆护肤)</t>
-        </is>
-      </c>
-      <c r="C172" s="1" t="inlineStr"/>
+          <t>[nachichanginchamachite] 烟酰胺 (美妆护肤)</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>nachichanginchamachite</t>
+        </is>
+      </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
           <t>烟酰胺 (美妆护肤)</t>
@@ -5603,10 +5939,14 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>蜂胶 (美妆护肤)</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr"/>
+          <t>[eruumringe] 蜂胶 (美妆护肤)</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>eruumringe</t>
+        </is>
+      </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
           <t>蜂胶 (美妆护肤)</t>
@@ -5631,10 +5971,14 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>安瓶 (美容与护肤)</t>
-        </is>
-      </c>
-      <c r="C174" s="1" t="inlineStr"/>
+          <t>[chengem] 安瓶 (美容与护肤)</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>chengem</t>
+        </is>
+      </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
           <t>安瓶 (美容与护肤)</t>
@@ -5659,10 +6003,14 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>神经醯胺 (美容与护肤)</t>
-        </is>
-      </c>
-      <c r="C175" s="1" t="inlineStr"/>
+          <t>[ngeramachite] 神经醯胺 (美容与护肤)</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>ngeramachite</t>
+        </is>
+      </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
           <t>神经醯胺 (美容与护肤)</t>
@@ -5697,7 +6045,7 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>[[pʰe̞p̚tʰa̠idɯ]] 胜肽 (美容与护肤)</t>
+          <t>胜肽 (美容与护肤)</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
@@ -5719,10 +6067,14 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>玫瑰果 (美容与护肤)</t>
-        </is>
-      </c>
-      <c r="C177" s="1" t="inlineStr"/>
+          <t>[rukeing] 玫瑰果 (美容与护肤)</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>rukeing</t>
+        </is>
+      </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
           <t>玫瑰果 (美容与护肤)</t>
@@ -5747,10 +6099,14 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>肤色底调 (美容与护肤)</t>
-        </is>
-      </c>
-      <c r="C178" s="1" t="inlineStr"/>
+          <t>[chontoun] 肤色底调 (美容与护肤)</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>chontoun</t>
+        </is>
+      </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
           <t>肤色底调 (美容与护肤)</t>
@@ -5785,7 +6141,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠duk̚]] 围棋 (Baduk) (嗜好与休闲)</t>
+          <t>围棋 (Baduk) (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -5817,7 +6173,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹nmunɦa̠k̚]] 天文学 (嗜好与休闲)</t>
+          <t>天文学 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -5849,7 +6205,7 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɯŋma̠]] 骑马 (嗜好与休闲)</t>
+          <t>骑马 (嗜好与休闲)</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -5881,7 +6237,7 @@
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛo̞ŋd͡ʑima̠]] 塞翁失马，焉知非福 (成语与谚语)</t>
+          <t>塞翁失马，焉知非福 (成语与谚语)</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -5913,7 +6269,7 @@
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t>[[ˈju(ː)jusʰa̠ŋd͡ʑo̞ŋ]] 物以类聚 (成语与谚语)</t>
+          <t>物以类聚 (成语与谚语)</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
@@ -5935,10 +6291,14 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>锦上添花 (惯用语与谚语)</t>
-        </is>
-      </c>
-      <c r="C184" s="1" t="inlineStr"/>
+          <t>[kengngatpongw] 锦上添花 (惯用语与谚语)</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>kengngatpongw</t>
+        </is>
+      </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
           <t>锦上添花 (惯用语与谚语)</t>
@@ -5963,10 +6323,14 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>两难局面 (惯用语与谚语)</t>
-        </is>
-      </c>
-      <c r="C185" s="1" t="inlineStr"/>
+          <t>[timrema] 两难局面 (惯用语与谚语)</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>timrema</t>
+        </is>
+      </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
           <t>两难局面 (惯用语与谚语)</t>
@@ -5991,10 +6355,14 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>口才出众 (惯用语与谚语)</t>
-        </is>
-      </c>
-      <c r="C186" s="1" t="inlineStr"/>
+          <t>[tampyonka] 口才出众 (惯用语与谚语)</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>tampyonka</t>
+        </is>
+      </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
           <t>口才出众 (惯用语与谚语)</t>
@@ -6029,7 +6397,7 @@
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛda̠nsʰa̠]] 网页装修工 (时尚穿搭)</t>
+          <t>网页装修工 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -6061,7 +6429,7 @@
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞ɭɭa̠bo̞]] 协作 (时尚与风格)</t>
+          <t>协作 (时尚与风格)</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6083,10 +6451,14 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>资金跑道 (时尚穿搭)</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr"/>
+          <t>[ronchechi] 资金跑道 (时尚穿搭)</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>ronchechi</t>
+        </is>
+      </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
           <t>资金跑道 (时尚穿搭)</t>
@@ -6111,10 +6483,14 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>温室气体 (环境)</t>
-        </is>
-      </c>
-      <c r="C190" s="1" t="inlineStr"/>
+          <t>[chunngimkange] 温室气体 (环境)</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>chunngimkange</t>
+        </is>
+      </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
           <t>温室气体 (环境)</t>
@@ -6139,10 +6515,14 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>再造林 (环境)</t>
-        </is>
-      </c>
-      <c r="C191" s="1" t="inlineStr"/>
+          <t>[kekuring] 再造林 (环境)</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>kekuring</t>
+        </is>
+      </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
           <t>再造林 (环境)</t>
@@ -6177,7 +6557,7 @@
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɡje̞]] 生态系统 (环境)</t>
+          <t>生态系统 (环境)</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
@@ -6199,10 +6579,14 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>臭氧层 (环境)</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="inlineStr"/>
+          <t>[chukunpet] 臭氧层 (环境)</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>chukunpet</t>
+        </is>
+      </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
           <t>臭氧层 (环境)</t>
@@ -6227,10 +6611,14 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>酸雨 (环境)</t>
-        </is>
-      </c>
-      <c r="C194" s="1" t="inlineStr"/>
+          <t>[nganngotpi] 酸雨 (环境)</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>nganngotpi</t>
+        </is>
+      </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
           <t>酸雨 (环境)</t>
@@ -6265,7 +6653,7 @@
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpo̞(ː)d͡ʑʌ̹n]] 保育 (环境)</t>
+          <t>保育 (环境)</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -6287,10 +6675,14 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>升级再造 (环境)</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="inlineStr"/>
+          <t>[chongngachihemrit] 升级再造 (环境)</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>chongngachihemrit</t>
+        </is>
+      </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
           <t>升级再造 (环境)</t>
@@ -6325,7 +6717,7 @@
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰɘ(ː)ɕʰik̚t͡ɕ͈i]] 栖息地 (环境)</t>
+          <t>栖息地 (环境)</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -6347,10 +6739,14 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>环境法 (环境)</t>
-        </is>
-      </c>
-      <c r="C198" s="1" t="inlineStr"/>
+          <t>[wnkyotpong] 环境法 (环境)</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>wnkyotpong</t>
+        </is>
+      </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
           <t>环境法 (环境)</t>
@@ -6375,10 +6771,14 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>环境部 (环境)</t>
-        </is>
-      </c>
-      <c r="C199" s="1" t="inlineStr"/>
+          <t>[wnkyotpi] 环境部 (环境)</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>wnkyotpi</t>
+        </is>
+      </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
           <t>环境部 (环境)</t>
@@ -6413,7 +6813,7 @@
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)sʰa̠nβwa̠tʰa̠nsʰo̞]] 二氧化碳 (环境)</t>
+          <t>二氧化碳 (环境)</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
@@ -6445,7 +6845,7 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>[[me̞tʰa̠n]] 甲烷 (环境)</t>
+          <t>甲烷 (环境)</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -6467,10 +6867,14 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>绿色税 (环境)</t>
-        </is>
-      </c>
-      <c r="C202" s="1" t="inlineStr"/>
+          <t>[wnkyotnge] 绿色税 (环境)</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>wnkyotnge</t>
+        </is>
+      </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
           <t>绿色税 (环境)</t>
@@ -6495,10 +6899,14 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>水处理 (环境)</t>
-        </is>
-      </c>
-      <c r="C203" s="1" t="inlineStr"/>
+          <t>[ngipori] 水处理 (环境)</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>ngipori</t>
+        </is>
+      </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
           <t>水处理 (环境)</t>
@@ -6533,7 +6941,7 @@
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋmuɭk͈wʌ̹n]] 生物圈 (环境)</t>
+          <t>生物圈 (环境)</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
@@ -6565,7 +6973,7 @@
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕiɦa̠sʰu]] 地下水 (环境)</t>
+          <t>地下水 (环境)</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
@@ -6587,10 +6995,14 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>过度捕捞 (环境)</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr"/>
+          <t>[nangwik] 过度捕捞 (环境)</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>nangwik</t>
+        </is>
+      </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
           <t>过度捕捞 (环境)</t>
@@ -6615,10 +7027,14 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>腐蚀 (环境)</t>
-        </is>
-      </c>
-      <c r="C207" s="1" t="inlineStr"/>
+          <t>[pingngik] 腐蚀 (环境)</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>pingngik</t>
+        </is>
+      </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
           <t>腐蚀 (环境)</t>
@@ -6653,7 +7069,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɦa̠k̚]] 生态 (环境)</t>
+          <t>生态 (环境)</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -6675,10 +7091,14 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>独立运动 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C209" s="1" t="inlineStr"/>
+          <t>[tukringchintut] 独立运动 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>tukringchintut</t>
+        </is>
+      </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
           <t>独立运动 (韩国历史)</t>
@@ -6703,10 +7123,14 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>三一运动 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C210" s="1" t="inlineStr"/>
+          <t>[ngangchimchintut] 三一运动 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>ngangchimchintut</t>
+        </is>
+      </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
           <t>三一运动 (韩国历史)</t>
@@ -6741,7 +7165,7 @@
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)d͡ʑo̞sʰʌ̹n]] 古朝鲜 (韩国历史)</t>
+          <t>古朝鲜 (韩国历史)</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
@@ -6773,7 +7197,7 @@
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ɡuɾjʌ̹]] 高句丽 (韩国历史)</t>
+          <t>高句丽 (韩国历史)</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -6805,7 +7229,7 @@
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>[[pɛk̚t͡ɕ͈e̞]] 百济王国 (韩国历史)</t>
+          <t>百济王国 (韩国历史)</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -6827,10 +7251,14 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>李成桂（太祖） (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C214" s="1" t="inlineStr"/>
+          <t>[chingotkye] 李成桂（太祖） (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>chingotkye</t>
+        </is>
+      </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t>李成桂（太祖） (韩国历史)</t>
@@ -6865,7 +7293,7 @@
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>[[juɡjo]] 韩国儒学 (韩国历史)</t>
+          <t>韩国儒学 (韩国历史)</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -6887,10 +7315,14 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>高丽大藏经 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C216" s="1" t="inlineStr"/>
+          <t>[ammantekatkyot] 高丽大藏经 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>ammantekatkyot</t>
+        </is>
+      </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
           <t>高丽大藏经 (韩国历史)</t>
@@ -6915,10 +7347,14 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>李舜臣将军 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C217" s="1" t="inlineStr"/>
+          <t>[chinginngin] 李舜臣将军 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>chinginngin</t>
+        </is>
+      </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
           <t>李舜臣将军 (韩国历史)</t>
@@ -6953,7 +7389,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>[[imd͡ʑinwɛɾa̠n]] 壬辰战争 (韩国历史)</t>
+          <t>壬辰战争 (韩国历史)</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -6975,10 +7411,14 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>临时政府 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr"/>
+          <t>[chingngikotpi] 临时政府 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>chingngikotpi</t>
+        </is>
+      </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
           <t>临时政府 (韩国历史)</t>
@@ -7013,7 +7453,7 @@
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ŋd͡ʑa̠]] 青瓷 (韩国历史)</t>
+          <t>青瓷 (韩国历史)</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
@@ -7045,7 +7485,7 @@
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>[[çud͡ʑʌ̹n]] 停战协定 (韩国历史)</t>
+          <t>停战协定 (韩国历史)</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
@@ -7077,7 +7517,7 @@
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠nɡun]] 檀君 (韩国历史)</t>
+          <t>檀君 (韩国历史)</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
@@ -7109,7 +7549,7 @@
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹nbi]] 儒生（朝鲜） (韩国历史)</t>
+          <t>儒生（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
@@ -7141,7 +7581,7 @@
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwa̠ɾa̠ŋ]] 花郎 (韩国历史)</t>
+          <t>花郎 (韩国历史)</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
@@ -7163,10 +7603,14 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>高宗皇帝 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C225" s="1" t="inlineStr"/>
+          <t>[kukut] 高宗皇帝 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>kukut</t>
+        </is>
+      </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
           <t>高宗皇帝 (韩国历史)</t>
@@ -7191,10 +7635,14 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>大韩帝国 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C226" s="1" t="inlineStr"/>
+          <t>[teankekik] 大韩帝国 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>teankekik</t>
+        </is>
+      </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
           <t>大韩帝国 (韩国历史)</t>
@@ -7219,10 +7667,14 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>甲午战争 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C227" s="1" t="inlineStr"/>
+          <t>[potchimkonket] 甲午战争 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>potchimkonket</t>
+        </is>
+      </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
           <t>甲午战争 (韩国历史)</t>
@@ -7247,10 +7699,14 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>瞻星台天文台 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C228" s="1" t="inlineStr"/>
+          <t>[pongngotte] 瞻星台天文台 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>pongngotte</t>
+        </is>
+      </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
           <t>瞻星台天文台 (韩国历史)</t>
@@ -7285,7 +7741,7 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ŋɡjunɡwa̠n]] 成均馆 (韩国历史)</t>
+          <t>成均馆 (韩国历史)</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -7307,10 +7763,14 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>宗庙 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C230" s="1" t="inlineStr"/>
+          <t>[kutmy] 宗庙 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>kutmy</t>
+        </is>
+      </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
           <t>宗庙 (韩国历史)</t>
@@ -7335,10 +7795,14 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>奎章阁御览所 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C231" s="1" t="inlineStr"/>
+          <t>[kwkatkak] 奎章阁御览所 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>kwkatkak</t>
+        </is>
+      </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
           <t>奎章阁御览所 (韩国历史)</t>
@@ -7363,10 +7827,14 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>东学运动 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C232" s="1" t="inlineStr"/>
+          <t>[tutakchintut] 东学运动 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>tutakchintut</t>
+        </is>
+      </c>
       <c r="D232" s="1" t="inlineStr">
         <is>
           <t>东学运动 (韩国历史)</t>
@@ -7401,7 +7869,7 @@
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>[[pʰuŋsʰu]] 风水（韩国堪舆学） (韩国历史)</t>
+          <t>风水（韩国堪舆学） (韩国历史)</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
@@ -7433,7 +7901,7 @@
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠ŋba̠n]] 两班（贵族） (韩国历史)</t>
+          <t>两班（贵族） (韩国历史)</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
@@ -7455,10 +7923,14 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>科举考试 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C235" s="1" t="inlineStr"/>
+          <t>[kwkongiong] 科举考试 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>kwkongiong</t>
+        </is>
+      </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
           <t>科举考试 (韩国历史)</t>
@@ -7483,10 +7955,14 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>朝鲜社会阶级 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C236" s="1" t="inlineStr"/>
+          <t>[nginpinketu] 朝鲜社会阶级 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>nginpinketu</t>
+        </is>
+      </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
           <t>朝鲜社会阶级 (韩国历史)</t>
@@ -7521,7 +7997,7 @@
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚k͈uŋ]] 韩国传统射箭 (韩国历史)</t>
+          <t>韩国传统射箭 (韩国历史)</t>
         </is>
       </c>
       <c r="E237" s="1" t="inlineStr">
@@ -7543,10 +8019,14 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>石窟庵 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C238" s="1" t="inlineStr"/>
+          <t>[ngokkimchang] 石窟庵 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>ngokkimchang</t>
+        </is>
+      </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
           <t>石窟庵 (韩国历史)</t>
@@ -7571,10 +8051,14 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>科举考试（朝鲜） (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C239" s="1" t="inlineStr"/>
+          <t>[kwkoketu] 科举考试（朝鲜） (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>kwkoketu</t>
+        </is>
+      </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
           <t>科举考试（朝鲜） (韩国历史)</t>
@@ -7599,10 +8083,14 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>统一新罗 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C240" s="1" t="inlineStr"/>
+          <t>[utchimnginra] 统一新罗 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>utchimnginra</t>
+        </is>
+      </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
           <t>统一新罗 (韩国历史)</t>
@@ -7627,10 +8115,14 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>王建（高丽太祖） (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C241" s="1" t="inlineStr"/>
+          <t>[chwtkon] 王建（高丽太祖） (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>chwtkon</t>
+        </is>
+      </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
           <t>王建（高丽太祖） (韩国历史)</t>
@@ -7665,7 +8157,7 @@
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰʌ̹ndo̞ɡjo]] 天道教 (韩国历史)</t>
+          <t>天道教 (韩国历史)</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
@@ -7697,7 +8189,7 @@
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuks͈a̠ɡi]] 三国史记 (韩国历史)</t>
+          <t>三国史记 (韩国历史)</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -7729,7 +8221,7 @@
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠mɡuɡjusʰa̠]] 三国遗事 (韩国历史)</t>
+          <t>三国遗事 (韩国历史)</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
@@ -7751,10 +8243,14 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>东医宝鉴 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C245" s="1" t="inlineStr"/>
+          <t>[tutchypukang] 东医宝鉴 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>tutchypukang</t>
+        </is>
+      </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
           <t>东医宝鉴 (韩国历史)</t>
@@ -7779,10 +8275,14 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>朴正熙 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C246" s="1" t="inlineStr"/>
+          <t>[pakkoty] 朴正熙 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>pakkoty</t>
+        </is>
+      </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
           <t>朴正熙 (韩国历史)</t>
@@ -7807,10 +8307,14 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>李承晚 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C247" s="1" t="inlineStr"/>
+          <t>[chingetman] 李承晚 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>chingetman</t>
+        </is>
+      </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
           <t>李承晚 (韩国历史)</t>
@@ -7835,10 +8339,14 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>安重根 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C248" s="1" t="inlineStr"/>
+          <t>[chankitken] 安重根 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>chankitken</t>
+        </is>
+      </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
           <t>安重根 (韩国历史)</t>
@@ -7863,10 +8371,14 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>直指心传 (韩国历史)</t>
-        </is>
-      </c>
-      <c r="C249" s="1" t="inlineStr"/>
+          <t>[kikkingingpechykom] 直指心传 (韩国历史)</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>kikkingingpechykom</t>
+        </is>
+      </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
           <t>直指心传 (韩国历史)</t>
@@ -7901,7 +8413,7 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɘ(ː)np͈ʌ̹p̚]] 宪法 (法律与政府)</t>
+          <t>宪法 (法律与政府)</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
@@ -7933,7 +8445,7 @@
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰa̠(ː)ŋwʌ̹nɰiwʌ̹n]] 参议员 (法律与政府)</t>
+          <t>参议员 (法律与政府)</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
@@ -7965,7 +8477,7 @@
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ŋβwa̠ɡuk̚]] 共和国 (法律与政府)</t>
+          <t>共和国 (法律与政府)</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
@@ -7987,10 +8499,14 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>君主制 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C253" s="1" t="inlineStr"/>
+          <t>[kinpike] 君主制 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>kinpike</t>
+        </is>
+      </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
           <t>君主制 (法律与政府)</t>
@@ -8025,7 +8541,7 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>[[ip̚p͈ʌ̹p̚]] 立法 (法律与政府)</t>
+          <t>立法 (法律与政府)</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8057,7 +8573,7 @@
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t>[[wʌ̹nɡo̞]] 原告 (法律与政府)</t>
+          <t>原告 (法律与政府)</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
@@ -8079,10 +8595,14 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>陪审团 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C256" s="1" t="inlineStr"/>
+          <t>[pengingtan] 陪审团 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>pengingtan</t>
+        </is>
+      </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
           <t>陪审团 (法律与政府)</t>
@@ -8117,7 +8637,7 @@
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ŋɡjʌ̹ɭ]] 判决 (法律与政府)</t>
+          <t>判决 (法律与政府)</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
@@ -8149,7 +8669,7 @@
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ŋsʰo̞]] 上诉 (法律与政府)</t>
+          <t>上诉 (法律与政府)</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
@@ -8181,7 +8701,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律与政府)</t>
+          <t>搜查令 (法律与政府)</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
@@ -8213,7 +8733,7 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɕʰi(ː)mink͈wʌ̹n]] 公民权利 (法律与政府)</t>
+          <t>公民权利 (法律与政府)</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
@@ -8245,7 +8765,7 @@
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t>[[ɸwe̞ŋɲʌ̹ŋ]] 挪用公款 (法律与政府)</t>
+          <t>挪用公款 (法律与政府)</t>
         </is>
       </c>
       <c r="E261" s="1" t="inlineStr">
@@ -8277,7 +8797,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>[[tʰa̠ɭs͈e̞]] 逃漏税 (法律与政府)</t>
+          <t>逃漏税 (法律与政府)</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -8299,10 +8819,14 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>性骚扰 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C263" s="1" t="inlineStr"/>
+          <t>[ngotyrut] 性骚扰 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>ngotyrut</t>
+        </is>
+      </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
           <t>性骚扰 (法律与政府)</t>
@@ -8337,7 +8861,7 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕɘ(ː)d͡ʑa̠k̚k͈wʌ̹n]] 版权 (法律与政府)</t>
+          <t>版权 (法律与政府)</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
@@ -8369,7 +8893,7 @@
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠ŋpʰjo]] 商标 (法律与政府)</t>
+          <t>商标 (法律与政府)</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
@@ -8401,7 +8925,7 @@
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɯkʰʌ̹]] 专利 (法律与政府)</t>
+          <t>专利 (法律与政府)</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
@@ -8433,7 +8957,7 @@
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋd͡ʑɯŋin]] 公证人 (法律与政府)</t>
+          <t>公证人 (法律与政府)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
@@ -8455,10 +8979,14 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>民法 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C268" s="1" t="inlineStr"/>
+          <t>[minpong] 民法 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>minpong</t>
+        </is>
+      </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
           <t>民法 (法律与政府)</t>
@@ -8493,7 +9021,7 @@
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>[[çʌ̹ŋp͈ʌ̹p̚]] 刑法 (法律与政府)</t>
+          <t>刑法 (法律与政府)</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -8525,7 +9053,7 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹p̚]] 行政法 (法律与政府)</t>
+          <t>行政法 (法律与政府)</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
@@ -8557,7 +9085,7 @@
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>[[kuk̚t͡ɕ͈e̞bʌ̹p̚]] 国际法 (法律与政府)</t>
+          <t>国际法 (法律与政府)</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
@@ -8589,7 +9117,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ja̠k̚]] 条约 (法律与政府)</t>
+          <t>条约 (法律与政府)</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -8621,7 +9149,7 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋsʰa̠]] 领事 (法律与政府)</t>
+          <t>领事 (法律与政府)</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
@@ -8653,7 +9181,7 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>[[ˈwe̞(ː)ɡjo]] 外交事务 (法律与政府)</t>
+          <t>外交事务 (法律与政府)</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
@@ -8675,10 +9203,14 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>归化 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C275" s="1" t="inlineStr"/>
+          <t>[kew] 归化 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>kew</t>
+        </is>
+      </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
           <t>归化 (法律与政府)</t>
@@ -8703,10 +9235,14 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>居民登记 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C276" s="1" t="inlineStr"/>
+          <t>[kimintetruk] 居民登记 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>kimintetruk</t>
+        </is>
+      </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
           <t>居民登记 (法律与政府)</t>
@@ -8741,7 +9277,7 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋmu]] 公务员制度 (法律与政府)</t>
+          <t>公务员制度 (法律与政府)</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
@@ -8773,7 +9309,7 @@
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠ʎʎod͡ʑe̞]] 官僚制 (法律与政府)</t>
+          <t>官僚制 (法律与政府)</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
@@ -8805,7 +9341,7 @@
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕipʰɛŋ]] 强制执行 (法律与政府)</t>
+          <t>强制执行 (法律与政府)</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
@@ -8837,7 +9373,7 @@
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>[[kwa̠sʰe̞]] 税项 (法律与政府)</t>
+          <t>税项 (法律与政府)</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
@@ -8869,7 +9405,7 @@
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋa̠ŋɯnɦɛŋ]] 中央银行 (法律与政府)</t>
+          <t>中央银行 (法律与政府)</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
@@ -8901,7 +9437,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>[[tɛbʌ̹bwʌ̹n]] 最高法院 (法律与政府)</t>
+          <t>最高法院 (法律与政府)</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -8933,7 +9469,7 @@
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>[[hʌ̹nbʌ̹p̚t͡ɕ͈ɛpʰa̠nsʰo̞]] 宪法法庭 (法律与政府)</t>
+          <t>宪法法庭 (法律与政府)</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
@@ -8965,7 +9501,7 @@
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>[[hɛŋd͡ʑʌ̹ŋbʌ̹bwʌ̹n]] 行政法院 (法律与政府)</t>
+          <t>行政法院 (法律与政府)</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
@@ -8997,7 +9533,7 @@
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>[[kuŋmintʰupʰjo]] 公民投票 (法律与政府)</t>
+          <t>公民投票 (法律与政府)</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
@@ -9029,7 +9565,7 @@
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>[[ˈtʰa̠(ː)nɦɛk̚]] 弹劾 (法律与政府)</t>
+          <t>弹劾 (法律与政府)</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
@@ -9061,7 +9597,7 @@
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t>[[pʰa̠ʎʎe̞]] 成案 ,判例 (法律与政府)</t>
+          <t>成案 ,判例 (法律与政府)</t>
         </is>
       </c>
       <c r="E287" s="1" t="inlineStr">
@@ -9083,10 +9619,14 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>时效法规 (法律与政府)</t>
-        </is>
-      </c>
-      <c r="C288" s="1" t="inlineStr"/>
+          <t>[kutngungiy] 时效法规 (法律与政府)</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>kutngungiy</t>
+        </is>
+      </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
           <t>时效法规 (法律与政府)</t>
@@ -9121,7 +9661,7 @@
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t>[[kut̚]] 巫俗仪式 (宗教)</t>
+          <t>巫俗仪式 (宗教)</t>
         </is>
       </c>
       <c r="E289" s="1" t="inlineStr">
@@ -9143,10 +9683,14 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>排灯节 (宗教)</t>
-        </is>
-      </c>
-      <c r="C290" s="1" t="inlineStr"/>
+          <t>[tichwmri] 排灯节 (宗教)</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>tichwmri</t>
+        </is>
+      </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
           <t>排灯节 (宗教)</t>
@@ -9181,7 +9725,7 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>[[ˈi(ː)ɡjodo̞]] 异教徒 (宗教)</t>
+          <t>异教徒 (宗教)</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
@@ -9203,10 +9747,14 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>不可知论者 (宗教)</t>
-        </is>
-      </c>
-      <c r="C292" s="1" t="inlineStr"/>
+          <t>[pimkakirunka] 不可知论者 (宗教)</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>pimkakirunka</t>
+        </is>
+      </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
           <t>不可知论者 (宗教)</t>
@@ -9241,7 +9789,7 @@
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰo̞(ː)ɡjo]] 传教 (宗教)</t>
+          <t>传教 (宗教)</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
@@ -9273,7 +9821,7 @@
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹n]] 禅 (宗教)</t>
+          <t>禅 (宗教)</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
@@ -9305,7 +9853,7 @@
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ɡjo]] 道教徒 (宗教)</t>
+          <t>道教徒 (宗教)</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
@@ -9327,10 +9875,14 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>驱魔 (宗教)</t>
-        </is>
-      </c>
-      <c r="C296" s="1" t="inlineStr"/>
+          <t>[pikke] 驱魔 (宗教)</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>pikke</t>
+        </is>
+      </c>
       <c r="D296" s="1" t="inlineStr">
         <is>
           <t>驱魔 (宗教)</t>
@@ -9355,10 +9907,14 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>台湾加权 (金融与银行)</t>
-        </is>
-      </c>
-      <c r="C297" s="1" t="inlineStr"/>
+          <t>[hungei] 台湾加权 (金融与银行)</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>hungei</t>
+        </is>
+      </c>
       <c r="D297" s="1" t="inlineStr">
         <is>
           <t>台湾加权 (金融与银行)</t>
@@ -9393,7 +9949,7 @@
       </c>
       <c r="D298" s="1" t="inlineStr">
         <is>
-          <t>[[pitʰɯkʰo̞in]] 比特币 (金融与银行)</t>
+          <t>比特币 (金融与银行)</t>
         </is>
       </c>
       <c r="E298" s="1" t="inlineStr">
@@ -9415,10 +9971,14 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>企业税 (金融与银行)</t>
-        </is>
-      </c>
-      <c r="C299" s="1" t="inlineStr"/>
+          <t>[pongchinnge] 企业税 (金融与银行)</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>pongchinnge</t>
+        </is>
+      </c>
       <c r="D299" s="1" t="inlineStr">
         <is>
           <t>企业税 (金融与银行)</t>
@@ -9453,7 +10013,7 @@
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰa̠(ː)sʰa̠n]] 破产 (金融与银行)</t>
+          <t>破产 (金融与银行)</t>
         </is>
       </c>
       <c r="E300" s="1" t="inlineStr">
@@ -9485,7 +10045,7 @@
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)ɡwʌ̹ɲd͡ʑa̠]] 债权人 (金融与银行)</t>
+          <t>债权人 (金融与银行)</t>
         </is>
       </c>
       <c r="E301" s="1" t="inlineStr">
@@ -9517,7 +10077,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɛ(ː)mud͡ʑa̠]] 债务人 (金融与银行)</t>
+          <t>债务人 (金融与银行)</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
@@ -9549,7 +10109,7 @@
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>[[ta̠mbo̞]] 抵押品 (金融与银行)</t>
+          <t>抵押品 (金融与银行)</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
@@ -9571,10 +10131,14 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>担保人 (金融与银行)</t>
-        </is>
-      </c>
-      <c r="C304" s="1" t="inlineStr"/>
+          <t>[puketchin] 担保人 (金融与银行)</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>puketchin</t>
+        </is>
+      </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
           <t>担保人 (金融与银行)</t>
@@ -9609,7 +10173,7 @@
       </c>
       <c r="D305" s="1" t="inlineStr">
         <is>
-          <t>[[tipʰɯɭɭe̞iɕʰʌ̹n]] 通货紧缩 (金融与银行)</t>
+          <t>通货紧缩 (金融与银行)</t>
         </is>
       </c>
       <c r="E305" s="1" t="inlineStr">
@@ -9631,10 +10195,14 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>金融监督委员会 (金融银行)</t>
-        </is>
-      </c>
-      <c r="C306" s="1" t="inlineStr"/>
+          <t>[kengchwtkangtukchechenwi] 金融监督委员会 (金融银行)</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>kengchwtkangtukchechenwi</t>
+        </is>
+      </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
           <t>金融监督委员会 (金融银行)</t>
@@ -9659,10 +10227,14 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>经济合作与发展组织（OECD） (金融银行)</t>
-        </is>
-      </c>
-      <c r="C307" s="1" t="inlineStr"/>
+          <t>[kyotkeyongryokkepamkiki] 经济合作与发展组织（OECD） (金融银行)</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>kyotkeyongryokkepamkiki</t>
+        </is>
+      </c>
       <c r="D307" s="1" t="inlineStr">
         <is>
           <t>经济合作与发展组织（OECD） (金融银行)</t>
@@ -9687,10 +10259,14 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF） (金融银行)</t>
-        </is>
-      </c>
-      <c r="C308" s="1" t="inlineStr"/>
+          <t>[kikkeutwkikeng] 国际货币基金组织（IMF） (金融银行)</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>kikkeutwkikeng</t>
+        </is>
+      </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
           <t>国际货币基金组织（IMF） (金融银行)</t>
@@ -9715,10 +10291,14 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>世界银行 (金融银行)</t>
-        </is>
-      </c>
-      <c r="C309" s="1" t="inlineStr"/>
+          <t>[ngekyechenet] 世界银行 (金融银行)</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>ngekyechenet</t>
+        </is>
+      </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
           <t>世界银行 (金融银行)</t>
@@ -9743,10 +10323,14 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>并购 (金融银行)</t>
-        </is>
-      </c>
-      <c r="C310" s="1" t="inlineStr"/>
+          <t>[chinngiangpyot] 并购 (金融银行)</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>chinngiangpyot</t>
+        </is>
+      </c>
       <c r="D310" s="1" t="inlineStr">
         <is>
           <t>并购 (金融银行)</t>
@@ -9781,7 +10365,7 @@
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕuŋɡɛin]] 经纪商 (金融银行)</t>
+          <t>经纪商 (金融银行)</t>
         </is>
       </c>
       <c r="E311" s="1" t="inlineStr">
@@ -9803,10 +10387,14 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>交易商 (金融银行)</t>
-        </is>
-      </c>
-      <c r="C312" s="1" t="inlineStr"/>
+          <t>[erechito] 交易商 (金融银行)</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>erechito</t>
+        </is>
+      </c>
       <c r="D312" s="1" t="inlineStr">
         <is>
           <t>交易商 (金融银行)</t>
@@ -9831,10 +10419,14 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>幕墙 (建筑)</t>
-        </is>
-      </c>
-      <c r="C313" s="1" t="inlineStr"/>
+          <t>[hoenchem] 幕墙 (建筑)</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>hoenchem</t>
+        </is>
+      </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
           <t>幕墙 (建筑)</t>
@@ -9859,10 +10451,14 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>分区 (建筑)</t>
-        </is>
-      </c>
-      <c r="C314" s="1" t="inlineStr"/>
+          <t>[chyttukichyok] 分区 (建筑)</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>chyttukichyok</t>
+        </is>
+      </c>
       <c r="D314" s="1" t="inlineStr">
         <is>
           <t>分区 (建筑)</t>
@@ -9887,10 +10483,14 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>寻路。 (建筑)</t>
-        </is>
-      </c>
-      <c r="C315" s="1" t="inlineStr"/>
+          <t>[kimpapki] 寻路。 (建筑)</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>kimpapki</t>
+        </is>
+      </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
           <t>寻路。 (建筑)</t>
@@ -9925,7 +10525,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>[[ɯmʝa̠ŋ]] 声学 (建筑)</t>
+          <t>声学 (建筑)</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -9947,10 +10547,14 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>暖通空调 (建筑)</t>
-        </is>
-      </c>
-      <c r="C317" s="1" t="inlineStr"/>
+          <t>[netnanpat] 暖通空调 (建筑)</t>
+        </is>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>netnanpat</t>
+        </is>
+      </c>
       <c r="D317" s="1" t="inlineStr">
         <is>
           <t>暖通空调 (建筑)</t>
@@ -9975,10 +10579,14 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>预制 (建筑)</t>
-        </is>
-      </c>
-      <c r="C318" s="1" t="inlineStr"/>
+          <t>[erieng] 预制 (建筑)</t>
+        </is>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>erieng</t>
+        </is>
+      </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
           <t>预制 (建筑)</t>
@@ -10003,10 +10611,14 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>神经科学 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C319" s="1" t="inlineStr"/>
+          <t>[nginkyotkwak] 神经科学 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>nginkyotkwak</t>
+        </is>
+      </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
           <t>神经科学 (科学与研究)</t>
@@ -10041,7 +10653,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t>[[iʎʎuɦa̠k̚]] 人类学 (科学与研究)</t>
+          <t>人类学 (科学与研究)</t>
         </is>
       </c>
       <c r="E320" s="1" t="inlineStr">
@@ -10073,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)ɡo̞ɦa̠k̚]] 考古学 (科学与研究)</t>
+          <t>考古学 (科学与研究)</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10105,7 +10717,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>[[ʌ̹nʌ̹ɦa̠k̚]] 语言学 (科学与研究)</t>
+          <t>语言学 (科学与研究)</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -10127,10 +10739,14 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>机器人学 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C323" s="1" t="inlineStr"/>
+          <t>[ruputkutak] 机器人学 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>ruputkutak</t>
+        </is>
+      </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
           <t>机器人学 (科学与研究)</t>
@@ -10165,7 +10781,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t>[[na̠no̞ɡisʰuɭ]] 奈米技术 (科学与研究)</t>
+          <t>奈米技术 (科学与研究)</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
@@ -10187,10 +10803,14 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>生物技术 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C325" s="1" t="inlineStr"/>
+          <t>[ngetmyotkutak] 生物技术 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>ngetmyotkutak</t>
+        </is>
+      </c>
       <c r="D325" s="1" t="inlineStr">
         <is>
           <t>生物技术 (科学与研究)</t>
@@ -10215,10 +10835,14 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>基因工程 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C326" s="1" t="inlineStr"/>
+          <t>[chwkonkutak] 基因工程 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>chwkonkutak</t>
+        </is>
+      </c>
       <c r="D326" s="1" t="inlineStr">
         <is>
           <t>基因工程 (科学与研究)</t>
@@ -10243,10 +10867,14 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>干细胞 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C327" s="1" t="inlineStr"/>
+          <t>[kimkingeu] 干细胞 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C327" s="1" t="inlineStr">
+        <is>
+          <t>kimkingeu</t>
+        </is>
+      </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
           <t>干细胞 (科学与研究)</t>
@@ -10271,10 +10899,14 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>临床试验 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C328" s="1" t="inlineStr"/>
+          <t>[chingngatngiong] 临床试验 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>chingngatngiong</t>
+        </is>
+      </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
           <t>临床试验 (科学与研究)</t>
@@ -10299,10 +10931,14 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>博士后研究员 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C329" s="1" t="inlineStr"/>
+          <t>[pakngaichyonkichen] 博士后研究员 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>pakngaichyonkichen</t>
+        </is>
+      </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
           <t>博士后研究员 (科学与研究)</t>
@@ -10327,10 +10963,14 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>元分析 (科学研究)</t>
-        </is>
-      </c>
-      <c r="C330" s="1" t="inlineStr"/>
+          <t>[meapinngok] 元分析 (科学研究)</t>
+        </is>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>meapinngok</t>
+        </is>
+      </c>
       <c r="D330" s="1" t="inlineStr">
         <is>
           <t>元分析 (科学研究)</t>
@@ -10355,10 +10995,14 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>对照组 (科学研究)</t>
-        </is>
-      </c>
-      <c r="C331" s="1" t="inlineStr"/>
+          <t>[tekukin] 对照组 (科学研究)</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>tekukin</t>
+        </is>
+      </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
           <t>对照组 (科学研究)</t>
@@ -10393,7 +11037,7 @@
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpjɘ(ː)nsʰu]] 变量 (科学研究)</t>
+          <t>变量 (科学研究)</t>
         </is>
       </c>
       <c r="E332" s="1" t="inlineStr">
@@ -10415,10 +11059,14 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>相关性 (科学研究)</t>
-        </is>
-      </c>
-      <c r="C333" s="1" t="inlineStr"/>
+          <t>[ngatkwnkwnkye] 相关性 (科学研究)</t>
+        </is>
+      </c>
+      <c r="C333" s="1" t="inlineStr">
+        <is>
+          <t>ngatkwnkwnkye</t>
+        </is>
+      </c>
       <c r="D333" s="1" t="inlineStr">
         <is>
           <t>相关性 (科学研究)</t>
@@ -10443,10 +11091,14 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>因果关系 (科学研究)</t>
-        </is>
-      </c>
-      <c r="C334" s="1" t="inlineStr"/>
+          <t>[chinkwkwnkye] 因果关系 (科学研究)</t>
+        </is>
+      </c>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>chinkwkwnkye</t>
+        </is>
+      </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
           <t>因果关系 (科学研究)</t>
@@ -10481,7 +11133,7 @@
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t>[[ɕʰimjuɭɭe̞iɕʰʌ̹n]] 模拟 (科学研究)</t>
+          <t>模拟 (科学研究)</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
@@ -10513,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕid͡ʑinɦa̠k̚]] 地震学 (科学研究)</t>
+          <t>地震学 (科学研究)</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -10545,7 +11197,7 @@
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t>[[ˈɸwa̠(ː)sʰa̠nɦa̠k̚]] 火山学 (科学研究)</t>
+          <t>火山学 (科学研究)</t>
         </is>
       </c>
       <c r="E337" s="1" t="inlineStr">
@@ -10577,7 +11229,7 @@
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t>[[ˈko̞(ː)sʰɛŋmuɾɦa̠k̚]] 古生物 (科学研究)</t>
+          <t>古生物 (科学研究)</t>
         </is>
       </c>
       <c r="E338" s="1" t="inlineStr">
@@ -10609,7 +11261,7 @@
       </c>
       <c r="D339" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpɘ(ː)bɰiɦa̠k̚]] 法医学 (科学研究)</t>
+          <t>法医学 (科学研究)</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
@@ -10631,10 +11283,14 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>毒理学 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C340" s="1" t="inlineStr"/>
+          <t>[tukngotak] 毒理学 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t>tukngotak</t>
+        </is>
+      </c>
       <c r="D340" s="1" t="inlineStr">
         <is>
           <t>毒理学 (科学与研究)</t>
@@ -10669,7 +11325,7 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹kʰa̠k̚]] 流行病学 (科学与研究)</t>
+          <t>流行病学 (科学与研究)</t>
         </is>
       </c>
       <c r="E341" s="1" t="inlineStr">
@@ -10691,10 +11347,14 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>材料科学 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C342" s="1" t="inlineStr"/>
+          <t>[kerykwak] 材料科学 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C342" s="1" t="inlineStr">
+        <is>
+          <t>kerykwak</t>
+        </is>
+      </c>
       <c r="D342" s="1" t="inlineStr">
         <is>
           <t>材料科学 (科学与研究)</t>
@@ -10719,10 +11379,14 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>知情同意 (科学与研究)</t>
-        </is>
-      </c>
-      <c r="C343" s="1" t="inlineStr"/>
+          <t>[tutchyngo] 知情同意 (科学与研究)</t>
+        </is>
+      </c>
+      <c r="C343" s="1" t="inlineStr">
+        <is>
+          <t>tutchyngo</t>
+        </is>
+      </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
           <t>知情同意 (科学与研究)</t>
@@ -10757,7 +11421,7 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t>[[po̞ŋni]] 复利 (金融与银行)</t>
+          <t>复利 (金融与银行)</t>
         </is>
       </c>
       <c r="E344" s="1" t="inlineStr">
@@ -10779,10 +11443,14 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>净资产 (金融与银行)</t>
-        </is>
-      </c>
-      <c r="C345" s="1" t="inlineStr"/>
+          <t>[nginkangan] 净资产 (金融与银行)</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t>nginkangan</t>
+        </is>
+      </c>
       <c r="D345" s="1" t="inlineStr">
         <is>
           <t>净资产 (金融与银行)</t>
@@ -10807,10 +11475,14 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>建筑规范 (建筑)</t>
-        </is>
-      </c>
-      <c r="C346" s="1" t="inlineStr"/>
+          <t>[konpikpong] 建筑规范 (建筑)</t>
+        </is>
+      </c>
+      <c r="C346" s="1" t="inlineStr">
+        <is>
+          <t>konpikpong</t>
+        </is>
+      </c>
       <c r="D346" s="1" t="inlineStr">
         <is>
           <t>建筑规范 (建筑)</t>
@@ -10835,10 +11507,14 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>储蓄率 (金融与银行)</t>
-        </is>
-      </c>
-      <c r="C347" s="1" t="inlineStr"/>
+          <t>[kopikrwm] 储蓄率 (金融与银行)</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t>kopikrwm</t>
+        </is>
+      </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
           <t>储蓄率 (金融与银行)</t>
@@ -10873,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>[[tɛdɯɭbo̞]] 木梁 (建筑)</t>
+          <t>木梁 (建筑)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -10895,10 +11571,14 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>悬臂 (建筑)</t>
-        </is>
-      </c>
-      <c r="C349" s="1" t="inlineStr"/>
+          <t>[henimrepo] 悬臂 (建筑)</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="inlineStr">
+        <is>
+          <t>henimrepo</t>
+        </is>
+      </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
           <t>悬臂 (建筑)</t>
@@ -10923,10 +11603,14 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>女儿墙 (建筑)</t>
-        </is>
-      </c>
-      <c r="C350" s="1" t="inlineStr"/>
+          <t>[nankanpyok] 女儿墙 (建筑)</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t>nankanpyok</t>
+        </is>
+      </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
           <t>女儿墙 (建筑)</t>
@@ -10951,10 +11635,14 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>高窗 (建筑)</t>
-        </is>
-      </c>
-      <c r="C351" s="1" t="inlineStr"/>
+          <t>[kupat] 高窗 (建筑)</t>
+        </is>
+      </c>
+      <c r="C351" s="1" t="inlineStr">
+        <is>
+          <t>kupat</t>
+        </is>
+      </c>
       <c r="D351" s="1" t="inlineStr">
         <is>
           <t>高窗 (建筑)</t>
@@ -10979,10 +11667,14 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>厚涂法 (艺术与设计)</t>
-        </is>
-      </c>
-      <c r="C352" s="1" t="inlineStr"/>
+          <t>[chingangeu] 厚涂法 (艺术与设计)</t>
+        </is>
+      </c>
+      <c r="C352" s="1" t="inlineStr">
+        <is>
+          <t>chingangeu</t>
+        </is>
+      </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
           <t>厚涂法 (艺术与设计)</t>
@@ -11017,7 +11709,7 @@
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
-          <t>[[ˈkɘ(ː)mɲʌ̹ɭ]] 审查 (媒体与新闻)</t>
+          <t>审查 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E353" s="1" t="inlineStr">
@@ -11049,7 +11741,7 @@
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t>[[sʰʌ̹ɲd͡ʑʌ̹n]] 宣传 (媒体与新闻)</t>
+          <t>宣传 (媒体与新闻)</t>
         </is>
       </c>
       <c r="E354" s="1" t="inlineStr">
@@ -11071,10 +11763,14 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>评论文章 (媒体与新闻)</t>
-        </is>
-      </c>
-      <c r="C355" s="1" t="inlineStr"/>
+          <t>[kikumin] 评论文章 (媒体与新闻)</t>
+        </is>
+      </c>
+      <c r="C355" s="1" t="inlineStr">
+        <is>
+          <t>kikumin</t>
+        </is>
+      </c>
       <c r="D355" s="1" t="inlineStr">
         <is>
           <t>评论文章 (媒体与新闻)</t>
@@ -11099,10 +11795,14 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>新闻摄影 (媒体与新闻)</t>
-        </is>
-      </c>
-      <c r="C356" s="1" t="inlineStr"/>
+          <t>[uukonomrikeng] 新闻摄影 (媒体与新闻)</t>
+        </is>
+      </c>
+      <c r="C356" s="1" t="inlineStr">
+        <is>
+          <t>uukonomrikeng</t>
+        </is>
+      </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
           <t>新闻摄影 (媒体与新闻)</t>
@@ -11127,10 +11827,14 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>评论员 (媒体与新闻)</t>
-        </is>
-      </c>
-      <c r="C357" s="1" t="inlineStr"/>
+          <t>[nunyotka] 评论员 (媒体与新闻)</t>
+        </is>
+      </c>
+      <c r="C357" s="1" t="inlineStr">
+        <is>
+          <t>nunyotka</t>
+        </is>
+      </c>
       <c r="D357" s="1" t="inlineStr">
         <is>
           <t>评论员 (媒体与新闻)</t>
@@ -11155,10 +11859,14 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>煽情主义 (媒体与新闻学)</t>
-        </is>
-      </c>
-      <c r="C358" s="1" t="inlineStr"/>
+          <t>[ngonkotkichy] 煽情主义 (媒体与新闻学)</t>
+        </is>
+      </c>
+      <c r="C358" s="1" t="inlineStr">
+        <is>
+          <t>ngonkotkichy</t>
+        </is>
+      </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
           <t>煽情主义 (媒体与新闻学)</t>
@@ -11183,10 +11891,14 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>深度伪造 (媒体与新闻学)</t>
-        </is>
-      </c>
-      <c r="C359" s="1" t="inlineStr"/>
+          <t>[tingechihe] 深度伪造 (媒体与新闻学)</t>
+        </is>
+      </c>
+      <c r="C359" s="1" t="inlineStr">
+        <is>
+          <t>tingechihe</t>
+        </is>
+      </c>
       <c r="D359" s="1" t="inlineStr">
         <is>
           <t>深度伪造 (媒体与新闻学)</t>
@@ -11211,10 +11923,14 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>媒体法 (媒体与新闻学)</t>
-        </is>
-      </c>
-      <c r="C360" s="1" t="inlineStr"/>
+          <t>[chonrunpong] 媒体法 (媒体与新闻学)</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>chonrunpong</t>
+        </is>
+      </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
           <t>媒体法 (媒体与新闻学)</t>
@@ -11239,10 +11955,14 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>广播权限 (媒体与新闻学)</t>
-        </is>
-      </c>
-      <c r="C361" s="1" t="inlineStr"/>
+          <t>[patngutken] 广播权限 (媒体与新闻学)</t>
+        </is>
+      </c>
+      <c r="C361" s="1" t="inlineStr">
+        <is>
+          <t>patngutken</t>
+        </is>
+      </c>
       <c r="D361" s="1" t="inlineStr">
         <is>
           <t>广播权限 (媒体与新闻学)</t>
@@ -11267,10 +11987,14 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>编辑委员会 (媒体与新闻业)</t>
-        </is>
-      </c>
-      <c r="C362" s="1" t="inlineStr"/>
+          <t>[yonkingchechenwi] 编辑委员会 (媒体与新闻业)</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>yonkingchechenwi</t>
+        </is>
+      </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
           <t>编辑委员会 (媒体与新闻业)</t>
@@ -11305,7 +12029,7 @@
       </c>
       <c r="D363" s="1" t="inlineStr">
         <is>
-          <t>[[jukʰwe̞]] 生拌牛肉 (韩国美食与餐饮)</t>
+          <t>生拌牛肉 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E363" s="1" t="inlineStr">
@@ -11337,7 +12061,7 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>[[kud͡ʑʌ̹ɭpʰa̠n]] 九节板 (韩国美食与餐饮)</t>
+          <t>九节板 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -11369,7 +12093,7 @@
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>[[ˈha̠(ː)ɲd͡ʑʌ̹ŋɕʰik̚]] 韩定食 (韩国美食与餐饮)</t>
+          <t>韩定食 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -11401,7 +12125,7 @@
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t>[[ja̠kɕ͈ik̚]] 药饭 (韩国美食与餐饮)</t>
+          <t>药饭 (韩国美食与餐饮)</t>
         </is>
       </c>
       <c r="E366" s="1" t="inlineStr">
@@ -11423,10 +12147,14 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>年糕排 (Tteok Galbi) (韩国饮食)</t>
-        </is>
-      </c>
-      <c r="C367" s="1" t="inlineStr"/>
+          <t>[tokkampi] 年糕排 (Tteok Galbi) (韩国饮食)</t>
+        </is>
+      </c>
+      <c r="C367" s="1" t="inlineStr">
+        <is>
+          <t>tokkampi</t>
+        </is>
+      </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
           <t>年糕排 (Tteok Galbi) (韩国饮食)</t>
@@ -11461,7 +12189,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛud͡ʑʌ̹t̚]] 虾酱 (Saeujeot) (韩国饮食)</t>
+          <t>虾酱 (Saeujeot) (韩国饮食)</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -11493,7 +12221,7 @@
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹k̚]] Jeok (韩国饮食文化)</t>
+          <t>Jeok (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
@@ -11525,7 +12253,7 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韩国饮食文化)</t>
+          <t>Sea Squirt (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E370" s="1" t="inlineStr">
@@ -11547,10 +12275,14 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>Nakji Bokkeum (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C371" s="1" t="inlineStr"/>
+          <t>[nakkipukcheng] Nakji Bokkeum (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C371" s="1" t="inlineStr">
+        <is>
+          <t>nakkipukcheng</t>
+        </is>
+      </c>
       <c r="D371" s="1" t="inlineStr">
         <is>
           <t>Nakji Bokkeum (韩国饮食文化)</t>
@@ -11575,10 +12307,14 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Fish Mandu (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C372" s="1" t="inlineStr"/>
+          <t>[chomanti] Fish Mandu (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C372" s="1" t="inlineStr">
+        <is>
+          <t>chomanti</t>
+        </is>
+      </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
           <t>Fish Mandu (韩国饮食文化)</t>
@@ -11603,10 +12339,14 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>Toranguk (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C373" s="1" t="inlineStr"/>
+          <t>[urankik] Toranguk (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C373" s="1" t="inlineStr">
+        <is>
+          <t>urankik</t>
+        </is>
+      </c>
       <c r="D373" s="1" t="inlineStr">
         <is>
           <t>Toranguk (韩国饮食文化)</t>
@@ -11641,7 +12381,7 @@
       </c>
       <c r="D374" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲuk̚]] 肉片 (韩国饮食文化)</t>
+          <t>肉片 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="E374" s="1" t="inlineStr">
@@ -11663,10 +12403,14 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>牛尾汤 (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C375" s="1" t="inlineStr"/>
+          <t>[kurikungat] 牛尾汤 (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C375" s="1" t="inlineStr">
+        <is>
+          <t>kurikungat</t>
+        </is>
+      </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
           <t>牛尾汤 (韩国饮食文化)</t>
@@ -11691,10 +12435,14 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>烤山药根 (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C376" s="1" t="inlineStr"/>
+          <t>[totokkichi] 烤山药根 (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t>totokkichi</t>
+        </is>
+      </c>
       <c r="D376" s="1" t="inlineStr">
         <is>
           <t>烤山药根 (韩国饮食文化)</t>
@@ -11719,10 +12467,14 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>清汤 (韩国饮食文化)</t>
-        </is>
-      </c>
-      <c r="C377" s="1" t="inlineStr"/>
+          <t>[ponat] 清汤 (韩国饮食文化)</t>
+        </is>
+      </c>
+      <c r="C377" s="1" t="inlineStr">
+        <is>
+          <t>ponat</t>
+        </is>
+      </c>
       <c r="D377" s="1" t="inlineStr">
         <is>
           <t>清汤 (韩国饮食文化)</t>
@@ -11757,7 +12509,7 @@
       </c>
       <c r="D378" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞ʝʌ̹nbjʌ̹ŋ]] 精神分裂症 (心理健康与保健)</t>
+          <t>精神分裂症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E378" s="1" t="inlineStr">
@@ -11779,10 +12531,14 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>认知行为疗法 (心理健康与保健)</t>
-        </is>
-      </c>
-      <c r="C379" s="1" t="inlineStr"/>
+          <t>[chinkiettutpiry] 认知行为疗法 (心理健康与保健)</t>
+        </is>
+      </c>
+      <c r="C379" s="1" t="inlineStr">
+        <is>
+          <t>chinkiettutpiry</t>
+        </is>
+      </c>
       <c r="D379" s="1" t="inlineStr">
         <is>
           <t>认知行为疗法 (心理健康与保健)</t>
@@ -11817,7 +12573,7 @@
       </c>
       <c r="D380" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠ɡiɛ]] 自恋 (心理健康与保健)</t>
+          <t>自恋 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
@@ -11849,7 +12605,7 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t>[[ˈhɛ(ː)ɾi]] 分离 (心理健康与保健)</t>
+          <t>分离 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E381" s="1" t="inlineStr">
@@ -11881,7 +12637,7 @@
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕa̠pʰje̞t͡ɕ͈ɯŋ]] 自闭症 (心理健康与保健)</t>
+          <t>自闭症 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E382" s="1" t="inlineStr">
@@ -11913,7 +12669,7 @@
       </c>
       <c r="D383" s="1" t="inlineStr">
         <is>
-          <t>[[pʰjʌ̹ɲd͡ʑip̚t͡ɕ͈ɯŋ]] 偏执 (心理健康与保健)</t>
+          <t>偏执 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E383" s="1" t="inlineStr">
@@ -11945,7 +12701,7 @@
       </c>
       <c r="D384" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠sʰɯɾa̠itʰiŋ]] 煤气灯效应 (心理健康与保健)</t>
+          <t>煤气灯效应 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E384" s="1" t="inlineStr">
@@ -11967,10 +12723,14 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>共依存 (心理健康与保健)</t>
-        </is>
-      </c>
-      <c r="C385" s="1" t="inlineStr"/>
+          <t>[kutchykun] 共依存 (心理健康与保健)</t>
+        </is>
+      </c>
+      <c r="C385" s="1" t="inlineStr">
+        <is>
+          <t>kutchykun</t>
+        </is>
+      </c>
       <c r="D385" s="1" t="inlineStr">
         <is>
           <t>共依存 (心理健康与保健)</t>
@@ -12005,7 +12765,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t>[[mo̞ɾip̚]] 心流状态 (心理健康与保健)</t>
+          <t>心流状态 (心理健康与保健)</t>
         </is>
       </c>
       <c r="E386" s="1" t="inlineStr">
@@ -12027,10 +12787,14 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>生物回馈 (心理健康与养生)</t>
-        </is>
-      </c>
-      <c r="C387" s="1" t="inlineStr"/>
+          <t>[pachichuitepek] 生物回馈 (心理健康与养生)</t>
+        </is>
+      </c>
+      <c r="C387" s="1" t="inlineStr">
+        <is>
+          <t>pachichuitepek</t>
+        </is>
+      </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
           <t>生物回馈 (心理健康与养生)</t>
@@ -12065,7 +12829,7 @@
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t>[[ˈt͡ɕʰɥi(ː)ja̠ks͈ʌ̹ŋ]] 脆弱性 (心理健康与养生)</t>
+          <t>脆弱性 (心理健康与养生)</t>
         </is>
       </c>
       <c r="E388" s="1" t="inlineStr">
@@ -12097,7 +12861,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)ɡje̞ɡwa̠n]] 世界观 (韩国流行文化)</t>
+          <t>世界观 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -12119,10 +12883,14 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>续约/合约 (韩国流行文化)</t>
-        </is>
-      </c>
-      <c r="C390" s="1" t="inlineStr"/>
+          <t>[kekyechyak] 续约/合约 (韩国流行文化)</t>
+        </is>
+      </c>
+      <c r="C390" s="1" t="inlineStr">
+        <is>
+          <t>kekyechyak</t>
+        </is>
+      </c>
       <c r="D390" s="1" t="inlineStr">
         <is>
           <t>续约/合约 (韩国流行文化)</t>
@@ -12147,10 +12915,14 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>HYBE (韩国流行文化)</t>
-        </is>
-      </c>
-      <c r="C391" s="1" t="inlineStr"/>
+          <t>[achipe] HYBE (韩国流行文化)</t>
+        </is>
+      </c>
+      <c r="C391" s="1" t="inlineStr">
+        <is>
+          <t>achipe</t>
+        </is>
+      </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
           <t>HYBE (韩国流行文化)</t>
@@ -12185,7 +12957,7 @@
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t>[[ˈsʰe̞(ː)dɛ]] 世代 (韩国流行文化)</t>
+          <t>世代 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E392" s="1" t="inlineStr">
@@ -12207,10 +12979,14 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>动物权利 (宠物护理与动物)</t>
-        </is>
-      </c>
-      <c r="C393" s="1" t="inlineStr"/>
+          <t>[tutmimken] 动物权利 (宠物护理与动物)</t>
+        </is>
+      </c>
+      <c r="C393" s="1" t="inlineStr">
+        <is>
+          <t>tutmimken</t>
+        </is>
+      </c>
       <c r="D393" s="1" t="inlineStr">
         <is>
           <t>动物权利 (宠物护理与动物)</t>
@@ -12235,10 +13011,14 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>一网打尽 (韩国流行文化)</t>
-        </is>
-      </c>
-      <c r="C394" s="1" t="inlineStr"/>
+          <t>[chumhim] 一网打尽 (韩国流行文化)</t>
+        </is>
+      </c>
+      <c r="C394" s="1" t="inlineStr">
+        <is>
+          <t>chumhim</t>
+        </is>
+      </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
           <t>一网打尽 (韩国流行文化)</t>
@@ -12263,10 +13043,14 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>刷榜派对 (韩国流行文化)</t>
-        </is>
-      </c>
-      <c r="C395" s="1" t="inlineStr"/>
+          <t>[putkut] 刷榜派对 (韩国流行文化)</t>
+        </is>
+      </c>
+      <c r="C395" s="1" t="inlineStr">
+        <is>
+          <t>putkut</t>
+        </is>
+      </c>
       <c r="D395" s="1" t="inlineStr">
         <is>
           <t>刷榜派对 (韩国流行文化)</t>
@@ -12301,7 +13085,7 @@
       </c>
       <c r="D396" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɭɭa̠ks͈a̠]] 宠物安乐死 (宠物照护与动物)</t>
+          <t>宠物安乐死 (宠物照护与动物)</t>
         </is>
       </c>
       <c r="E396" s="1" t="inlineStr">
@@ -12323,10 +13107,14 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>速通 (游戏与电竞)</t>
-        </is>
-      </c>
-      <c r="C397" s="1" t="inlineStr"/>
+          <t>[ngeiteron] 速通 (游戏与电竞)</t>
+        </is>
+      </c>
+      <c r="C397" s="1" t="inlineStr">
+        <is>
+          <t>ngeiteron</t>
+        </is>
+      </c>
       <c r="D397" s="1" t="inlineStr">
         <is>
           <t>速通 (游戏与电竞)</t>
@@ -12351,10 +13139,14 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>观战者（旁观工具） (游戏与电竞)</t>
-        </is>
-      </c>
-      <c r="C398" s="1" t="inlineStr"/>
+          <t>[chungkopo] 观战者（旁观工具） (游戏与电竞)</t>
+        </is>
+      </c>
+      <c r="C398" s="1" t="inlineStr">
+        <is>
+          <t>chungkopo</t>
+        </is>
+      </c>
       <c r="D398" s="1" t="inlineStr">
         <is>
           <t>观战者（旁观工具） (游戏与电竞)</t>

--- a/languages/ko/output/import/韩语TOPIK3.xlsx
+++ b/languages/ko/output/import/韩语TOPIK3.xlsx
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɭma̠ŋɦa̠da̠]] 渴望&amp;#x0D; (情感)</t>
+          <t>[[ka̠ɭma̠ŋɦa̠da̠]] 渴望 (动词)</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>渴望&amp;#x0D; (情感)</t>
+          <t>渴望 (动词)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK3.xlsx
+++ b/languages/ko/output/import/韩语TOPIK3.xlsx
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>[[sʰa̠sʰɛŋpʰɛn]] Sasaeng (文化)</t>
+          <t>[[sʰa̠sʰɛŋpʰɛn]] 私生饭 (명사)</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Sasaeng (文化)</t>
+          <t>私生饭 (명사)</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>[kutkengmat] Supply Chain (商业)</t>
+          <t>[kutkengmat] 供应链 (명사)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>Supply Chain (商业)</t>
+          <t>供应链 (명사)</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>[atkinkeng] Tangjinjam (俚语)</t>
+          <t>[atkinkeng] 挥霍消费的乐趣；小放纵的快乐 (명사)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>Tangjinjam (俚语)</t>
+          <t>挥霍消费的乐趣；小放纵的快乐 (명사)</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>[herungeit] Crossfit (运动)</t>
+          <t>[herungeit] 混合健身；Crossfit (명사)</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>Crossfit (运动)</t>
+          <t>混合健身；Crossfit (명사)</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>[kakikutmyotchyotngat] MRI (健康与医疗)</t>
+          <t>[kakikutmyotchyotngat] 磁共振成像；MRI (명사)</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>MRI (健康与医疗)</t>
+          <t>磁共振成像；MRI (명사)</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>[pekimryatkingi] Prowess BMI计算器 (健康医疗)</t>
+          <t>[pekimryatkingi] 身体质量指数；BMI (명사)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>Prowess BMI计算器 (健康医疗)</t>
+          <t>身体质量指数；BMI (명사)</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>[kengat] Jesa桌子 (节日庆典)</t>
+          <t>[kengat] 祭桌；祭祀桌 (명사)</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>Jesa桌子 (节日庆典)</t>
+          <t>祭桌；祭祀桌 (명사)</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpʰje̞(ː)bɛk̚]] Pyebaek (传统婚礼仪式) (节日与庆典)</t>
+          <t>[[ˈpʰje̞(ː)bɛk̚]] 币帛；韩国传统婚礼仪式 (명사)</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>Pyebaek (传统婚礼仪式) (节日与庆典)</t>
+          <t>币帛；韩国传统婚礼仪式 (명사)</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>[[judu]] Yudu（夏日沐浴节） (节日与庆典)</t>
+          <t>[[judu]] 流头节；夏日沐浴节 (명사)</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>Yudu（夏日沐浴节） (节日与庆典)</t>
+          <t>流头节；夏日沐浴节 (명사)</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>[[pa̠duk̚]] 围棋 (Baduk) (嗜好与休闲)</t>
+          <t>[[pa̠duk̚]] 围棋 (명사)</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>围棋 (Baduk) (嗜好与休闲)</t>
+          <t>围棋 (명사)</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>[tokkampi] 年糕排 (Tteok Galbi) (韩国饮食)</t>
+          <t>[tokkampi] 烤排骨肉饼；年糕排骨 (명사)</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t>年糕排 (Tteok Galbi) (韩国饮食)</t>
+          <t>烤排骨肉饼；年糕排骨 (명사)</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛud͡ʑʌ̹t̚]] 虾酱 (Saeujeot) (韩国饮食)</t>
+          <t>[[sʰɛud͡ʑʌ̹t̚]] 虾酱 (명사)</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>虾酱 (Saeujeot) (韩国饮食)</t>
+          <t>虾酱 (명사)</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʌ̹k̚]] Jeok (韩国饮食文化)</t>
+          <t>[[t͡ɕʌ̹k̚]] 炙烤肉串；串烧 (명사)</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t>Jeok (韩国饮食文化)</t>
+          <t>炙烤肉串；串烧 (명사)</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>[[mʌ̹ŋɡe̞]] Sea Squirt (韩国饮食文化)</t>
+          <t>[[mʌ̹ŋɡe̞]] 海鞘；海菠萝 (명사)</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t>Sea Squirt (韩国饮食文化)</t>
+          <t>海鞘；海菠萝 (명사)</t>
         </is>
       </c>
       <c r="E370" s="1" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>[nakkipukcheng] Nakji Bokkeum (韩国饮食文化)</t>
+          <t>[nakkipukcheng] 辣炒章鱼 (명사)</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="D371" s="1" t="inlineStr">
         <is>
-          <t>Nakji Bokkeum (韩国饮食文化)</t>
+          <t>辣炒章鱼 (명사)</t>
         </is>
       </c>
       <c r="E371" s="1" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>[chomanti] Fish Mandu (韩国饮食文化)</t>
+          <t>[chomanti] 鱼肉饺子 (명사)</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
-          <t>Fish Mandu (韩国饮食文化)</t>
+          <t>鱼肉饺子 (명사)</t>
         </is>
       </c>
       <c r="E372" s="1" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>[urankik] Toranguk (韩国饮食文化)</t>
+          <t>[urankik] 芋头汤 (명사)</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="D373" s="1" t="inlineStr">
         <is>
-          <t>Toranguk (韩国饮食文化)</t>
+          <t>芋头汤 (명사)</t>
         </is>
       </c>
       <c r="E373" s="1" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[achipe] HYBE (韩国流行文化)</t>
+          <t>[achipe] HYBE (韩国娱乐经纪企划社) (명사)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t>HYBE (韩国流行文化)</t>
+          <t>HYBE (韩国娱乐经纪企划社) (명사)</t>
         </is>
       </c>
       <c r="E391" s="1" t="inlineStr">

--- a/languages/ko/output/import/韩语TOPIK3.xlsx
+++ b/languages/ko/output/import/韩语TOPIK3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,12 +627,12 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>[kychwkkwkot] 课程大纲 (教育)</t>
+          <t>[[kjo.juk̚.kwa.dʑʌŋ]] 课程大纲 (教育)</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>kychwkkwkot</t>
+          <t>[kjo.juk̚.kwa.dʑʌŋ]</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -691,12 +691,12 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>[akchenunmin] 学位论文 (教育)</t>
+          <t>[[ɦa.ɡwi.non.mun]] 学位论文 (教育)</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>akchenunmin</t>
+          <t>[ɦa.ɡwi.non.mun]</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>[[sʰunɯŋ]] 大学修业能力测验 (教育)</t>
+          <t>[[sʰunɯŋ]] 大学修学能力考试 (教育)</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>大学修业能力测验 (教育)</t>
+          <t>大学修学能力考试 (教育)</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>[ymatpata] 充满希望 (情感)</t>
+          <t>[[ɦi.maŋ.tɕʰa.da]] 充满希望 (情感)</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>ymatpata</t>
+          <t>[ɦi.maŋ.tɕʰa.da]</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>[wtumata] 狂喜 (情绪)</t>
+          <t>[[ɦwaŋ.ɦo.ɾa.da]] 狂喜 (情绪)</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>wtumata</t>
+          <t>[ɦwaŋ.ɦo.ɾa.da]</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[kankomata] 渴望 (情绪)</t>
+          <t>[[kan.dʑʌ.ɾa.da]] 渴望 (情绪)</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>kankomata</t>
+          <t>[kan.dʑʌ.ɾa.da]</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>[chykichyatchyatata] 兴高采烈 (情绪)</t>
+          <t>[[ɰi.ɡi.jaŋ.jaŋ.ɦa.da]] 兴高采烈 (情绪)</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>chykichyatchyatata</t>
+          <t>[ɰi.ɡi.jaŋ.jaŋ.ɦa.da]</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[[muŋkxɯɾɦa̠da̠]] 移动 (情感)</t>
+          <t>[[muŋkxɯɾɦa̠da̠]] 哽咽 (情感)</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>移动 (情感)</t>
+          <t>哽咽 (情感)</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[pinnuata] 愤怒 (情感)</t>
+          <t>[[pun.no.ɦa.da]] 愤怒 (情感)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>pinnuata</t>
+          <t>[pun.no.ɦa.da]</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[kyokpinata] 激怒 (情感)</t>
+          <t>[[kjʌk̚.pun.ɦa.da]] 激怒 (情感)</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>kyokpinata</t>
+          <t>[kjʌk̚.pun.ɦa.da]</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] 恐惧 (情感)</t>
+          <t>[[kjʌ̹ŋa̠kʰa̠da̠]] 惊愕 (情感)</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>恐惧 (情感)</t>
+          <t>惊愕 (情感)</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>[kyomchyonata] 决心 (情感)</t>
+          <t>[[kjʌ.ɾjʌn.ɦa.da]] 决心 (情感)</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>kyomchyonata</t>
+          <t>[kjʌ.ɾjʌn.ɦa.da]</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] 组成 (情感)</t>
+          <t>[[t͡ɕʰimt͡ɕʰa̠kʰa̠da̠]] 沉着 (情感)</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>组成 (情感)</t>
+          <t>沉着 (情感)</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>[tamhungcengcemata] 痛快乐 (情感)</t>
+          <t>[[dal.kʰom.ɕip̚.s͈ɯ.ɾa.da]] 痛快乐 (情感)</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>tamhungcengcemata</t>
+          <t>[dal.kʰom.ɕip̚.s͈ɯ.ɾa.da]</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>[[a̠ɾjʌ̹nɦa̠da̠]] 渴望的 (情感)</t>
+          <t>[[a̠ɾjʌ̹nɦa̠da̠]] 朦胧 (情感)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>渴望的 (情感)</t>
+          <t>朦胧 (情感)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>[ketchuata] 憎恨 (情绪)</t>
+          <t>[[tɕɯŋ.o.ɦa.da]] 憎恨 (情绪)</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>ketchuata</t>
+          <t>[tɕɯŋ.o.ɦa.da]</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>[ngotyotngingim] 整形手术 (文化)</t>
+          <t>[[sʌŋ.çʌŋ.su.sul]] 整形手术 (文化)</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ngotyotngingim</t>
+          <t>[sʌŋ.çʌŋ.su.sul]</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>[mikangkakan] 麻木 (情绪)</t>
+          <t>[[mu.kaŋ.ka.kʰaːn]] 麻木 (情绪)</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>mikangkakan</t>
+          <t>[mu.kaŋ.ka.kʰaːn]</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] 花生酱 (食物)</t>
+          <t>[[ka̠ɲd͡ʑa̠ŋɡe̞(ː)d͡ʑa̠ŋ]] 酱油腌蟹 (食物)</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>花生酱 (食物)</t>
+          <t>酱油腌蟹 (食物)</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>[[tʰɛk̚k͈jʌ̹n]] 跆拳 (文化)</t>
+          <t>[[tʰɛk̚k͈jʌ̹n]] 韩国传统摔跤 (文化)</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>跆拳 (文化)</t>
+          <t>韩国传统摔跤 (文化)</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>[kamtepa] 芦苇田 (自然)</t>
+          <t>[[kaɭ.dɛ.pat̚]] 芦苇田 (自然)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>kamtepa</t>
+          <t>[kaɭ.dɛ.pat̚]</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>[anki] 韩纸 (文化)</t>
+          <t>[[han.dʑi]] 韩纸 (文化)</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>anki</t>
+          <t>[han.dʑi]</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>[namtarangke] 飞鼠 (动物)</t>
+          <t>[[naɭ.t͈a.ɾam.tɕɥi]] 飞鼠 (动物)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>namtarangke</t>
+          <t>[naɭ.t͈a.ɾam.tɕɥi]</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>[kiutngek] 绯红色 (颜色与形状)</t>
+          <t>[[tɕu.ɦoŋ.sɛk̚]] 绯红色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>kiutngek</t>
+          <t>[tɕu.ɦoŋ.sɛk̚]</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>[chemeramtengek] 翠绿色 (颜色与形状)</t>
+          <t>[[e.me.ɾaɭ.dɯ.sɛk̚]] 翠绿色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>chemeramtengek</t>
+          <t>[e.me.ɾaɭ.dɯ.sɛk̚]</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>[hupamengek] 钴蓝色 (颜色与形状)</t>
+          <t>[[kʰo.baɭ.dɯ.sɛk̚]] 钴蓝色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>hupamengek</t>
+          <t>[kʰo.baɭ.dɯ.sɛk̚]</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>[upakngek] 琥珀色 (颜色与形状)</t>
+          <t>[[ɦo.baːk̚.sɛk̚]] 琥珀色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>upakngek</t>
+          <t>[ɦo.baːk̚.sɛk̚]</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>[ngitngek] 炭灰色 (颜色与形状)</t>
+          <t>[[ɕuːk̚.s͈ɛk̚]] 炭灰色 (颜色与形状)</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>ngitngek</t>
+          <t>[ɕuːk̚.s͈ɛk̚]</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>[ngikikngon] 垂直线 (颜色与形状)</t>
+          <t>[[su.dʑik̚.sʌn]] 垂直线 (颜色与形状)</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>ngikikngon</t>
+          <t>[su.dʑik̚.sʌn]</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>[tatumring] 欺凌 (校园生活)</t>
+          <t>[[t͈a.to.ɾim]] 欺凌 (校园生活)</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>tatumring</t>
+          <t>[t͈a.to.ɾim]</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>[kichang] 气压 (天气)</t>
+          <t>[[ki.aːp̚]] 气压 (天气)</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>kichang</t>
+          <t>[ki.aːp̚]</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>[ngikot] 可见性 (天气)</t>
+          <t>[[ɕi.dʑʌŋ]] 可见性 (天气)</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>ngikot</t>
+          <t>[ɕi.dʑʌŋ]</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[chingemkong] 露点 (天气)</t>
+          <t>[[i.sɯɭ.tɕʌm]] 露点 (天气)</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>chingemkong</t>
+          <t>[i.sɯɭ.tɕʌm]</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>[katngomryat] 降雪量 (天气)</t>
+          <t>[[kaŋ.sʌɭːjaŋ]] 降雪量 (天气)</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>katngomryat</t>
+          <t>[kaŋ.sʌɭːjaŋ]</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>[uhetngehecho] 口袋巾 (服饰)</t>
+          <t>[[pʰo.kʰet̚.sɯ.kʰwɛ.ʌ]] 口袋巾 (服饰)</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>uhetngehecho</t>
+          <t>[pʰo.kʰet̚.sɯ.kʰwɛ.ʌ]</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[hoerithe] 袖扣 (服饰)</t>
+          <t>[[kʰʌ.pʰɯ.ɾiŋ.kʰɯ]] 袖扣 (服饰)</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>hoerithe</t>
+          <t>[kʰʌ.pʰɯ.ɾiŋ.kʰɯ]</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>[changpikpuk] 压力服 (服饰)</t>
+          <t>[[ap̚.tɕʰuk̚.p͈ok̚]] 压力服 (服饰)</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>changpikpuk</t>
+          <t>[ap̚.tɕʰuk̚.p͈ok̚]</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] 鼬属 (动物)</t>
+          <t>[[t͡ɕo̞k̚t͡ɕ͈e̞bi]] 鼬、黄鼠狼 (动物)</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>鼬属 (动物)</t>
+          <t>鼬、黄鼠狼 (动物)</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>[wikyechyontu] 年度 (数字与时间)</t>
+          <t>[[hwe.ɡje.jʌn.do]] 年度 (数字与时间)</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>wikyechyontu</t>
+          <t>[hwe.ɡje.jʌn.do]</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>[epit] 春季解冻 (天气)</t>
+          <t>[[hɛbiŋ]] 春季解冻 (天气)</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>epit</t>
+          <t>[hɛbiŋ]</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>[ngeukchungngyon] 股票期权 (商业)</t>
+          <t>[[sʰɯtʰoɡop̚ɕʰʌn]] 股票期权 (商业)</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>ngeukchungngyon</t>
+          <t>[sʰɯtʰoɡop̚ɕʰʌn]</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>[pikakapinge] 加值税 (商业)</t>
+          <t>[[puɡaɡatɕʰise]] 加值税 (商业)</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>pikakapinge</t>
+          <t>[puɡaɡatɕʰise]</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>[tepatekuy] 资产负债表 (商业)</t>
+          <t>[[tɛtɕʰatɛtɕop̚pʲʰjʌ]] 资产负债表 (商业)</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>tepatekuy</t>
+          <t>[tɛtɕʰatɛtɕop̚pʲʰjʌ]</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>[penpoheiam] 创投 (商业)</t>
+          <t>[[pɛntɕʰʌkʰɛpʰitʰaɭ]] 创投 (商业)</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>penpoheiam</t>
+          <t>[pɛntɕʰʌkʰɛpʰitʰaɭ]</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>[kichongkutke] 首次公开发行 (商业)</t>
+          <t>[[kiʌp̚koŋɡɛ]] 首次公开发行 (商业)</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>kichongkutke</t>
+          <t>[kiʌp̚koŋɡɛ]</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>[kawinga] 子公司 (商业)</t>
+          <t>[[tɕɥeːsa]] 子公司 (商业)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>kawinga</t>
+          <t>[tɕɥeːsa]</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>[pwikukemipekchingka] 财务长 (商业)</t>
+          <t>[[tɕʰweɡotɕɛmutɕʰɛɡimtɕa]] 财务长 (商业)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>pwikukemipekchingka</t>
+          <t>[tɕʰweɡotɕɛmutɕʰɛɡimtɕa]</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>[pwikuchinchyotpekchingka] 营运长 (商业)</t>
+          <t>[[tɕʰweɡounjʌŋtɕʰɛɡimtɕa]] 营运长 (商业)</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>pwikuchinchyotpekchingka</t>
+          <t>[tɕʰweɡounjʌŋtɕʰɛɡimtɕa]</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>[pamyata] 发酵 (烹饪)</t>
+          <t>[[paɾçoːhada]] 发酵 (烹饪)</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>pamyata</t>
+          <t>[paɾçoːhada]</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
@@ -3539,17 +3539,17 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>[chyongkatata] 治愈 (烹饪)</t>
+          <t>[[jʌmtɕaŋhada]] 腌制；盐渍 (烹饪)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>chyongkatata</t>
+          <t>[jʌmtɕaŋhada]</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>治愈 (烹饪)</t>
+          <t>腌制；盐渍 (烹饪)</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>[inkeata] 烟 (烹饪)</t>
+          <t>[[huntɕehada]] 熏制；烟熏 (烹饪)</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>inkeata</t>
+          <t>[huntɕehada]</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>烟 (烹饪)</t>
+          <t>熏制；烟熏 (烹饪)</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>[ngichikrwm] 利润率 (商业)</t>
+          <t>[[su.iŋɲjul]] 利润率 (商业)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>ngichikrwm</t>
+          <t>[su.iŋɲjul]</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>[kutkengmat] 供应链 (명사)</t>
+          <t>[[koŋɡɯmmaŋ]] 供应链 (명사)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>kutkengmat</t>
+          <t>[koŋɡɯmmaŋ]</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>[atkinkeng] 挥霍消费的乐趣；小放纵的快乐 (명사)</t>
+          <t>[[tʰaŋtɕintɕɛm]] 挥霍消费的乐趣；小放纵的快乐 (명사)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>atkinkeng</t>
+          <t>[tʰaŋtɕintɕɛm]</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>[kekngotngerongta] 没有寒意/强烈 (俚语)</t>
+          <t>[[kɯksʰʌŋsɯɾʌp̚ta]] 热衷；积极；狂热 (俚语)</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>kekngotngerongta</t>
+          <t>[kɯksʰʌŋsɯɾʌp̚ta]</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>没有寒意/强烈 (俚语)</t>
+          <t>热衷；积极；狂热 (俚语)</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>[kunna] 真真 (俚语)</t>
+          <t>[[tɕonna]] 真真 (俚语)</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>kunna</t>
+          <t>[tɕonna]</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>[pyorakkoki] 瞬间赤贫 (俚语)</t>
+          <t>[[pjʌɾak̚k͈ʌdʑi]] 瞬间赤贫 (俚语)</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>pyorakkoki</t>
+          <t>[pjʌɾak̚k͈ʌdʑi]</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>[elngiko] 泥土汤匙 (俚语)</t>
+          <t>[[hɯk̚s͈udʑʌ]] 泥土汤匙 (俚语)</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>elngiko</t>
+          <t>[hɯk̚s͈udʑʌ]</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>[nuryokpit] 努力中毒者 (俚语)</t>
+          <t>[[noɾjʌk̚tɕʰuŋ]] 努力中毒者 (俚语)</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>nuryokpit</t>
+          <t>[noɾjʌk̚tɕʰuŋ]</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>[chyomkotechi] 热情薪资 (俚语)</t>
+          <t>[[jʌɭdʑeŋpʰeː]] 热情薪资 (俚语)</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>chyomkotechi</t>
+          <t>[jʌɭdʑeŋpʰeː]</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>[erachichengemrun] 铁人三项 (运动)</t>
+          <t>[[tʰɯɾaieɕʰɯlːoːn]] 铁人三项 (运动)</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>erachichengemrun</t>
+          <t>[tʰɯɾaieɕʰɯlːoːn]</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>[herungeit] 混合健身；Crossfit (명사)</t>
+          <t>[[kʰɯɾosɯpʰit̚]] 混合健身；Crossfit (명사)</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>herungeit</t>
+          <t>[kʰɯɾosɯpʰit̚]</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>[pemrukpechin] 区块链 (科技)</t>
+          <t>[[pɯɭlok̚tɕʰeːn]] 区块链 (科技)</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>pemrukpechin</t>
+          <t>[pɯɭlok̚tɕʰeːn]</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>[kangatyonngim] 虚拟实境 (科技)</t>
+          <t>[[kasʰaŋçjʌnɕʰiɭ]] 虚拟实境 (科技)</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>kangatyonngim</t>
+          <t>[kasʰaŋçjʌnɕʰiɭ]</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>[ketkatyonngim] 扩增实境 (科技)</t>
+          <t>[[tɕʌŋkaŋçjʌnɕʰiɭ]] 扩增实境 (科技)</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>ketkatyonngim</t>
+          <t>[tɕʌŋkaŋçjʌnɕʰiɭ]</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>[chikikingim] 太空科技 (科技)</t>
+          <t>[[utɕukisʰuɭ]] 太空科技 (科技)</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>chikikingim</t>
+          <t>[utɕukisʰuɭ]</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[chyatkahongwit] 量子计算 (科技)</t>
+          <t>[[jaŋdʑakʰʌmpʰjutʰiŋ]] 量子计算 (科技)</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>chyatkahongwit</t>
+          <t>[jaŋdʑakʰʌmpʰjutʰiŋ]</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>[kengetchenokikingim] 再生能源科技 (科技)</t>
+          <t>[[tɕɛsʰeŋeneɾedʑikisʰuɭ]] 再生能源科技 (科技)</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>kengetchenokikingim</t>
+          <t>[tɕɛsʰeŋeneɾedʑikisʰuɭ]</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>[anchyak] 韩医学 (健康与医疗)</t>
+          <t>[[ha̠niɦa̠k̚]] 韩医学 (健康与医疗)</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>anchyak</t>
+          <t>[ha̠niɦa̠k̚]</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>[kakikutmyotchyotngat] 磁共振成像；MRI (명사)</t>
+          <t>[[t͡ɕa̠ɡiɡo̞ŋmjʌ̹ŋja̠ŋ]] 磁共振成像；MRI (명사)</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>kakikutmyotchyotngat</t>
+          <t>[t͡ɕa̠ɡiɡo̞ŋmjʌ̹ŋja̠ŋ]</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>[ngingkatnekw] 心脏病科 (健康医疗)</t>
+          <t>[[ɕʰimd͡ʑa̠ŋnɛɡwa̠]] 心脏病科 (健康医疗)</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>ngingkatnekw</t>
+          <t>[ɕʰimd͡ʑa̠ŋnɛɡwa̠]</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>[kotyotchwikw] 骨科 (健康医疗)</t>
+          <t>[[t͡ɕʌ̹ŋça̠ŋoe̞ɡwa̠]] 骨科 (健康医疗)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>kotyotchwikw</t>
+          <t>[t͡ɕʌ̹ŋça̠ŋoe̞ɡwa̠]</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>[nginkyotkw] 神经内科 (健康医疗)</t>
+          <t>[[ɕinɡjʌ̹ŋɡwa̠]] 神经内科 (健康医疗)</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>nginkyotkw</t>
+          <t>[ɕinɡjʌ̹ŋɡwa̠]</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>[pekimryatkingi] 身体质量指数；BMI (명사)</t>
+          <t>[[t͡ɕʰe̞d͡ʑiʎʎa̠ŋt͡ɕisu]] 身体质量指数；BMI (명사)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>pekimryatkingi</t>
+          <t>[t͡ɕʰe̞d͡ʑiʎʎa̠ŋt͡ɕisu]</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>[punchinpitangkeng] 定额手续费 (健康医疗)</t>
+          <t>[[po̞ninbuːda̠mɡɯm]] 定额手续费 (健康医疗)</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>punchinpitangkeng</t>
+          <t>[po̞ninbuːda̠mɡɯm]</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>[nginkatpyot] 肾脏疾病 (健康与医疗)</t>
+          <t>[[ɕind͡ʑa̠ŋbjʌ̹ŋ]] 肾脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>nginkatpyot</t>
+          <t>[ɕind͡ʑa̠ŋbjʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>[kankimwn] 肝脏疾病 (健康与医疗)</t>
+          <t>[[ka̠nd͡ʑiɦwa̠n]] 肝脏疾病 (健康与医疗)</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>kankimwn</t>
+          <t>[ka̠nd͡ʑiɦwa̠n]</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>[chenengikyot] 胃镜检查 (健康与医疗)</t>
+          <t>[[ɥine̞ɕiɡjʌ̹ŋ]] 胃镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>chenengikyot</t>
+          <t>[ɥine̞ɕiɡjʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>[tekatnengikyot] 结肠镜检查 (健康与医疗)</t>
+          <t>[[te̞d͡ʑa̠ŋne̞ɕiɡjʌ̹ŋ]] 结肠镜检查 (健康与医疗)</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>tekatnengikyot</t>
+          <t>[te̞d͡ʑa̠ŋne̞ɕiɡjʌ̹ŋ]</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[ungeinge] 临终关怀 (健康医疗)</t>
+          <t>[[ho̞sʰɯpʰisʰɯ]] 临终关怀 (健康医疗)</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>ungeinge</t>
+          <t>[ho̞sʰɯpʰisʰɯ]</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>[kotchemtepureng] 正月大满月（元宵） (节日庆典)</t>
+          <t>[[t͡ɕʌ̹ŋwʌ̹lda̠bo̞ɾɯm]] 正月大满月（元宵） (节日庆典)</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>kotchemtepureng</t>
+          <t>[t͡ɕʌ̹ŋwʌ̹lda̠bo̞ɾɯm]</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>[[ˈpu(ː)ɾʌ̹m]] 布拉姆 (节日庆典)</t>
+          <t>[[ˈpu(ː)ɾʌ̹m]] 正月十五咬坚果习俗（吃核桃、松子等硬壳坚果） (节日庆典)</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>布拉姆 (节日庆典)</t>
+          <t>正月十五咬坚果习俗（吃核桃、松子等硬壳坚果） (节日庆典)</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>[keponkom] 建国纪念日 (节日庆典)</t>
+          <t>[[ke̞t͡ɕʰʌ̹nd͡ʑʌ̹ɭ]] 建国纪念日 (节日庆典)</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>keponkom</t>
+          <t>[ke̞t͡ɕʰʌ̹nd͡ʑʌ̹ɭ]</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>[chyontetwi] 莲花灯节 (节日庆典)</t>
+          <t>[[jʌ̹ndɯŋɦwe̞]] 莲花灯节 (节日庆典)</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>chyontetwi</t>
+          <t>[jʌ̹ndɯŋɦwe̞]</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>[tanchu] 达诺节 (节日庆典)</t>
+          <t>[[ta̠no̞]] 达诺节 (节日庆典)</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>tanchu</t>
+          <t>[ta̠no̞]</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>[kiketu] 希赫多 (节日庆典)</t>
+          <t>[[kid͡ʑe̞do̞]] 忌祭图（祖先忌日祭祀图示）</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>kiketu</t>
+          <t>[kid͡ʑe̞do̞]</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>希赫多 (节日庆典)</t>
+          <t>忌祭图（祖先忌日祭祀图示）</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>[kengat] 祭桌；祭祀桌 (명사)</t>
+          <t>[[t͡ɕe̞sa̠ŋ]] 祭桌；祭祀桌 (명사)</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>kengat</t>
+          <t>[t͡ɕe̞sa̠ŋ]</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>[itmim] 农乐（韩国传统打击乐） (节日庆典)</t>
+          <t>[[pʰuŋmuɭ]] 农乐（韩国传统打击乐） (节日庆典)</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>itmim</t>
+          <t>[pʰuŋmuɭ]</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>[pichykeng] 哀悼金 (节日庆典)</t>
+          <t>[[puɰiɡɯm]] 奠仪；吊唁金 (节日庆典)</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>pichykeng</t>
+          <t>[puɰiɡɯm]</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>哀悼金 (节日庆典)</t>
+          <t>奠仪；吊唁金 (节日庆典)</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕe̞muɭ]] 祭祀食物 (节日与庆典)</t>
+          <t>[[t͡ɕe̞muɭ]] 祭品 (节日与庆典)</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>祭祀食物 (节日与庆典)</t>
+          <t>祭品 (节日与庆典)</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>[[ha̠nɡa̠ɥi]] 丰收之月 (节日与庆典)</t>
+          <t>[[ha̠nɡa̠ɥi]] 韩国中秋节；秋夕 (节日与庆典)</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>丰收之月 (节日与庆典)</t>
+          <t>韩国中秋节；秋夕 (节日与庆典)</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹nsʰʌ̹k̚]] 路沿 (交通)</t>
+          <t>[[jʌ̹nsʰʌ̹k̚]] 路缘石 (交通)</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>路沿 (交通)</t>
+          <t>路缘石 (交通)</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>[tukringchintutka] 独立运动家 (节庆与活动)</t>
+          <t>[[toŋnibunmoŋga]] 独立运动家 (节庆与活动)</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>tukringchintutka</t>
+          <t>[toŋnibunmoŋga]</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
@@ -5811,17 +5811,17 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>[nginche] 神主牌 (节日庆典)</t>
+          <t>[[ɕinwi]] 神位 (节日庆典)</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>nginche</t>
+          <t>[ɕinwi]</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>神主牌 (节日庆典)</t>
+          <t>神位 (节日庆典)</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>[ichamrirunngan] 玻尿酸 (美妆护肤)</t>
+          <t>[[çiaɭɭusaːn]] 玻尿酸 (美妆护肤)</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>ichamrirunngan</t>
+          <t>[çiaɭɭusaːn]</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>[nachichanginchamachite] 烟酰胺 (美妆护肤)</t>
+          <t>[[naiaɕʰinamai̯dɯ]] 烟酰胺 (美妆护肤)</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>nachichanginchamachite</t>
+          <t>[naiaɕʰinamai̯dɯ]</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>[eruumringe] 蜂胶 (美妆护肤)</t>
+          <t>[[pʰɯɾopʰoɭɭisʰɯ]] 蜂胶 (美妆护肤)</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>eruumringe</t>
+          <t>[pʰɯɾopʰoɭɭisʰɯ]</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>[chengem] 安瓶 (美容与护肤)</t>
+          <t>[[ɛmpʰɯɭ]] 安瓶 (美容与护肤)</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>chengem</t>
+          <t>[ɛmpʰɯɭ]</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>[ngeramachite] 神经醯胺 (美容与护肤)</t>
+          <t>[[sʰeɾamai̯dɯ]] 神经醯胺 (美容与护肤)</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>ngeramachite</t>
+          <t>[sʰeɾamai̯dɯ]</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>[rukeing] 玫瑰果 (美容与护肤)</t>
+          <t>[[ɾodʑɯhip̚]] 玫瑰果 (美容与护肤)</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>rukeing</t>
+          <t>[ɾodʑɯhip̚]</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>[chontoun] 肤色底调 (美容与护肤)</t>
+          <t>[[ʌndʌtʰoːn]] 肤色底调 (美容与护肤)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>chontoun</t>
+          <t>[ʌndʌtʰoːn]</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -6291,12 +6291,12 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>[kengngatpongw] 锦上添花 (惯用语与谚语)</t>
+          <t>[[kɯmsaŋtɕʰʌmwa]] 锦上添花 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>kengngatpongw</t>
+          <t>[kɯmsaŋtɕʰʌmwa]</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>[timrema] 两难局面 (惯用语与谚语)</t>
+          <t>[[tʰiɭɭeme̞]] 两难局面 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>timrema</t>
+          <t>[tʰiɭɭeme̞]</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>[tampyonka] 口才出众 (惯用语与谚语)</t>
+          <t>[[taɭbjʌnɡa]] 口才出众 (惯用语与谚语)</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>tampyonka</t>
+          <t>[taɭbjʌnɡa]</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>[[t͡ɕɛda̠nsʰa̠]] 网页装修工 (时尚穿搭)</t>
+          <t>[[t͡ɕɛda̠nsʰa̠]] 裁缝 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>网页装修工 (时尚穿搭)</t>
+          <t>裁缝 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>[[kʰo̞ɭɭa̠bo̞]] 协作 (时尚与风格)</t>
+          <t>[[kʰo̞ɭɭa̠bo̞]] 联名合作 (时尚与风格)</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>协作 (时尚与风格)</t>
+          <t>联名合作 (时尚与风格)</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>[ronchechi] 资金跑道 (时尚穿搭)</t>
+          <t>[[ɾʌnwe̞]] T台；天桥 (时尚穿搭)</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>ronchechi</t>
+          <t>[ɾʌnwe̞]</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>资金跑道 (时尚穿搭)</t>
+          <t>T台；天桥 (时尚穿搭)</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[chunngimkange] 温室气体 (环境)</t>
+          <t>[[o̞nɕiɭɡasʰɨ]] 温室气体 (环境)</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>chunngimkange</t>
+          <t>[o̞nɕiɭɡasʰɨ]</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>[kekuring] 再造林 (环境)</t>
+          <t>[[tɕe̞d͡ʑo̞ɾim]] 再造林 (环境)</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>kekuring</t>
+          <t>[tɕe̞d͡ʑo̞ɾim]</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>[chukunpet] 臭氧层 (环境)</t>
+          <t>[[o̞d͡ʑo̞ntɕʰɯŋ]] 臭氧层 (环境)</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>chukunpet</t>
+          <t>[o̞d͡ʑo̞ntɕʰɯŋ]</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>[nganngotpi] 酸雨 (环境)</t>
+          <t>[[sa̠nsʌŋbi]] 酸雨 (环境)</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>nganngotpi</t>
+          <t>[sa̠nsʌŋbi]</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>[chongngachihemrit] 升级再造 (环境)</t>
+          <t>[[ʌps͈a̠ikʰɯɭɭiŋ]] 升级再造 (环境)</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>chongngachihemrit</t>
+          <t>[ʌps͈a̠ikʰɯɭɭiŋ]</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>[wnkyotpong] 环境法 (环境)</t>
+          <t>[[hwa̠nɡjʌŋp͈ʌp̚]] 环境法 (环境)</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>wnkyotpong</t>
+          <t>[hwa̠nɡjʌŋp͈ʌp̚]</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>[wnkyotpi] 环境部 (环境)</t>
+          <t>[[hwa̠nɡjʌŋbu]] 环境部 (环境)</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>wnkyotpi</t>
+          <t>[hwa̠nɡjʌŋbu]</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>[wnkyotnge] 绿色税 (环境)</t>
+          <t>[[hwa̠nɡjʌŋs͈e̞]] 绿色税 (环境)</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>wnkyotnge</t>
+          <t>[hwa̠nɡjʌŋs͈e̞]</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>[ngipori] 水处理 (环境)</t>
+          <t>[[sutɕʰʌɾi]] 水处理 (环境)</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>ngipori</t>
+          <t>[sutɕʰʌɾi]</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>[nangwik] 过度捕捞 (环境)</t>
+          <t>[[na̠mhjøk̚]] 过度捕捞 (环境)</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>nangwik</t>
+          <t>[na̠mhjøk̚]</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>[pingngik] 腐蚀 (环境)</t>
+          <t>[[tɕʰimsʰik̚]] 腐蚀 (环境)</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>pingngik</t>
+          <t>[tɕʰimsʰik̚]</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[[sʰɛŋtʰɛɦa̠k̚]] 生态 (环境)</t>
+          <t>[[sʰɛŋtʰɛɦa̠k̚]] 生态学 (环境)</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>生态 (环境)</t>
+          <t>生态学 (环境)</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>[tukringchintut] 独立运动 (韩国历史)</t>
+          <t>[[to̞ŋnibunːʌŋ]] 独立运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>tukringchintut</t>
+          <t>[to̞ŋnibunːʌŋ]</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>[ngangchimchintut] 三一运动 (韩国历史)</t>
+          <t>[[sa̠miɾunːʌŋ]] 三一运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>ngangchimchintut</t>
+          <t>[sa̠miɾunːʌŋ]</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>[chingotkye] 李成桂（太祖） (韩国历史)</t>
+          <t>[[iːsʌŋɡe̞]] 李成桂（太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>chingotkye</t>
+          <t>[iːsʌŋɡe̞]</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>[ammantekatkyot] 高丽大藏经 (韩国历史)</t>
+          <t>[[pʰaɭɭa̠nde̞d͡ʑaŋɡjʌŋ]] 高丽大藏经 (韩国历史)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>ammantekatkyot</t>
+          <t>[pʰaɭɭa̠nde̞d͡ʑaŋɡjʌŋ]</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>[chinginngin] 李舜臣将军 (韩国历史)</t>
+          <t>[[iːsunɕin]] 李舜臣将军 (韩国历史)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>chinginngin</t>
+          <t>[iːsunɕin]</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>[chingngikotpi] 临时政府 (韩国历史)</t>
+          <t>[[imsʰid͡ʑʌŋbu]] 临时政府 (韩国历史)</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>chingngikotpi</t>
+          <t>[imsʰid͡ʑʌŋbu]</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>[kukut] 高宗皇帝 (韩国历史)</t>
+          <t>[[koːdʑoŋ]] 高宗皇帝 (韩国历史)</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>kukut</t>
+          <t>[koːdʑoŋ]</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>[teankekik] 大韩帝国 (韩国历史)</t>
+          <t>[[tɛːɦanʨeːɡuk̚]] 大韩帝国 (韩国历史)</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>teankekik</t>
+          <t>[tɛːɦanʨeːɡuk̚]</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>[potchimkonket] 甲午战争 (韩国历史)</t>
+          <t>[[ʨʰʌːŋil ʨʌːndʑɛːŋ]] 甲午战争 (韩国历史)</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>potchimkonket</t>
+          <t>[ʨʰʌːŋil ʨʌːndʑɛːŋ]</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>[pongngotte] 瞻星台天文台 (韩国历史)</t>
+          <t>[[ʨʰʌmsʌŋdɛ]] 瞻星台天文台 (韩国历史)</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>pongngotte</t>
+          <t>[ʨʰʌmsʌŋdɛ]</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>[kutmy] 宗庙 (韩国历史)</t>
+          <t>[[dʑoŋmjo]] 宗庙 (韩国历史)</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>kutmy</t>
+          <t>[dʑoŋmjo]</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>[kwkatkak] 奎章阁御览所 (韩国历史)</t>
+          <t>[[kydʑaŋɡak̚]] 奎章阁御览所 (韩国历史)</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>kwkatkak</t>
+          <t>[kydʑaŋɡak̚]</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>[tutakchintut] 东学运动 (韩国历史)</t>
+          <t>[[toŋɦaɡwundʌŋ]] 东学运动 (韩国历史)</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>tutakchintut</t>
+          <t>[toŋɦaɡwundʌŋ]</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>[kwkongiong] 科举考试 (韩国历史)</t>
+          <t>[[kwaɡʌɕiɦʌm]] 科举考试 (韩国历史)</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>kwkongiong</t>
+          <t>[kwaɡʌɕiɦʌm]</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>[nginpinketu] 朝鲜社会阶级 (韩国历史)</t>
+          <t>[[ɕinbudʑido]] 朝鲜社会阶级 (韩国历史)</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>nginpinketu</t>
+          <t>[ɕinbudʑido]</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>[ngokkimchang] 石窟庵 (韩国历史)</t>
+          <t>[[sʌɡuɾam]] 石窟庵 (韩国历史)</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>ngokkimchang</t>
+          <t>[sʌɡuɾam]</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>[kwkoketu] 科举考试（朝鲜） (韩国历史)</t>
+          <t>[[kwaɡʌdʑido]] 科举考试（朝鲜） (韩国历史)</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>kwkoketu</t>
+          <t>[kwaɡʌdʑido]</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>[utchimnginra] 统一新罗 (韩国历史)</t>
+          <t>[[tʰoŋilɕiɭɭa]] 统一新罗 (韩国历史)</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>utchimnginra</t>
+          <t>[tʰoŋilɕiɭɭa]</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>[chwtkon] 王建（高丽太祖） (韩国历史)</t>
+          <t>[[waŋɡʌn]] 王建（高丽太祖） (韩国历史)</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>chwtkon</t>
+          <t>[waŋɡʌn]</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>[tutchypukang] 东医宝鉴 (韩国历史)</t>
+          <t>[[toŋɯiboɡam]] 东医宝鉴 (韩国历史)</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>tutchypukang</t>
+          <t>[toŋɯiboɡam]</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>[pakkoty] 朴正熙 (韩国历史)</t>
+          <t>[[pak̚tɕʌŋɦi]] 朴正熙 (韩国历史)</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>pakkoty</t>
+          <t>[pak̚tɕʌŋɦi]</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>[chingetman] 李承晚 (韩国历史)</t>
+          <t>[[i sɯŋman]] 李承晚 (韩国历史)</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>chingetman</t>
+          <t>[i sɯŋman]</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>[chankitken] 安重根 (韩国历史)</t>
+          <t>[[andʑuŋɡɯn]] 安重根 (韩国历史)</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t>chankitken</t>
+          <t>[andʑuŋɡɯn]</t>
         </is>
       </c>
       <c r="D248" s="1" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>[kikkingingpechykom] 直指心传 (韩国历史)</t>
+          <t>[[tɕiktɕi ɕimtɕʰejo dʑʌl]] 直指心传 (韩国历史)</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t>kikkingingpechykom</t>
+          <t>[tɕiktɕi ɕimtɕʰejo dʑʌl]</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
@@ -8499,17 +8499,17 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>[kinpike] 君主制 (法律与政府)</t>
+          <t>[[kunbudʑe]] 军政府制；军人统治 (法律与政府)</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t>kinpike</t>
+          <t>[kunbudʑe]</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>君主制 (法律与政府)</t>
+          <t>军政府制；军人统治 (法律与政府)</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>[pengingtan] 陪审团 (法律与政府)</t>
+          <t>[[peɕimdan]] 陪审团 (法律与政府)</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t>pengingtan</t>
+          <t>[peɕimdan]</t>
         </is>
       </c>
       <c r="D256" s="1" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 搜查令 (法律与政府)</t>
+          <t>[[jʌ̹ŋt͡ɕ͈a̠ŋ]] 令状 (法律与政府)</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>搜查令 (法律与政府)</t>
+          <t>令状 (法律与政府)</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>[ngotyrut] 性骚扰 (法律与政府)</t>
+          <t>[[sʌŋɦiɾoŋ]] 性骚扰 (法律与政府)</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t>ngotyrut</t>
+          <t>[sʌŋɦiɾoŋ]</t>
         </is>
       </c>
       <c r="D263" s="1" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>[minpong] 民法 (法律与政府)</t>
+          <t>[[mimbʌp̚]] 民法 (法律与政府)</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>minpong</t>
+          <t>[mimbʌp̚]</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>[kew] 归化 (法律与政府)</t>
+          <t>[[kwiɦwa]] 归化 (法律与政府)</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>kew</t>
+          <t>[kwiɦwa]</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>[kimintetruk] 居民登记 (法律与政府)</t>
+          <t>[[t͡ɕuminɯŋno̞k̚]] 居民登记 (法律与政府)</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>kimintetruk</t>
+          <t>[t͡ɕuminɯŋno̞k̚]</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>[[ko̞ŋmu]] 公务员制度 (法律与政府)</t>
+          <t>[[ko̞ŋmu]] 公务 (法律与政府)</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>公务员制度 (法律与政府)</t>
+          <t>公务 (法律与政府)</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>[kutngungiy] 时效法规 (法律与政府)</t>
+          <t>[[ko̞ŋso̞sʰjo]] 时效法规 (法律与政府)</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>kutngungiy</t>
+          <t>[ko̞ŋso̞sʰjo]</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>[tichwmri] 排灯节 (宗教)</t>
+          <t>[[tiwaɭɭi]] 排灯节 (宗教)</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>tichwmri</t>
+          <t>[tiwaɭɭi]</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>[pimkakirunka] 不可知论者 (宗教)</t>
+          <t>[[puɭɡad͡ʑiɭo̞nd͡ʑa̠]] 不可知论者 (宗教)</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>pimkakirunka</t>
+          <t>[puɭɡad͡ʑiɭo̞nd͡ʑa̠]</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>[[ˈto̞(ː)ɡjo]] 道教徒 (宗教)</t>
+          <t>[[ˈto̞(ː)ɡjo]] 道教 (宗教)</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>道教徒 (宗教)</t>
+          <t>道教 (宗教)</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
@@ -9875,17 +9875,17 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>[pikke] 驱魔 (宗教)</t>
+          <t>[[t͡ɕʰuk̚kwi]] 驱鬼 (宗教)</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>pikke</t>
+          <t>[t͡ɕʰuk̚kwi]</t>
         </is>
       </c>
       <c r="D296" s="1" t="inlineStr">
         <is>
-          <t>驱魔 (宗教)</t>
+          <t>驱鬼 (宗教)</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
@@ -9907,17 +9907,17 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>[hungei] 台湾加权 (金融与银行)</t>
+          <t>[[kʰo̞sɯpʰi]] 韩国综合股价指数 (金融与银行)</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>hungei</t>
+          <t>[kʰo̞sɯpʰi]</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
         <is>
-          <t>台湾加权 (金融与银行)</t>
+          <t>韩国综合股价指数 (金融与银行)</t>
         </is>
       </c>
       <c r="E297" s="1" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>[pongchinnge] 企业税 (金融与银行)</t>
+          <t>[[pʌ̹binsʰe̞]] 企业税 (金融与银行)</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
-          <t>pongchinnge</t>
+          <t>[pʌ̹binsʰe̞]</t>
         </is>
       </c>
       <c r="D299" s="1" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>[puketchin] 担保人 (金融与银行)</t>
+          <t>[[po̞d͡ʑɯŋin]] 担保人 (金融与银行)</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>puketchin</t>
+          <t>[po̞d͡ʑɯŋin]</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>[kengchwtkangtukchechenwi] 金融监督委员会 (金融银行)</t>
+          <t>[[kɯmjɯŋkamdoɡwiwʌnɦwe]] 金融监督委员会 (金融银行)</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>kengchwtkangtukchechenwi</t>
+          <t>[kɯmjɯŋkamdoɡwiwʌnɦwe]</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>[kyotkeyongryokkepamkiki] 经济合作与发展组织（OECD） (金融银行)</t>
+          <t>[[kʌŋdʑeçʌbjʌɡɛbʌlɡigu]] 经济合作与发展组织（OECD） (金融银行)</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t>kyotkeyongryokkepamkiki</t>
+          <t>[kʌŋdʑeçʌbjʌɡɛbʌlɡigu]</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>[kikkeutwkikeng] 国际货币基金组织（IMF） (金融银行)</t>
+          <t>[[kuk̚t͈ɕetʰoŋhwagigɯm]] 国际货币基金组织（IMF） (金融银行)</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t>kikkeutwkikeng</t>
+          <t>[kuk̚t͈ɕetʰoŋhwagigɯm]</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>[ngekyechenet] 世界银行 (金融银行)</t>
+          <t>[[seɡeɯnɦɛŋ]] 世界银行 (金融银行)</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>ngekyechenet</t>
+          <t>[seɡeɯnɦɛŋ]</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>[chinngiangpyot] 并购 (金融银行)</t>
+          <t>[[insuɦap̚p͈jʌŋ]] 并购 (金融银行)</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t>chinngiangpyot</t>
+          <t>[insuɦap̚p͈jʌŋ]</t>
         </is>
       </c>
       <c r="D310" s="1" t="inlineStr">
@@ -10387,17 +10387,17 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>[erechito] 交易商 (金融银行)</t>
+          <t>[[tʰɯɾeidʌ]] 交易员 (金融银行)</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t>erechito</t>
+          <t>[tʰɯɾeidʌ]</t>
         </is>
       </c>
       <c r="D312" s="1" t="inlineStr">
         <is>
-          <t>交易商 (金融银行)</t>
+          <t>交易员 (金融银行)</t>
         </is>
       </c>
       <c r="E312" s="1" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>[hoenchem] 幕墙 (建筑)</t>
+          <t>[[kʰʌtʰɯnwʌl]] 幕墙 (建筑)</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>hoenchem</t>
+          <t>[kʰʌtʰɯnwʌl]</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>[chyttukichyok] 分区 (建筑)</t>
+          <t>[[joŋdodʑijʌk̚]] 分区 (建筑)</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>chyttukichyok</t>
+          <t>[joŋdodʑijʌk̚]</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[kimpapki] 寻路。 (建筑)</t>
+          <t>[[kiltɕʰat̚ki]] 寻路。 (建筑)</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t>kimpapki</t>
+          <t>[kiltɕʰat̚ki]</t>
         </is>
       </c>
       <c r="D315" s="1" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>[netnanpat] 暖通空调 (建筑)</t>
+          <t>[[nɛŋnambaŋ]] 暖通空调 (建筑)</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t>netnanpat</t>
+          <t>[nɛŋnambaŋ]</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>[erieng] 预制 (建筑)</t>
+          <t>[[pʰɯɾipʰap̚]] 预制 (建筑)</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t>erieng</t>
+          <t>[pʰɯɾipʰap̚]</t>
         </is>
       </c>
       <c r="D318" s="1" t="inlineStr">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>[nginkyotkwak] 神经科学 (科学与研究)</t>
+          <t>[[ɕiŋɡjʌŋɡwaɦak̚]] 神经科学 (科学与研究)</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t>nginkyotkwak</t>
+          <t>[ɕiŋɡjʌŋɡwaɦak̚]</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
@@ -10739,12 +10739,12 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>[ruputkutak] 机器人学 (科学与研究)</t>
+          <t>[[ɾobok͈oŋɦak̚]] 机器人学 (科学与研究)</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t>ruputkutak</t>
+          <t>[ɾobok͈oŋɦak̚]</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
@@ -10803,12 +10803,12 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>[ngetmyotkutak] 生物技术 (科学与研究)</t>
+          <t>[[sɛŋmjʌŋkoŋɦak̚]] 生物技术 (科学与研究)</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t>ngetmyotkutak</t>
+          <t>[sɛŋmjʌŋkoŋɦak̚]</t>
         </is>
       </c>
       <c r="D325" s="1" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>[chwkonkutak] 基因工程 (科学与研究)</t>
+          <t>[[judʑʌnkoŋɦak̚]] 基因工程 (科学与研究)</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t>chwkonkutak</t>
+          <t>[judʑʌnkoŋɦak̚]</t>
         </is>
       </c>
       <c r="D326" s="1" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>[kimkingeu] 干细胞 (科学与研究)</t>
+          <t>[[tɕulɡise̞pʰo]] 干细胞 (科学与研究)</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t>kimkingeu</t>
+          <t>[tɕulɡise̞pʰo]</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>[chingngatngiong] 临床试验 (科学与研究)</t>
+          <t>[[imsaŋɕiɦʌm]] 临床试验 (科学与研究)</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t>chingngatngiong</t>
+          <t>[imsaŋɕiɦʌm]</t>
         </is>
       </c>
       <c r="D328" s="1" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>[pakngaichyonkichen] 博士后研究员 (科学与研究)</t>
+          <t>[[paksʰaɦujʌŋɡuwʌn]] 博士后研究员 (科学与研究)</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t>pakngaichyonkichen</t>
+          <t>[paksʰaɦujʌŋɡuwʌn]</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>[meapinngok] 元分析 (科学研究)</t>
+          <t>[[meːtʰapunsʰʌk̚]] 元分析 (科学研究)</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t>meapinngok</t>
+          <t>[meːtʰapunsʰʌk̚]</t>
         </is>
       </c>
       <c r="D330" s="1" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>[tekukin] 对照组 (科学研究)</t>
+          <t>[[tɛːtɕoɡun]] 对照组 (科学研究)</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t>tekukin</t>
+          <t>[tɛːtɕoɡun]</t>
         </is>
       </c>
       <c r="D331" s="1" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>[ngatkwnkwnkye] 相关性 (科学研究)</t>
+          <t>[[saŋɡwaŋɡwaŋɡeː]] 相关性 (科学研究)</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t>ngatkwnkwnkye</t>
+          <t>[saŋɡwaŋɡwaŋɡeː]</t>
         </is>
       </c>
       <c r="D333" s="1" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>[chinkwkwnkye] 因果关系 (科学研究)</t>
+          <t>[[inɡwaŋɡwaŋɡeː]] 因果关系 (科学研究)</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t>chinkwkwnkye</t>
+          <t>[inɡwaŋɡwaŋɡeː]</t>
         </is>
       </c>
       <c r="D334" s="1" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>[tukngotak] 毒理学 (科学与研究)</t>
+          <t>[[toːksʰʌŋɦak̚]] 毒理学 (科学与研究)</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t>tukngotak</t>
+          <t>[toːksʰʌŋɦak̚]</t>
         </is>
       </c>
       <c r="D340" s="1" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>[kerykwak] 材料科学 (科学与研究)</t>
+          <t>[[tɕɛːɾjoɡwaɦak̚]] 材料科学 (科学与研究)</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>kerykwak</t>
+          <t>[tɕɛːɾjoɡwaɦak̚]</t>
         </is>
       </c>
       <c r="D342" s="1" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>[tutchyngo] 知情同意 (科学与研究)</t>
+          <t>[[toːŋɰisʰʌ]] 知情同意 (科学与研究)</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t>tutchyngo</t>
+          <t>[toːŋɰisʰʌ]</t>
         </is>
       </c>
       <c r="D343" s="1" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>[nginkangan] 净资产 (金融与银行)</t>
+          <t>[[suntɕasan]] 净资产 (金融与银行)</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t>nginkangan</t>
+          <t>[suntɕasan]</t>
         </is>
       </c>
       <c r="D345" s="1" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>[konpikpong] 建筑规范 (建筑)</t>
+          <t>[[kʌntɕʰukp͈ʌp̚]] 建筑规范 (建筑)</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
         <is>
-          <t>konpikpong</t>
+          <t>[kʌntɕʰukp͈ʌp̚]</t>
         </is>
       </c>
       <c r="D346" s="1" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>[kopikrwm] 储蓄率 (金融与银行)</t>
+          <t>[[tɕʌtɕʰuŋɲul]] 储蓄率 (金融与银行)</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
         <is>
-          <t>kopikrwm</t>
+          <t>[tɕʌtɕʰuŋɲul]</t>
         </is>
       </c>
       <c r="D347" s="1" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[[tɛdɯɭbo̞]] 木梁 (建筑)</t>
+          <t>[[tɛdɯɭbo̞]] 大梁 (建筑)</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>木梁 (建筑)</t>
+          <t>大梁 (建筑)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>[henimrepo] 悬臂 (建筑)</t>
+          <t>[[kʰɛntʰillebʌ]] 悬臂 (建筑)</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t>henimrepo</t>
+          <t>[kʰɛntʰillebʌ]</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>[nankanpyok] 女儿墙 (建筑)</t>
+          <t>[[naŋɡanp͈jʌk̚]] 女儿墙 (建筑)</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t>nankanpyok</t>
+          <t>[naŋɡanp͈jʌk̚]</t>
         </is>
       </c>
       <c r="D350" s="1" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>[kupat] 高窗 (建筑)</t>
+          <t>[[koːtɕʰaŋ]] 高窗 (建筑)</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t>kupat</t>
+          <t>[koːtɕʰaŋ]</t>
         </is>
       </c>
       <c r="D351" s="1" t="inlineStr">
@@ -11667,12 +11667,12 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>[chingangeu] 厚涂法 (艺术与设计)</t>
+          <t>[[impʰasɯtʰo]] 厚涂法 (艺术与设计)</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t>chingangeu</t>
+          <t>[impʰasɯtʰo]</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>[kikumin] 评论文章 (媒体与新闻)</t>
+          <t>[[kiɡomun]] 评论文章 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
         <is>
-          <t>kikumin</t>
+          <t>[kiɡomun]</t>
         </is>
       </c>
       <c r="D355" s="1" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>[uukonomrikeng] 新闻摄影 (媒体与新闻)</t>
+          <t>[[pʰotʰotɕʌnɛllidʑɯm]] 新闻摄影 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t>uukonomrikeng</t>
+          <t>[pʰotʰotɕʌnɛllidʑɯm]</t>
         </is>
       </c>
       <c r="D356" s="1" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t>[nunyotka] 评论员 (媒体与新闻)</t>
+          <t>[[nonpʰjʌŋɡa]] 评论员 (媒体与新闻)</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
         <is>
-          <t>nunyotka</t>
+          <t>[nonpʰjʌŋɡa]</t>
         </is>
       </c>
       <c r="D357" s="1" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>[ngonkotkichy] 煽情主义 (媒体与新闻学)</t>
+          <t>[[sʌntɕʌŋtɕuɰi]] 煽情主义 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t>ngonkotkichy</t>
+          <t>[sʌntɕʌŋtɕuɰi]</t>
         </is>
       </c>
       <c r="D358" s="1" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>[tingechihe] 深度伪造 (媒体与新闻学)</t>
+          <t>[[tipʰeːkʰ]] 深度伪造 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t>tingechihe</t>
+          <t>[tipʰeːkʰ]</t>
         </is>
       </c>
       <c r="D359" s="1" t="inlineStr">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>[chonrunpong] 媒体法 (媒体与新闻学)</t>
+          <t>[[ʌl.lon.p͈ʌp̚]] 媒体法 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
         <is>
-          <t>chonrunpong</t>
+          <t>[ʌl.lon.p͈ʌp̚]</t>
         </is>
       </c>
       <c r="D360" s="1" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>[patngutken] 广播权限 (媒体与新闻学)</t>
+          <t>[[paŋ.soŋ.k͈wʌn]] 广播权限 (媒体与新闻学)</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
         <is>
-          <t>patngutken</t>
+          <t>[paŋ.soŋ.k͈wʌn]</t>
         </is>
       </c>
       <c r="D361" s="1" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>[yonkingchechenwi] 编辑委员会 (媒体与新闻业)</t>
+          <t>[[pʰjʌn.dʑi.bwi.wʌ.nβwe]] 编辑委员会 (媒体与新闻业)</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t>yonkingchechenwi</t>
+          <t>[pʰjʌn.dʑi.bwi.wʌ.nβwe]</t>
         </is>
       </c>
       <c r="D362" s="1" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>[tokkampi] 烤排骨肉饼；年糕排骨 (명사)</t>
+          <t>[[t͈ʌk̚.kaɾ.bi]] 烤排骨肉饼；年糕排骨 (명사)</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t>tokkampi</t>
+          <t>[t͈ʌk̚.kaɾ.bi]</t>
         </is>
       </c>
       <c r="D367" s="1" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>[nakkipukcheng] 辣炒章鱼 (명사)</t>
+          <t>[[nak̚.tɕi.po.k͈ɯm]] 辣炒章鱼 (명사)</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t>nakkipukcheng</t>
+          <t>[nak̚.tɕi.po.k͈ɯm]</t>
         </is>
       </c>
       <c r="D371" s="1" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>[chomanti] 鱼肉饺子 (명사)</t>
+          <t>[[ʌ.man.du]] 鱼肉饺子 (명사)</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t>chomanti</t>
+          <t>[ʌ.man.du]</t>
         </is>
       </c>
       <c r="D372" s="1" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>[urankik] 芋头汤 (명사)</t>
+          <t>[[tʰo.ɾan.guk̚]] 芋头汤 (명사)</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
         <is>
-          <t>urankik</t>
+          <t>[tʰo.ɾan.guk̚]</t>
         </is>
       </c>
       <c r="D373" s="1" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>[kurikungat] 牛尾汤 (韩国饮食文化)</t>
+          <t>[[k͈o.ɾi.gom.tʰaŋ]] 牛尾汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t>kurikungat</t>
+          <t>[k͈o.ɾi.gom.tʰaŋ]</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>[totokkichi] 烤山药根 (韩国饮食文化)</t>
+          <t>[[tʌ.dʌk̚.ku.i]] 烤山药根 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t>totokkichi</t>
+          <t>[tʌ.dʌk̚.ku.i]</t>
         </is>
       </c>
       <c r="D376" s="1" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>[ponat] 清汤 (韩国饮食文化)</t>
+          <t>[[tɕʰʌn.tʰaŋ]] 清汤 (韩国饮食文化)</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
         <is>
-          <t>ponat</t>
+          <t>[tɕʰʌn.tʰaŋ]</t>
         </is>
       </c>
       <c r="D377" s="1" t="inlineStr">
@@ -12531,12 +12531,12 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t>[chinkiettutpiry] 认知行为疗法 (心理健康与保健)</t>
+          <t>[[in.dʑi.hɛŋ.doŋ.tɕʰi.ɾjo]] 认知行为疗法 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
         <is>
-          <t>chinkiettutpiry</t>
+          <t>[in.dʑi.hɛŋ.doŋ.tɕʰi.ɾjo]</t>
         </is>
       </c>
       <c r="D379" s="1" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>[kutchykun] 共依存 (心理健康与保健)</t>
+          <t>[[koŋ.ɰi.dʑon]] 共依存 (心理健康与保健)</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t>kutchykun</t>
+          <t>[koŋ.ɰi.dʑon]</t>
         </is>
       </c>
       <c r="D385" s="1" t="inlineStr">
@@ -12787,17 +12787,17 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>[pachichuitepek] 生物回馈 (心理健康与养生)</t>
+          <t>[[pa.i.o.pʰi.dɯ.bɛk̚]] 生物反馈 (心理健康与养生)</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t>pachichuitepek</t>
+          <t>[pa.i.o.pʰi.dɯ.bɛk̚]</t>
         </is>
       </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
-          <t>生物回馈 (心理健康与养生)</t>
+          <t>生物反馈 (心理健康与养生)</t>
         </is>
       </c>
       <c r="E387" s="1" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>[kekyechyak] 续约/合约 (韩国流行文化)</t>
+          <t>[[tɕɛ.gje.jak̚]] 续约/合约 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t>kekyechyak</t>
+          <t>[tɕɛ.gje.jak̚]</t>
         </is>
       </c>
       <c r="D390" s="1" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[achipe] HYBE (韩国娱乐经纪企划社) (명사)</t>
+          <t>[[ha.i.bɯ]] HYBE (韩国娱乐经纪企划社) (명사)</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t>achipe</t>
+          <t>[ha.i.bɯ]</t>
         </is>
       </c>
       <c r="D391" s="1" t="inlineStr">
@@ -12979,12 +12979,12 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>[tutmimken] 动物权利 (宠物护理与动物)</t>
+          <t>[[toŋ.muɾ.gwʌn]] 动物权利 (宠物护理与动物)</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t>tutmimken</t>
+          <t>[toŋ.muɾ.gwʌn]</t>
         </is>
       </c>
       <c r="D393" s="1" t="inlineStr">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>[chumhim] 一网打尽 (韩国流行文化)</t>
+          <t>[[ol.kʰil]] 全榜第一；横扫榜单 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t>chumhim</t>
+          <t>[ol.kʰil]</t>
         </is>
       </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t>一网打尽 (韩国流行文化)</t>
+          <t>全榜第一；横扫榜单 (韩国流行文化)</t>
         </is>
       </c>
       <c r="E394" s="1" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>[putkut] 刷榜派对 (韩国流行文化)</t>
+          <t>[[tɕʰoŋ.goŋ]] 刷榜派对 (韩国流行文化)</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t>putkut</t>
+          <t>[tɕʰoŋ.goŋ]</t>
         </is>
       </c>
       <c r="D395" s="1" t="inlineStr">
@@ -13107,12 +13107,12 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>[ngeiteron] 速通 (游戏与电竞)</t>
+          <t>[[sɯ.pʰi.dɯ.ɾʌn]] 速通 (游戏与电竞)</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t>ngeiteron</t>
+          <t>[sɯ.pʰi.dɯ.ɾʌn]</t>
         </is>
       </c>
       <c r="D397" s="1" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>[chungkopo] 观战者（旁观工具） (游戏与电竞)</t>
+          <t>[[op̚.tɕʌ.bʌ]] 观战者（旁观工具） (游戏与电竞)</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t>chungkopo</t>
+          <t>[op̚.tɕʌ.bʌ]</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
